--- a/research/traditional_assets/database/data/mexico/mexico_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_real_estate_operations_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.1801233845183951</v>
       </c>
       <c r="X2">
-        <v>0.09413034437537514</v>
+        <v>0.0941194366234078</v>
       </c>
       <c r="Y2">
-        <v>0.08599304014301996</v>
+        <v>0.0860039478949873</v>
       </c>
       <c r="Z2">
         <v>0.0887040887040887</v>
@@ -662,10 +662,10 @@
         <v>0.06009557754087619</v>
       </c>
       <c r="AB2">
-        <v>0.08318550319829777</v>
+        <v>0.08317765107211271</v>
       </c>
       <c r="AC2">
-        <v>-0.02308992565742159</v>
+        <v>-0.02308207353123652</v>
       </c>
       <c r="AD2">
         <v>848.3</v>
@@ -787,10 +787,10 @@
         <v>0.1801233845183951</v>
       </c>
       <c r="X3">
-        <v>0.09413034437537514</v>
+        <v>0.0941194366234078</v>
       </c>
       <c r="Y3">
-        <v>0.08599304014301996</v>
+        <v>0.0860039478949873</v>
       </c>
       <c r="Z3">
         <v>0.0887040887040887</v>
@@ -799,10 +799,10 @@
         <v>0.06009557754087619</v>
       </c>
       <c r="AB3">
-        <v>0.08318550319829777</v>
+        <v>0.08317765107211271</v>
       </c>
       <c r="AC3">
-        <v>-0.02308992565742159</v>
+        <v>-0.02308207353123652</v>
       </c>
       <c r="AD3">
         <v>848.3</v>
@@ -1139,49 +1139,49 @@
         <v>4.23325635103926</v>
       </c>
       <c r="F2">
-        <v>4.61396430496019</v>
+        <v>4.5369456722664</v>
       </c>
       <c r="G2">
         <v>4.60532030401737</v>
       </c>
       <c r="H2">
-        <v>3.12355048859935</v>
+        <v>3.28794788273616</v>
       </c>
       <c r="I2">
         <v>0.280133412588336</v>
       </c>
       <c r="J2">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="K2">
         <v>2179.9</v>
       </c>
       <c r="L2">
-        <v>2456.32615685354</v>
+        <v>2449.32198899011</v>
       </c>
       <c r="M2">
         <v>2747</v>
       </c>
       <c r="N2">
-        <v>2750.48415685354</v>
+        <v>2773.76198899011</v>
       </c>
       <c r="O2">
         <v>848.3</v>
       </c>
       <c r="P2">
-        <v>575.3579999999999</v>
+        <v>605.64</v>
       </c>
       <c r="Q2">
-        <v>0.0831855031982978</v>
+        <v>0.0831776510721127</v>
       </c>
       <c r="R2">
-        <v>0.0831252217636671</v>
+        <v>0.0827185153579803</v>
       </c>
       <c r="S2">
         <v>0.055060241755517</v>
       </c>
       <c r="T2">
-        <v>0.053730241755517</v>
+        <v>0.051910241755517</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0941303443753751</v>
+        <v>0.0941194366234078</v>
       </c>
       <c r="X2">
-        <v>0.090020340531011</v>
+        <v>0.0904205837585962</v>
       </c>
       <c r="Y2">
         <v>0.703106678313469</v>
       </c>
       <c r="Z2">
-        <v>0.643314612103015</v>
+        <v>0.649283862215318</v>
       </c>
       <c r="AA2">
         <v>848.3</v>
@@ -1236,7 +1236,7 @@
         <v>2179.9</v>
       </c>
       <c r="AK2">
-        <v>0.06873828092673559</v>
+        <v>0.06872276727524602</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08378353746566161</v>
+        <v>0.08377496490093292</v>
       </c>
       <c r="C2">
-        <v>2994.106943515207</v>
+        <v>2994.147261739984</v>
       </c>
       <c r="D2">
-        <v>2712.906943515207</v>
+        <v>2712.947261739984</v>
       </c>
       <c r="E2">
         <v>-848.3</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08378353746566161</v>
+        <v>0.08377496490093292</v>
       </c>
       <c r="T2">
         <v>0.5525820103960151</v>
       </c>
       <c r="U2">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08370548927081979</v>
+        <v>0.08368714242378529</v>
       </c>
       <c r="C3">
-        <v>2968.22626387915</v>
+        <v>2968.818966535154</v>
       </c>
       <c r="D3">
-        <v>2717.308263879151</v>
+        <v>2717.900966535154</v>
       </c>
       <c r="E3">
         <v>-818.0179999999999</v>
@@ -1539,37 +1539,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M3">
-        <v>2.136621858343665</v>
+        <v>2.094227058343665</v>
       </c>
       <c r="N3">
-        <v>201.630044808323</v>
+        <v>201.672439608323</v>
       </c>
       <c r="O3">
-        <v>60.4890134424969</v>
+        <v>60.5017318824969</v>
       </c>
       <c r="P3">
-        <v>141.1410313658261</v>
+        <v>141.1707077258261</v>
       </c>
       <c r="Q3">
-        <v>142.0410313658261</v>
+        <v>142.0707077258261</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08405210793259052</v>
+        <v>0.08404347475376781</v>
       </c>
       <c r="T3">
         <v>0.5564891559240677</v>
       </c>
       <c r="U3">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>95.36861465258484</v>
+        <v>97.299223527284</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08362744107597797</v>
+        <v>0.08359931994663766</v>
       </c>
       <c r="C4">
-        <v>2942.359888530137</v>
+        <v>2943.508794852912</v>
       </c>
       <c r="D4">
-        <v>2721.723888530137</v>
+        <v>2722.872794852912</v>
       </c>
       <c r="E4">
         <v>-787.736</v>
@@ -1621,37 +1621,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M4">
-        <v>4.27324371668733</v>
+        <v>4.188454116687329</v>
       </c>
       <c r="N4">
-        <v>199.4934229499794</v>
+        <v>199.5782125499794</v>
       </c>
       <c r="O4">
-        <v>59.84802688499381</v>
+        <v>59.8734637649938</v>
       </c>
       <c r="P4">
-        <v>139.6453960649856</v>
+        <v>139.7047487849856</v>
       </c>
       <c r="Q4">
-        <v>140.5453960649855</v>
+        <v>140.6047487849855</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08432615942945677</v>
+        <v>0.08431746439951768</v>
       </c>
       <c r="T4">
         <v>0.5604760391159581</v>
       </c>
       <c r="U4">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>47.68430732629242</v>
+        <v>48.64961176364201</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08354939288113616</v>
+        <v>0.08351149746949005</v>
       </c>
       <c r="C5">
-        <v>2916.507887315047</v>
+        <v>2918.21684633505</v>
       </c>
       <c r="D5">
-        <v>2726.153887315047</v>
+        <v>2727.86284633505</v>
       </c>
       <c r="E5">
         <v>-757.454</v>
@@ -1703,37 +1703,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M5">
-        <v>6.409865575030993</v>
+        <v>6.282681175030993</v>
       </c>
       <c r="N5">
-        <v>197.3568010916357</v>
+        <v>197.4839854916357</v>
       </c>
       <c r="O5">
-        <v>59.2070403274907</v>
+        <v>59.2451956474907</v>
       </c>
       <c r="P5">
-        <v>138.149760764145</v>
+        <v>138.238789844145</v>
       </c>
       <c r="Q5">
-        <v>139.0497607641449</v>
+        <v>139.138789844145</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08460586147265016</v>
+        <v>0.08459710331631395</v>
       </c>
       <c r="T5">
         <v>0.564545126085001</v>
       </c>
       <c r="U5">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.78953821752828</v>
+        <v>32.43307450909467</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08347134468629434</v>
+        <v>0.08342367499234241</v>
       </c>
       <c r="C6">
-        <v>2890.670330536246</v>
+        <v>2892.943221355139</v>
       </c>
       <c r="D6">
-        <v>2730.598330536247</v>
+        <v>2732.871221355139</v>
       </c>
       <c r="E6">
         <v>-727.1719999999999</v>
@@ -1785,37 +1785,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M6">
-        <v>8.54648743337466</v>
+        <v>8.376908233374659</v>
       </c>
       <c r="N6">
-        <v>195.220179233292</v>
+        <v>195.389758433292</v>
       </c>
       <c r="O6">
-        <v>58.5660537699876</v>
+        <v>58.61692752998761</v>
       </c>
       <c r="P6">
-        <v>136.6541254633044</v>
+        <v>136.7728309033044</v>
       </c>
       <c r="Q6">
-        <v>137.5541254633044</v>
+        <v>137.6728309033044</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08489139064174341</v>
+        <v>0.0848825680438768</v>
       </c>
       <c r="T6">
         <v>0.5686989856992322</v>
       </c>
       <c r="U6">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.84215366314621</v>
+        <v>24.324805881821</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08339329649145254</v>
+        <v>0.08333585251519479</v>
       </c>
       <c r="C7">
-        <v>2864.847288955303</v>
+        <v>2867.688021025244</v>
       </c>
       <c r="D7">
-        <v>2735.057288955303</v>
+        <v>2737.898021025244</v>
       </c>
       <c r="E7">
         <v>-696.89</v>
@@ -1867,37 +1867,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M7">
-        <v>10.68310929171832</v>
+        <v>10.47113529171832</v>
       </c>
       <c r="N7">
-        <v>193.0835573749484</v>
+        <v>193.2955313749484</v>
       </c>
       <c r="O7">
-        <v>57.92506721248451</v>
+        <v>57.9886594124845</v>
       </c>
       <c r="P7">
-        <v>135.1584901624639</v>
+        <v>135.3068719624638</v>
       </c>
       <c r="Q7">
-        <v>136.0584901624638</v>
+        <v>136.2068719624638</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08518293095123862</v>
+        <v>0.08517404255517783</v>
       </c>
       <c r="T7">
         <v>0.5729402949895525</v>
       </c>
       <c r="U7">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.07372293051697</v>
+        <v>19.4598447054568</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08331524829661072</v>
+        <v>0.08324803003804715</v>
       </c>
       <c r="C8">
-        <v>2839.038833796746</v>
+        <v>2842.451347202744</v>
       </c>
       <c r="D8">
-        <v>2739.530833796746</v>
+        <v>2742.943347202744</v>
       </c>
       <c r="E8">
         <v>-666.6079999999999</v>
@@ -1949,37 +1949,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M8">
-        <v>12.81973115006199</v>
+        <v>12.56536235006199</v>
       </c>
       <c r="N8">
-        <v>190.9469355166047</v>
+        <v>191.2013043166047</v>
       </c>
       <c r="O8">
-        <v>57.28408065498141</v>
+        <v>57.36039129498141</v>
       </c>
       <c r="P8">
-        <v>133.6628548616233</v>
+        <v>133.8409130216233</v>
       </c>
       <c r="Q8">
-        <v>134.5628548616233</v>
+        <v>134.7409130216233</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08548067424604223</v>
+        <v>0.08547171865182568</v>
       </c>
       <c r="T8">
         <v>0.577271844903071</v>
       </c>
       <c r="U8">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.89476910876414</v>
+        <v>16.21653725454734</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08323720010176891</v>
+        <v>0.08316020756089952</v>
       </c>
       <c r="C9">
-        <v>2813.245036751855</v>
+        <v>2817.233302497199</v>
       </c>
       <c r="D9">
-        <v>2744.019036751856</v>
+        <v>2748.007302497199</v>
       </c>
       <c r="E9">
         <v>-636.3259999999999</v>
@@ -2031,37 +2031,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M9">
-        <v>14.95635300840565</v>
+        <v>14.65958940840565</v>
       </c>
       <c r="N9">
-        <v>188.810313658261</v>
+        <v>189.107077258261</v>
       </c>
       <c r="O9">
-        <v>56.64309409747831</v>
+        <v>56.73212317747831</v>
       </c>
       <c r="P9">
-        <v>132.1672195607827</v>
+        <v>132.3749540807827</v>
       </c>
       <c r="Q9">
-        <v>133.0672195607827</v>
+        <v>133.2749540807827</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08578482062245454</v>
+        <v>0.08577579638496058</v>
       </c>
       <c r="T9">
         <v>0.5816965464276331</v>
       </c>
       <c r="U9">
-        <v>0.07055748822216712</v>
+        <v>0.06915748822216712</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.04939024175551698</v>
+        <v>0.04841024175551698</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>13.62408780751212</v>
+        <v>13.89988907532629</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08322075190692708</v>
+        <v>0.08315638508375189</v>
       </c>
       <c r="C10">
-        <v>2783.910775781073</v>
+        <v>2787.172136030777</v>
       </c>
       <c r="D10">
-        <v>2744.966775781073</v>
+        <v>2748.228136030777</v>
       </c>
       <c r="E10">
         <v>-606.044</v>
@@ -2113,37 +2113,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M10">
-        <v>17.35945646674931</v>
+        <v>17.11720046674931</v>
       </c>
       <c r="N10">
-        <v>186.4072101999174</v>
+        <v>186.6494661999174</v>
       </c>
       <c r="O10">
-        <v>55.9221630599752</v>
+        <v>55.99483985997521</v>
       </c>
       <c r="P10">
-        <v>130.4850471399421</v>
+        <v>130.6546263399422</v>
       </c>
       <c r="Q10">
-        <v>131.3850471399421</v>
+        <v>131.5546263399421</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08609557887661493</v>
+        <v>0.0860864845035984</v>
       </c>
       <c r="T10">
         <v>0.5862174371157726</v>
       </c>
       <c r="U10">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.73807872711717</v>
+        <v>11.90420519187642</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08315040371208529</v>
+        <v>0.08307906260660426</v>
       </c>
       <c r="C11">
-        <v>2757.689611904781</v>
+        <v>2761.364871189102</v>
       </c>
       <c r="D11">
-        <v>2749.027611904781</v>
+        <v>2752.702871189102</v>
       </c>
       <c r="E11">
         <v>-575.7619999999999</v>
@@ -2195,37 +2195,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M11">
-        <v>19.52938852509298</v>
+        <v>19.25685052509298</v>
       </c>
       <c r="N11">
-        <v>184.2372781415737</v>
+        <v>184.5098161415737</v>
       </c>
       <c r="O11">
-        <v>55.27118344247211</v>
+        <v>55.35294484247211</v>
       </c>
       <c r="P11">
-        <v>128.9660946991016</v>
+        <v>129.1568712991016</v>
       </c>
       <c r="Q11">
-        <v>129.8660946991016</v>
+        <v>130.0568712991016</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08641316698251511</v>
+        <v>0.08640400093253597</v>
       </c>
       <c r="T11">
         <v>0.5908376880388161</v>
       </c>
       <c r="U11">
-        <v>0.07165748822216711</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.05016024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>10.43384775743748</v>
+        <v>10.58151572611238</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08323405551724346</v>
+        <v>0.08312074012945664</v>
       </c>
       <c r="C12">
-        <v>2722.580175971502</v>
+        <v>2728.669139190138</v>
       </c>
       <c r="D12">
-        <v>2744.200175971502</v>
+        <v>2750.289139190138</v>
       </c>
       <c r="E12">
         <v>-545.48</v>
@@ -2277,37 +2277,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M12">
-        <v>22.36552458343665</v>
+        <v>21.91129458343665</v>
       </c>
       <c r="N12">
-        <v>181.40114208323</v>
+        <v>181.85537208323</v>
       </c>
       <c r="O12">
-        <v>54.42034262496901</v>
+        <v>54.55661162496901</v>
       </c>
       <c r="P12">
-        <v>126.980799458261</v>
+        <v>127.298760458261</v>
       </c>
       <c r="Q12">
-        <v>127.880799458261</v>
+        <v>128.198760458261</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08673781260187974</v>
+        <v>0.0867285732821166</v>
       </c>
       <c r="T12">
         <v>0.595560611204594</v>
       </c>
       <c r="U12">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.110748371069787</v>
+        <v>9.299617870169092</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08317910732240164</v>
+        <v>0.083055317652309</v>
       </c>
       <c r="C13">
-        <v>2695.467251299711</v>
+        <v>2702.177943279116</v>
       </c>
       <c r="D13">
-        <v>2747.369251299711</v>
+        <v>2754.079943279116</v>
       </c>
       <c r="E13">
         <v>-515.198</v>
@@ -2359,37 +2359,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M13">
-        <v>24.60207704178031</v>
+        <v>24.10242404178031</v>
       </c>
       <c r="N13">
-        <v>179.1645896248864</v>
+        <v>179.6642426248864</v>
       </c>
       <c r="O13">
-        <v>53.74937688746591</v>
+        <v>53.8992727874659</v>
       </c>
       <c r="P13">
-        <v>125.4152127374205</v>
+        <v>125.7649698374205</v>
       </c>
       <c r="Q13">
-        <v>126.3152127374204</v>
+        <v>126.6649698374204</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08706975362842109</v>
+        <v>0.08706043939236195</v>
       </c>
       <c r="T13">
         <v>0.6003896674752208</v>
       </c>
       <c r="U13">
-        <v>0.07385748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.05170024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.282498519154352</v>
+        <v>8.454198063790084</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08325015912755983</v>
+        <v>0.08298989517516138</v>
       </c>
       <c r="C14">
-        <v>2661.088803179246</v>
+        <v>2675.697211744101</v>
       </c>
       <c r="D14">
-        <v>2743.272803179246</v>
+        <v>2757.881211744101</v>
       </c>
       <c r="E14">
         <v>-484.916</v>
@@ -2441,45 +2441,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M14">
-        <v>27.38370550012397</v>
+        <v>26.29355350012397</v>
       </c>
       <c r="N14">
-        <v>176.3829611665427</v>
+        <v>177.4731131665427</v>
       </c>
       <c r="O14">
-        <v>52.91488834996282</v>
+        <v>53.24193394996281</v>
       </c>
       <c r="P14">
-        <v>123.4680728165799</v>
+        <v>124.2311792165799</v>
       </c>
       <c r="Q14">
-        <v>124.3680728165799</v>
+        <v>125.1311792165799</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08740923876920204</v>
+        <v>0.0873998479142038</v>
       </c>
       <c r="T14">
         <v>0.6053284750247256</v>
       </c>
       <c r="U14">
-        <v>0.07535748822216712</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.05275024175551698</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.44116484402537</v>
+        <v>7.749681558474244</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08320571093271803</v>
+        <v>0.08299727269801374</v>
       </c>
       <c r="C15">
-        <v>2633.368004496298</v>
+        <v>2644.986027722242</v>
       </c>
       <c r="D15">
-        <v>2745.834004496298</v>
+        <v>2757.452027722242</v>
       </c>
       <c r="E15">
         <v>-454.634</v>
@@ -2523,37 +2523,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M15">
-        <v>29.66568095846764</v>
+        <v>28.79961575846764</v>
       </c>
       <c r="N15">
-        <v>174.100985708199</v>
+        <v>174.967050908199</v>
       </c>
       <c r="O15">
-        <v>52.23029571245971</v>
+        <v>52.49011527245971</v>
       </c>
       <c r="P15">
-        <v>121.8706899957393</v>
+        <v>122.4769356357393</v>
       </c>
       <c r="Q15">
-        <v>122.7706899957393</v>
+        <v>123.3769356357393</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08775652816609289</v>
+        <v>0.08774705893080062</v>
       </c>
       <c r="T15">
         <v>0.6103808183799661</v>
       </c>
       <c r="U15">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.86876754833111</v>
+        <v>7.075325878497368</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.0831612627378762</v>
+        <v>0.08293745022086611</v>
       </c>
       <c r="C16">
-        <v>2605.651992710435</v>
+        <v>2618.188027847925</v>
       </c>
       <c r="D16">
-        <v>2748.399992710435</v>
+        <v>2760.936027847925</v>
       </c>
       <c r="E16">
         <v>-424.3519999999999</v>
@@ -2605,37 +2605,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M16">
-        <v>31.94765641681131</v>
+        <v>31.01497081681131</v>
       </c>
       <c r="N16">
-        <v>171.8190102498554</v>
+        <v>172.7516958498554</v>
       </c>
       <c r="O16">
-        <v>51.54570307495661</v>
+        <v>51.82550875495661</v>
       </c>
       <c r="P16">
-        <v>120.2733071748988</v>
+        <v>120.9261870948988</v>
       </c>
       <c r="Q16">
-        <v>121.1733071748988</v>
+        <v>121.8261870948987</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08811189406058584</v>
+        <v>0.08810234462220203</v>
       </c>
       <c r="T16">
         <v>0.6155506580923051</v>
       </c>
       <c r="U16">
-        <v>0.07535748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.05275024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.378141294878888</v>
+        <v>6.569945458604698</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08326381454303437</v>
+        <v>0.0828776277437185</v>
       </c>
       <c r="C17">
-        <v>2569.456907699278</v>
+        <v>2591.398843077308</v>
       </c>
       <c r="D17">
-        <v>2742.486907699278</v>
+        <v>2764.428843077308</v>
       </c>
       <c r="E17">
         <v>-394.07</v>
@@ -2687,45 +2687,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M17">
-        <v>34.86555387515497</v>
+        <v>33.23032587515496</v>
       </c>
       <c r="N17">
-        <v>168.9011127915117</v>
+        <v>170.5363407915117</v>
       </c>
       <c r="O17">
-        <v>50.67033383745351</v>
+        <v>51.16090223745351</v>
       </c>
       <c r="P17">
-        <v>118.2307789540582</v>
+        <v>119.3754385540582</v>
       </c>
       <c r="Q17">
-        <v>119.1307789540582</v>
+        <v>120.2754385540582</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.08847562150553745</v>
+        <v>0.08846598997693053</v>
       </c>
       <c r="T17">
         <v>0.6208421410919934</v>
       </c>
       <c r="U17">
-        <v>0.07675748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05373024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>5.844354786282913</v>
+        <v>6.13194909469772</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08322916634819257</v>
+        <v>0.08292980526657086</v>
       </c>
       <c r="C18">
-        <v>2541.169856948</v>
+        <v>2558.069896737541</v>
       </c>
       <c r="D18">
-        <v>2744.481856948001</v>
+        <v>2761.381896737541</v>
       </c>
       <c r="E18">
         <v>-363.788</v>
@@ -2769,37 +2769,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M18">
-        <v>37.18992413349864</v>
+        <v>35.93019293349863</v>
       </c>
       <c r="N18">
-        <v>166.576742533168</v>
+        <v>167.836473733168</v>
       </c>
       <c r="O18">
-        <v>49.97302275995041</v>
+        <v>50.35094211995041</v>
       </c>
       <c r="P18">
-        <v>116.6037197732176</v>
+        <v>117.4855316132176</v>
       </c>
       <c r="Q18">
-        <v>117.5037197732176</v>
+        <v>118.3855316132176</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.08884800912774982</v>
+        <v>0.08883829355439064</v>
       </c>
       <c r="T18">
         <v>0.6262596117821504</v>
       </c>
       <c r="U18">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.47908261214023</v>
+        <v>5.671182090332998</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08319451815335074</v>
+        <v>0.08287698278942324</v>
       </c>
       <c r="C19">
-        <v>2512.88571065517</v>
+        <v>2530.872547748165</v>
       </c>
       <c r="D19">
-        <v>2746.47971065517</v>
+        <v>2764.466547748165</v>
       </c>
       <c r="E19">
         <v>-333.506</v>
@@ -2851,37 +2851,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M19">
-        <v>39.5142943918423</v>
+        <v>38.17582999184229</v>
       </c>
       <c r="N19">
-        <v>164.2523722748244</v>
+        <v>165.5908366748244</v>
       </c>
       <c r="O19">
-        <v>49.27571168244732</v>
+        <v>49.67725100244732</v>
       </c>
       <c r="P19">
-        <v>114.9766605923771</v>
+        <v>115.9135856723771</v>
       </c>
       <c r="Q19">
-        <v>115.876660592377</v>
+        <v>116.8135856723771</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.08922936994567815</v>
+        <v>0.08921956830239199</v>
       </c>
       <c r="T19">
         <v>0.6318076239347209</v>
       </c>
       <c r="U19">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.15678363495551</v>
+        <v>5.337583143842823</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08315986995850894</v>
+        <v>0.0828241603122756</v>
       </c>
       <c r="C20">
-        <v>2484.604475168329</v>
+        <v>2503.682097994811</v>
       </c>
       <c r="D20">
-        <v>2748.480475168329</v>
+        <v>2767.558097994811</v>
       </c>
       <c r="E20">
         <v>-303.224</v>
@@ -2933,37 +2933,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M20">
-        <v>41.83866465018595</v>
+        <v>40.42146705018595</v>
       </c>
       <c r="N20">
-        <v>161.9280020164807</v>
+        <v>163.3451996164807</v>
       </c>
       <c r="O20">
-        <v>48.57840060494421</v>
+        <v>49.00355988494422</v>
       </c>
       <c r="P20">
-        <v>113.3496014115365</v>
+        <v>114.3416397315365</v>
       </c>
       <c r="Q20">
-        <v>114.2496014115365</v>
+        <v>115.2416397315365</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.08962003224697059</v>
+        <v>0.08961014243449091</v>
       </c>
       <c r="T20">
         <v>0.6374909534568661</v>
       </c>
       <c r="U20">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.870295655235761</v>
+        <v>5.041050746962666</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08312522176366714</v>
+        <v>0.08277133783512797</v>
       </c>
       <c r="C21">
-        <v>2456.326156853539</v>
+        <v>2476.498570649993</v>
       </c>
       <c r="D21">
-        <v>2750.484156853539</v>
+        <v>2770.656570649993</v>
       </c>
       <c r="E21">
         <v>-272.942</v>
@@ -3015,37 +3015,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M21">
-        <v>44.16303490852962</v>
+        <v>42.66710410852962</v>
       </c>
       <c r="N21">
-        <v>159.6036317581371</v>
+        <v>161.0995625581371</v>
       </c>
       <c r="O21">
-        <v>47.88108952744111</v>
+        <v>48.32986876744111</v>
       </c>
       <c r="P21">
-        <v>111.722542230696</v>
+        <v>112.7696937906959</v>
       </c>
       <c r="Q21">
-        <v>112.6225422306959</v>
+        <v>113.6696937906959</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09002034053101099</v>
+        <v>0.09001036037232067</v>
       </c>
       <c r="T21">
         <v>0.643314612103015</v>
       </c>
       <c r="U21">
-        <v>0.07675748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.05373024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.613964304960194</v>
+        <v>4.77573228659621</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08345457356882532</v>
+        <v>0.08271851535798035</v>
       </c>
       <c r="C22">
-        <v>2407.115251617699</v>
+        <v>2449.321988990115</v>
       </c>
       <c r="D22">
-        <v>2731.555251617699</v>
+        <v>2773.761988990115</v>
       </c>
       <c r="E22">
         <v>-242.66</v>
@@ -3097,45 +3097,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M22">
-        <v>48.06206916687329</v>
+        <v>44.91274116687329</v>
       </c>
       <c r="N22">
-        <v>155.7045974997934</v>
+        <v>158.8539254997934</v>
       </c>
       <c r="O22">
-        <v>46.71137924993801</v>
+        <v>47.65617764993801</v>
       </c>
       <c r="P22">
-        <v>108.9932182498554</v>
+        <v>111.1977478498554</v>
       </c>
       <c r="Q22">
-        <v>109.8932182498554</v>
+        <v>112.0977478498554</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.0904306565221524</v>
+        <v>0.09042058375859618</v>
       </c>
       <c r="T22">
         <v>0.6492838622153178</v>
       </c>
       <c r="U22">
-        <v>0.07935748822216712</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05555024175551698</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.239656556591045</v>
+        <v>4.536945672266398</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08343812537398348</v>
+        <v>0.08303319288083272</v>
       </c>
       <c r="C23">
-        <v>2377.772399153992</v>
+        <v>2400.642294557549</v>
       </c>
       <c r="D23">
-        <v>2732.494399153992</v>
+        <v>2755.364294557549</v>
       </c>
       <c r="E23">
         <v>-212.378</v>
@@ -3179,37 +3179,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M23">
-        <v>50.46517262521695</v>
+        <v>48.74818322521695</v>
       </c>
       <c r="N23">
-        <v>153.3014940414497</v>
+        <v>155.0184834414497</v>
       </c>
       <c r="O23">
-        <v>45.99044821243492</v>
+        <v>46.50554503243492</v>
       </c>
       <c r="P23">
-        <v>107.3110458290148</v>
+        <v>108.5129384090148</v>
       </c>
       <c r="Q23">
-        <v>108.2110458290148</v>
+        <v>109.4129384090148</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09085136025990496</v>
+        <v>0.09084119254705589</v>
       </c>
       <c r="T23">
         <v>0.6554042325836279</v>
       </c>
       <c r="U23">
-        <v>0.07935748822216712</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05555024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.03776814913433</v>
+        <v>4.179984836055597</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.0838374771791417</v>
+        <v>0.08353687040368508</v>
       </c>
       <c r="C24">
-        <v>2324.869479421275</v>
+        <v>2341.415284708909</v>
       </c>
       <c r="D24">
-        <v>2709.873479421276</v>
+        <v>2726.419284708909</v>
       </c>
       <c r="E24">
         <v>-182.096</v>
@@ -3261,37 +3261,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M24">
-        <v>54.66702688356062</v>
+        <v>53.40123928356062</v>
       </c>
       <c r="N24">
-        <v>149.0996397831061</v>
+        <v>150.3654273831061</v>
       </c>
       <c r="O24">
-        <v>44.72989193493181</v>
+        <v>45.10962821493182</v>
       </c>
       <c r="P24">
-        <v>104.3697478481742</v>
+        <v>105.2557991681742</v>
       </c>
       <c r="Q24">
-        <v>105.2697478481742</v>
+        <v>106.1557991681742</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09128285127298455</v>
+        <v>0.09127258617624531</v>
       </c>
       <c r="T24">
         <v>0.6616815355254847</v>
       </c>
       <c r="U24">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.05744024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.727414463213529</v>
+        <v>3.815766626401038</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08383992898429986</v>
+        <v>0.08352604792653745</v>
       </c>
       <c r="C25">
-        <v>2294.449755866791</v>
+        <v>2311.748829225829</v>
       </c>
       <c r="D25">
-        <v>2709.735755866791</v>
+        <v>2727.034829225829</v>
       </c>
       <c r="E25">
         <v>-151.814</v>
@@ -3343,37 +3343,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M25">
-        <v>57.15189174190429</v>
+        <v>55.82856834190429</v>
       </c>
       <c r="N25">
-        <v>146.6147749247624</v>
+        <v>147.9380983247624</v>
       </c>
       <c r="O25">
-        <v>43.98443247742872</v>
+        <v>44.38142949742872</v>
       </c>
       <c r="P25">
-        <v>102.6303424473337</v>
+        <v>103.5566688273337</v>
       </c>
       <c r="Q25">
-        <v>103.5303424473337</v>
+        <v>104.4566688273337</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09172554984484541</v>
+        <v>0.09171518483476435</v>
       </c>
       <c r="T25">
         <v>0.668121885297</v>
       </c>
       <c r="U25">
-        <v>0.08205748822216712</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05744024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.565352964812941</v>
+        <v>3.649863729600992</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08463198078945805</v>
+        <v>0.08398562544938983</v>
       </c>
       <c r="C26">
-        <v>2220.397273780662</v>
+        <v>2255.57005289673</v>
       </c>
       <c r="D26">
-        <v>2665.965273780662</v>
+        <v>2701.138052896731</v>
       </c>
       <c r="E26">
         <v>-121.532</v>
@@ -3425,37 +3425,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M26">
-        <v>63.05256620024794</v>
+        <v>60.29084780024795</v>
       </c>
       <c r="N26">
-        <v>140.7141004664188</v>
+        <v>143.4758188664187</v>
       </c>
       <c r="O26">
-        <v>42.21423013992563</v>
+        <v>43.04274565992562</v>
       </c>
       <c r="P26">
-        <v>98.49987032649312</v>
+        <v>100.4330732064931</v>
       </c>
       <c r="Q26">
-        <v>99.3998703264931</v>
+        <v>101.3330732064931</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09217989837912365</v>
+        <v>0.0921694308264023</v>
       </c>
       <c r="T26">
         <v>0.6747317179572394</v>
       </c>
       <c r="U26">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.231695059318068</v>
+        <v>3.379728003523425</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08466733259461623</v>
+        <v>0.0839944029722422</v>
       </c>
       <c r="C27">
-        <v>2188.194598770466</v>
+        <v>2224.798233217225</v>
       </c>
       <c r="D27">
-        <v>2664.044598770466</v>
+        <v>2700.648233217225</v>
       </c>
       <c r="E27">
         <v>-91.25</v>
@@ -3507,37 +3507,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M27">
-        <v>65.67975645859161</v>
+        <v>62.80296645859161</v>
       </c>
       <c r="N27">
-        <v>138.0869102080751</v>
+        <v>140.9637002080751</v>
       </c>
       <c r="O27">
-        <v>41.42607306242252</v>
+        <v>42.28911006242252</v>
       </c>
       <c r="P27">
-        <v>96.66083714565255</v>
+        <v>98.67459014565256</v>
       </c>
       <c r="Q27">
-        <v>97.56083714565253</v>
+        <v>99.57459014565254</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09264636287431599</v>
+        <v>0.09263579004448394</v>
       </c>
       <c r="T27">
         <v>0.6815178128217519</v>
       </c>
       <c r="U27">
-        <v>0.08675748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.06073024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.102427256945345</v>
+        <v>3.244538883382488</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08639528439977441</v>
+        <v>0.08400318049509456</v>
       </c>
       <c r="C28">
-        <v>2067.291224471622</v>
+        <v>2194.026591151611</v>
       </c>
       <c r="D28">
-        <v>2573.423224471622</v>
+        <v>2700.158591151611</v>
       </c>
       <c r="E28">
         <v>-60.96799999999996</v>
@@ -3589,45 +3589,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M28">
-        <v>75.62913431693528</v>
+        <v>65.31508511693528</v>
       </c>
       <c r="N28">
-        <v>128.1375323497314</v>
+        <v>138.4515815497314</v>
       </c>
       <c r="O28">
-        <v>38.44125970491942</v>
+        <v>41.53547446491942</v>
       </c>
       <c r="P28">
-        <v>89.69627264481198</v>
+        <v>96.91610708481198</v>
       </c>
       <c r="Q28">
-        <v>90.59627264481196</v>
+        <v>97.81610708481196</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09312543451802703</v>
+        <v>0.09311475356575696</v>
       </c>
       <c r="T28">
         <v>0.6884873156555755</v>
       </c>
       <c r="U28">
-        <v>0.09605748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.06724024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.694287968612093</v>
+        <v>3.119748926329315</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.0864957362049326</v>
+        <v>0.08401195801794693</v>
       </c>
       <c r="C29">
-        <v>2031.930337797383</v>
+        <v>2163.255126603297</v>
       </c>
       <c r="D29">
-        <v>2568.344337797384</v>
+        <v>2699.669126603297</v>
       </c>
       <c r="E29">
         <v>-30.68599999999992</v>
@@ -3671,45 +3671,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M29">
-        <v>78.53794717527894</v>
+        <v>67.82720377527895</v>
       </c>
       <c r="N29">
-        <v>125.2287194913877</v>
+        <v>135.9394628913877</v>
       </c>
       <c r="O29">
-        <v>37.56861584741632</v>
+        <v>40.78183886741632</v>
       </c>
       <c r="P29">
-        <v>87.66010364397141</v>
+        <v>95.15762402397141</v>
       </c>
       <c r="Q29">
-        <v>88.56010364397139</v>
+        <v>96.05762402397139</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09361763141225071</v>
+        <v>0.09360683937528405</v>
       </c>
       <c r="T29">
         <v>0.6956477637725177</v>
       </c>
       <c r="U29">
-        <v>0.09605748822216711</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.06724024175551697</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.594499525330163</v>
+        <v>3.0042026697986</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08659618801009078</v>
+        <v>0.0855495355407993</v>
       </c>
       <c r="C30">
-        <v>1996.589458932904</v>
+        <v>2049.886439280837</v>
       </c>
       <c r="D30">
-        <v>2563.285458932904</v>
+        <v>2616.582439280837</v>
       </c>
       <c r="E30">
         <v>-0.4039999999998827</v>
@@ -3753,37 +3753,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M30">
-        <v>81.44676003362261</v>
+        <v>76.95291123362261</v>
       </c>
       <c r="N30">
-        <v>122.3199066330441</v>
+        <v>126.8137554330441</v>
       </c>
       <c r="O30">
-        <v>36.69597198991322</v>
+        <v>38.04412662991322</v>
       </c>
       <c r="P30">
-        <v>85.62393464313085</v>
+        <v>88.76962880313084</v>
       </c>
       <c r="Q30">
-        <v>86.52393464313083</v>
+        <v>89.66962880313082</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09412350044242504</v>
+        <v>0.09411259423507577</v>
       </c>
       <c r="T30">
         <v>0.7030071132260414</v>
       </c>
       <c r="U30">
-        <v>0.09605748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.06724024175551697</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.501838827996943</v>
+        <v>2.647939673757736</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08765073981524897</v>
+        <v>0.08561291306365168</v>
       </c>
       <c r="C31">
-        <v>1914.377333604971</v>
+        <v>2016.28929086965</v>
       </c>
       <c r="D31">
-        <v>2511.355333604971</v>
+        <v>2613.26729086965</v>
       </c>
       <c r="E31">
         <v>29.87799999999993</v>
@@ -3835,45 +3835,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M31">
-        <v>88.48300949196627</v>
+        <v>79.70122949196626</v>
       </c>
       <c r="N31">
-        <v>115.2836571747004</v>
+        <v>124.0654371747004</v>
       </c>
       <c r="O31">
-        <v>34.58509715241012</v>
+        <v>37.21963115241012</v>
       </c>
       <c r="P31">
-        <v>80.69856002229028</v>
+        <v>86.8458060222903</v>
       </c>
       <c r="Q31">
-        <v>81.59856002229026</v>
+        <v>87.74580602229028</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09464361930443529</v>
+        <v>0.09463259571063629</v>
       </c>
       <c r="T31">
         <v>0.7105737682979744</v>
       </c>
       <c r="U31">
-        <v>0.1007574882221671</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.07053024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.302890327042589</v>
+        <v>2.556631409145401</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08778409162040715</v>
+        <v>0.08649529058650404</v>
       </c>
       <c r="C32">
-        <v>1877.678062773994</v>
+        <v>1940.709441775547</v>
       </c>
       <c r="D32">
-        <v>2504.938062773994</v>
+        <v>2567.969441775547</v>
       </c>
       <c r="E32">
         <v>60.15999999999997</v>
@@ -3917,37 +3917,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M32">
-        <v>91.53414775030994</v>
+        <v>85.99254175030993</v>
       </c>
       <c r="N32">
-        <v>112.2325189163567</v>
+        <v>117.7741249163568</v>
       </c>
       <c r="O32">
-        <v>33.66975567490702</v>
+        <v>35.33223747490702</v>
       </c>
       <c r="P32">
-        <v>78.56276324144972</v>
+        <v>82.44188744144972</v>
       </c>
       <c r="Q32">
-        <v>79.46276324144969</v>
+        <v>83.3418874414497</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09517859870536009</v>
+        <v>0.0951674543712128</v>
       </c>
       <c r="T32">
         <v>0.7183566135148196</v>
       </c>
       <c r="U32">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V32">
         <v>0.3</v>
       </c>
       <c r="W32">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.226127316141169</v>
+        <v>2.36958534448637</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08791744342556533</v>
+        <v>0.08658596810935641</v>
       </c>
       <c r="C33">
-        <v>1841.011504480158</v>
+        <v>1905.861231717268</v>
       </c>
       <c r="D33">
-        <v>2498.553504480158</v>
+        <v>2563.403231717268</v>
       </c>
       <c r="E33">
         <v>90.44200000000001</v>
@@ -3999,37 +3999,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M33">
-        <v>94.58528600865361</v>
+        <v>88.85895980865359</v>
       </c>
       <c r="N33">
-        <v>109.1813806580131</v>
+        <v>114.9077068580131</v>
       </c>
       <c r="O33">
-        <v>32.75441419740392</v>
+        <v>34.47231205740393</v>
       </c>
       <c r="P33">
-        <v>76.42696646060915</v>
+        <v>80.43539480060916</v>
       </c>
       <c r="Q33">
-        <v>77.32696646060913</v>
+        <v>81.33539480060914</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09572908475558707</v>
+        <v>0.09571781618137125</v>
       </c>
       <c r="T33">
         <v>0.7263650484480951</v>
       </c>
       <c r="U33">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V33">
         <v>0.3</v>
       </c>
       <c r="W33">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.15431675755597</v>
+        <v>2.293147107567455</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08805079523072352</v>
+        <v>0.08667664563220878</v>
       </c>
       <c r="C34">
-        <v>1804.377409227322</v>
+        <v>1871.029231560127</v>
       </c>
       <c r="D34">
-        <v>2492.201409227323</v>
+        <v>2558.853231560127</v>
       </c>
       <c r="E34">
         <v>120.724</v>
@@ -4081,37 +4081,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M34">
-        <v>97.63642426699728</v>
+        <v>91.72537786699726</v>
       </c>
       <c r="N34">
-        <v>106.1302423996694</v>
+        <v>112.0412887996694</v>
       </c>
       <c r="O34">
-        <v>31.83907271990082</v>
+        <v>33.61238663990083</v>
       </c>
       <c r="P34">
-        <v>74.29116967976859</v>
+        <v>78.4289021597686</v>
       </c>
       <c r="Q34">
-        <v>75.19116967976856</v>
+        <v>79.32890215976857</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.09629576157199721</v>
+        <v>0.09628436510359317</v>
       </c>
       <c r="T34">
         <v>0.7346090255852906</v>
       </c>
       <c r="U34">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V34">
         <v>0.3</v>
       </c>
       <c r="W34">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.086994358882346</v>
+        <v>2.221486260455972</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.0881841470358817</v>
+        <v>0.08676732315506117</v>
       </c>
       <c r="C35">
-        <v>1767.775530050099</v>
+        <v>1836.213355140111</v>
       </c>
       <c r="D35">
-        <v>2485.8815300501</v>
+        <v>2554.319355140111</v>
       </c>
       <c r="E35">
         <v>151.0060000000001</v>
@@ -4163,37 +4163,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M35">
-        <v>100.687562525341</v>
+        <v>94.59179592534093</v>
       </c>
       <c r="N35">
-        <v>103.0791041413257</v>
+        <v>109.1748707413257</v>
       </c>
       <c r="O35">
-        <v>30.92373124239772</v>
+        <v>32.75246122239772</v>
       </c>
       <c r="P35">
-        <v>72.15537289892801</v>
+        <v>76.42240951892802</v>
       </c>
       <c r="Q35">
-        <v>73.05537289892798</v>
+        <v>77.322409518928</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09687935411427032</v>
+        <v>0.09686782593394114</v>
       </c>
       <c r="T35">
         <v>0.7430990915922532</v>
       </c>
       <c r="U35">
-        <v>0.1007574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.07053024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.02375210558288</v>
+        <v>2.154168494987609</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09219689884103989</v>
+        <v>0.08685800067791352</v>
       </c>
       <c r="C36">
-        <v>1561.250086164587</v>
+        <v>1801.413516902802</v>
       </c>
       <c r="D36">
-        <v>2309.638086164587</v>
+        <v>2549.801516902802</v>
       </c>
       <c r="E36">
         <v>181.288</v>
@@ -4245,45 +4245,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M36">
-        <v>120.5209851836846</v>
+        <v>97.45821398368459</v>
       </c>
       <c r="N36">
-        <v>83.24568148298206</v>
+        <v>106.3084526829821</v>
       </c>
       <c r="O36">
-        <v>24.97370444489462</v>
+        <v>31.89253580489463</v>
       </c>
       <c r="P36">
-        <v>58.27197703808744</v>
+        <v>74.41591687808747</v>
       </c>
       <c r="Q36">
-        <v>59.17197703808742</v>
+        <v>75.31591687808745</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.09748063127903656</v>
+        <v>0.09746896739551175</v>
       </c>
       <c r="T36">
         <v>0.7518464323266992</v>
       </c>
       <c r="U36">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.69071524229667</v>
+        <v>2.090810598076208</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09244435064619808</v>
+        <v>0.08694867820076591</v>
       </c>
       <c r="C37">
-        <v>1520.914287057412</v>
+        <v>1766.629631897992</v>
       </c>
       <c r="D37">
-        <v>2299.584287057412</v>
+        <v>2545.299631897993</v>
       </c>
       <c r="E37">
         <v>211.5700000000002</v>
@@ -4327,45 +4327,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M37">
-        <v>124.0657200420283</v>
+        <v>100.3246320420283</v>
       </c>
       <c r="N37">
-        <v>79.70094662463839</v>
+        <v>103.4420346246384</v>
       </c>
       <c r="O37">
-        <v>23.91028398739152</v>
+        <v>31.03261038739152</v>
       </c>
       <c r="P37">
-        <v>55.79066263724688</v>
+        <v>72.4094242372469</v>
       </c>
       <c r="Q37">
-        <v>56.69066263724685</v>
+        <v>73.30942423724687</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.09810040927964175</v>
+        <v>0.09808860551743841</v>
       </c>
       <c r="T37">
         <v>0.7608629220068207</v>
       </c>
       <c r="U37">
-        <v>0.1170574882221671</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.08194024175551699</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.642409092516765</v>
+        <v>2.031073152416888</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09269180245135626</v>
+        <v>0.09061775572361828</v>
       </c>
       <c r="C38">
-        <v>1480.665636486756</v>
+        <v>1566.634258131023</v>
       </c>
       <c r="D38">
-        <v>2289.617636486756</v>
+        <v>2375.586258131023</v>
       </c>
       <c r="E38">
         <v>241.8519999999999</v>
@@ -4409,37 +4409,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M38">
-        <v>127.6104549003719</v>
+        <v>118.6712085003719</v>
       </c>
       <c r="N38">
-        <v>76.15621176629476</v>
+        <v>85.09545816629478</v>
       </c>
       <c r="O38">
-        <v>22.84686352988843</v>
+        <v>25.52863744988843</v>
       </c>
       <c r="P38">
-        <v>53.30934823640634</v>
+        <v>59.56682071640634</v>
       </c>
       <c r="Q38">
-        <v>54.20934823640631</v>
+        <v>60.46682071640632</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.09873955534276586</v>
+        <v>0.09872760733067526</v>
       </c>
       <c r="T38">
         <v>0.770161176989446</v>
       </c>
       <c r="U38">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.596786617724633</v>
+        <v>1.717069112564301</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09293925425651445</v>
+        <v>0.09080783324647065</v>
       </c>
       <c r="C39">
-        <v>1440.503006208598</v>
+        <v>1528.174688233369</v>
       </c>
       <c r="D39">
-        <v>2279.737006208598</v>
+        <v>2367.408688233369</v>
       </c>
       <c r="E39">
         <v>272.134</v>
@@ -4491,37 +4491,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M39">
-        <v>131.1551897587156</v>
+        <v>121.9676309587156</v>
       </c>
       <c r="N39">
-        <v>72.61147690795107</v>
+        <v>81.79903570795109</v>
       </c>
       <c r="O39">
-        <v>21.78344307238532</v>
+        <v>24.53971071238533</v>
       </c>
       <c r="P39">
-        <v>50.82803383556575</v>
+        <v>57.25932499556576</v>
       </c>
       <c r="Q39">
-        <v>51.72803383556572</v>
+        <v>58.15932499556574</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.09939899175710026</v>
+        <v>0.0993868949157609</v>
       </c>
       <c r="T39">
         <v>0.7797546146699323</v>
       </c>
       <c r="U39">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.553630222650994</v>
+        <v>1.670661839251752</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09318670606167265</v>
+        <v>0.09099791076932304</v>
       </c>
       <c r="C40">
-        <v>1400.425287370561</v>
+        <v>1489.771225109921</v>
       </c>
       <c r="D40">
-        <v>2269.941287370561</v>
+        <v>2359.287225109922</v>
       </c>
       <c r="E40">
         <v>302.4159999999999</v>
@@ -4573,37 +4573,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M40">
-        <v>134.6999246170593</v>
+        <v>125.2640534170592</v>
       </c>
       <c r="N40">
-        <v>69.06674204960743</v>
+        <v>78.50261324960744</v>
       </c>
       <c r="O40">
-        <v>20.72002261488223</v>
+        <v>23.55078397488223</v>
       </c>
       <c r="P40">
-        <v>48.3467194347252</v>
+        <v>54.95182927472521</v>
       </c>
       <c r="Q40">
-        <v>49.24671943472518</v>
+        <v>55.85182927472518</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1000797003138326</v>
+        <v>0.1000674498423009</v>
       </c>
       <c r="T40">
         <v>0.7896575180820473</v>
       </c>
       <c r="U40">
-        <v>0.1170574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.08194024175551699</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.512745216791757</v>
+        <v>1.626697054008285</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1126905884554749</v>
+        <v>0.09118798829217539</v>
       </c>
       <c r="C41">
-        <v>795.8658369561144</v>
+        <v>1451.423293307118</v>
       </c>
       <c r="D41">
-        <v>1695.663836956114</v>
+        <v>2351.221293307118</v>
       </c>
       <c r="E41">
         <v>332.6980000000001</v>
@@ -4655,45 +4655,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M41">
-        <v>215.4819286754029</v>
+        <v>128.5604758754029</v>
       </c>
       <c r="N41">
-        <v>-11.71526200873626</v>
+        <v>75.20619079126374</v>
       </c>
       <c r="O41">
-        <v>-3.514578602620878</v>
+        <v>22.56185723737912</v>
       </c>
       <c r="P41">
-        <v>-8.200683406115383</v>
+        <v>52.64433355388462</v>
       </c>
       <c r="Q41">
-        <v>-7.300683406115406</v>
+        <v>53.5443335538846</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1011788160068397</v>
+        <v>0.1007703180451209</v>
       </c>
       <c r="T41">
-        <v>0.8056473810548875</v>
+        <v>0.7998851068519366</v>
       </c>
       <c r="U41">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V41">
-        <v>0.283689682822938</v>
+        <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.1306961812597506</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.9456322760764599</v>
+        <v>1.584986873136277</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1140571633376966</v>
+        <v>0.09137806581502776</v>
       </c>
       <c r="C42">
-        <v>736.0494310088741</v>
+        <v>1413.130325214022</v>
       </c>
       <c r="D42">
-        <v>1666.129431008874</v>
+        <v>2343.210325214022</v>
       </c>
       <c r="E42">
         <v>362.98</v>
@@ -4737,45 +4737,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M42">
-        <v>221.0071063337466</v>
+        <v>131.8568983337466</v>
       </c>
       <c r="N42">
-        <v>-17.2404396670799</v>
+        <v>71.90976833292009</v>
       </c>
       <c r="O42">
-        <v>-5.172131900123969</v>
+        <v>21.57293049987603</v>
       </c>
       <c r="P42">
-        <v>-12.06830776695593</v>
+        <v>50.33683783304407</v>
       </c>
       <c r="Q42">
-        <v>-11.16830776695595</v>
+        <v>51.23683783304405</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1021017962736203</v>
+        <v>0.101496615188035</v>
       </c>
       <c r="T42">
-        <v>0.8190748374058022</v>
+        <v>0.8104536152474888</v>
       </c>
       <c r="U42">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V42">
-        <v>0.2765974407523645</v>
+        <v>0.3</v>
       </c>
       <c r="W42">
-        <v>0.131990213933811</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.9219914691745486</v>
+        <v>1.54536220130787</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1154237382199183</v>
+        <v>0.09156814333788013</v>
       </c>
       <c r="C43">
-        <v>677.2442492942625</v>
+        <v>1374.891760929181</v>
       </c>
       <c r="D43">
-        <v>1637.606249294263</v>
+        <v>2335.253760929182</v>
       </c>
       <c r="E43">
         <v>393.2620000000002</v>
@@ -4819,45 +4819,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M43">
-        <v>226.5322839920903</v>
+        <v>135.1533207920903</v>
       </c>
       <c r="N43">
-        <v>-22.76561732542359</v>
+        <v>68.61334587457642</v>
       </c>
       <c r="O43">
-        <v>-6.829685197627077</v>
+        <v>20.58400376237293</v>
       </c>
       <c r="P43">
-        <v>-15.93593212779651</v>
+        <v>48.02934211220349</v>
       </c>
       <c r="Q43">
-        <v>-15.03593212779654</v>
+        <v>48.92934211220347</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1030560640070715</v>
+        <v>0.1022475325730816</v>
       </c>
       <c r="T43">
-        <v>0.8329574617686125</v>
+        <v>0.821380378164924</v>
       </c>
       <c r="U43">
-        <v>0.1824574882221671</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V43">
-        <v>0.2698511617096239</v>
+        <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.1332211230627953</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>0.8995038723654131</v>
+        <v>1.507670440300361</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1167903131021399</v>
+        <v>0.1093005966447285</v>
       </c>
       <c r="C44">
-        <v>619.3992312014061</v>
+        <v>782.8190937030952</v>
       </c>
       <c r="D44">
-        <v>1610.043231201406</v>
+        <v>1773.463093703095</v>
       </c>
       <c r="E44">
         <v>423.5439999999999</v>
@@ -4901,37 +4901,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M44">
-        <v>232.0574616504339</v>
+        <v>210.6904824504339</v>
       </c>
       <c r="N44">
-        <v>-28.2907949837672</v>
+        <v>-6.923815783767225</v>
       </c>
       <c r="O44">
-        <v>-8.487238495130159</v>
+        <v>-2.077144735130168</v>
       </c>
       <c r="P44">
-        <v>-19.80355648863704</v>
+        <v>-4.846671048637058</v>
       </c>
       <c r="Q44">
-        <v>-18.90355648863707</v>
+        <v>-3.94667104863708</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1040432375244348</v>
+        <v>0.1032954505288979</v>
       </c>
       <c r="T44">
-        <v>0.8473187973163472</v>
+        <v>0.8366288612712454</v>
       </c>
       <c r="U44">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V44">
-        <v>0.263426134049871</v>
+        <v>0.2901412502787408</v>
       </c>
       <c r="W44">
-        <v>0.1343934174713518</v>
+        <v>0.1175934174713518</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.8780871134995701</v>
+        <v>0.9671375009291362</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1181568879843616</v>
+        <v>0.1104991715269502</v>
       </c>
       <c r="C45">
-        <v>562.4666968797389</v>
+        <v>724.1609189290361</v>
       </c>
       <c r="D45">
-        <v>1583.392696879739</v>
+        <v>1745.086918929036</v>
       </c>
       <c r="E45">
         <v>453.826</v>
@@ -4983,37 +4983,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M45">
-        <v>237.5826393087776</v>
+        <v>215.7069225087776</v>
       </c>
       <c r="N45">
-        <v>-33.81597264211089</v>
+        <v>-11.94025584211093</v>
       </c>
       <c r="O45">
-        <v>-10.14479179263327</v>
+        <v>-3.582076752633279</v>
       </c>
       <c r="P45">
-        <v>-23.67118084947763</v>
+        <v>-8.35817908947765</v>
       </c>
       <c r="Q45">
-        <v>-22.77118084947765</v>
+        <v>-7.458179089477673</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.105065048709074</v>
+        <v>0.10430414264344</v>
       </c>
       <c r="T45">
-        <v>0.8621840393745287</v>
+        <v>0.8513065605917934</v>
       </c>
       <c r="U45">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V45">
-        <v>0.2572999448859205</v>
+        <v>0.2833937793420259</v>
       </c>
       <c r="W45">
-        <v>0.13551118655858</v>
+        <v>0.1187111865585801</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.8576664829530685</v>
+        <v>0.9446459311400863</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1195234628665833</v>
+        <v>0.1116977464091719</v>
       </c>
       <c r="C46">
-        <v>506.4020719918244</v>
+        <v>666.3965056673337</v>
       </c>
       <c r="D46">
-        <v>1557.610071991824</v>
+        <v>1717.604505667334</v>
       </c>
       <c r="E46">
         <v>484.1079999999999</v>
@@ -5065,37 +5065,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M46">
-        <v>243.1078169671212</v>
+        <v>220.7233625671213</v>
       </c>
       <c r="N46">
-        <v>-39.34115030045456</v>
+        <v>-16.95669590045458</v>
       </c>
       <c r="O46">
-        <v>-11.80234509013637</v>
+        <v>-5.087008770136372</v>
       </c>
       <c r="P46">
-        <v>-27.53880521031819</v>
+        <v>-11.8696871303182</v>
       </c>
       <c r="Q46">
-        <v>-26.63880521031821</v>
+        <v>-10.96968713031823</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1061233531503075</v>
+        <v>0.1053488594763585</v>
       </c>
       <c r="T46">
-        <v>0.8775801829347882</v>
+        <v>0.8665084634595041</v>
       </c>
       <c r="U46">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V46">
-        <v>0.2514522188657859</v>
+        <v>0.2769530116297071</v>
       </c>
       <c r="W46">
-        <v>0.1365781479600252</v>
+        <v>0.1197781479600252</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.8381740628859532</v>
+        <v>0.9231767054323572</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1208900377488049</v>
+        <v>0.1128963212913935</v>
       </c>
       <c r="C47">
-        <v>451.1636389266635</v>
+        <v>609.4842825287149</v>
       </c>
       <c r="D47">
-        <v>1532.653638926663</v>
+        <v>1690.974282528715</v>
       </c>
       <c r="E47">
         <v>514.3900000000001</v>
@@ -5147,37 +5147,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M47">
-        <v>248.6329946254649</v>
+        <v>225.7398026254649</v>
       </c>
       <c r="N47">
-        <v>-44.86632795879825</v>
+        <v>-21.97313595879825</v>
       </c>
       <c r="O47">
-        <v>-13.45989838763948</v>
+        <v>-6.591940787639476</v>
       </c>
       <c r="P47">
-        <v>-31.40642957115877</v>
+        <v>-15.38119517115878</v>
       </c>
       <c r="Q47">
-        <v>-30.5064295711588</v>
+        <v>-14.4811951711588</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.107220141389404</v>
+        <v>0.1064315660122923</v>
       </c>
       <c r="T47">
-        <v>0.8935361862608752</v>
+        <v>0.8822631627951313</v>
       </c>
       <c r="U47">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V47">
-        <v>0.2458643917798796</v>
+        <v>0.2707985002601581</v>
       </c>
       <c r="W47">
-        <v>0.1375976888547395</v>
+        <v>0.1207976888547395</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8195479725995987</v>
+        <v>0.9026616675338603</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1222566126310266</v>
+        <v>0.1140948961736152</v>
       </c>
       <c r="C48">
-        <v>396.712311552601</v>
+        <v>553.3852169000354</v>
       </c>
       <c r="D48">
-        <v>1508.484311552601</v>
+        <v>1665.157216900035</v>
       </c>
       <c r="E48">
         <v>544.672</v>
@@ -5229,37 +5229,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M48">
-        <v>254.1581722838086</v>
+        <v>230.7562426838086</v>
       </c>
       <c r="N48">
-        <v>-50.39150561714189</v>
+        <v>-26.98957601714193</v>
       </c>
       <c r="O48">
-        <v>-15.11745168514257</v>
+        <v>-8.096872805142578</v>
       </c>
       <c r="P48">
-        <v>-35.27405393199932</v>
+        <v>-18.89270321199935</v>
       </c>
       <c r="Q48">
-        <v>-34.37405393199934</v>
+        <v>-17.99270321199937</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1083575514151337</v>
+        <v>0.1075543727902977</v>
       </c>
       <c r="T48">
-        <v>0.9100831526731137</v>
+        <v>0.8986013695135597</v>
       </c>
       <c r="U48">
-        <v>0.1824574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V48">
-        <v>0.2405195136977083</v>
+        <v>0.264911576341459</v>
       </c>
       <c r="W48">
-        <v>0.1385729018844661</v>
+        <v>0.1217729018844662</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8017317123256944</v>
+        <v>0.8830385878048633</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1490920325850154</v>
+        <v>0.1152934710558369</v>
       </c>
       <c r="C49">
-        <v>9.753166391072</v>
+        <v>498.0626240540159</v>
       </c>
       <c r="D49">
-        <v>1151.807166391072</v>
+        <v>1640.116624054016</v>
       </c>
       <c r="E49">
         <v>574.954</v>
@@ -5311,45 +5311,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M49">
-        <v>333.9772087421522</v>
+        <v>235.7726827421523</v>
       </c>
       <c r="N49">
-        <v>-130.2105420754856</v>
+        <v>-32.00601607548558</v>
       </c>
       <c r="O49">
-        <v>-39.06316262264567</v>
+        <v>-9.601804822645672</v>
       </c>
       <c r="P49">
-        <v>-91.14737945283989</v>
+        <v>-22.4042112528399</v>
       </c>
       <c r="Q49">
-        <v>-90.24737945283991</v>
+        <v>-21.50421125283993</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1113017411998855</v>
+        <v>0.1087195496353977</v>
       </c>
       <c r="T49">
-        <v>0.9529150324504082</v>
+        <v>0.9155561123345702</v>
       </c>
       <c r="U49">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V49">
-        <v>0.1830364420082196</v>
+        <v>0.2592751598235556</v>
       </c>
       <c r="W49">
-        <v>0.191706616487396</v>
+        <v>0.122706616487396</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.6101214733607321</v>
+        <v>0.8642505327451855</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1509806074672371</v>
+        <v>0.1164920459380585</v>
       </c>
       <c r="C50">
-        <v>-39.38149929972474</v>
+        <v>443.4819932274297</v>
       </c>
       <c r="D50">
-        <v>1132.954500700275</v>
+        <v>1615.817993227429</v>
       </c>
       <c r="E50">
         <v>605.2359999999999</v>
@@ -5393,45 +5393,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M50">
-        <v>341.0831068004959</v>
+        <v>240.7891228004959</v>
       </c>
       <c r="N50">
-        <v>-137.3164401338292</v>
+        <v>-37.02245613382922</v>
       </c>
       <c r="O50">
-        <v>-41.19493204014876</v>
+        <v>-11.10673684014877</v>
       </c>
       <c r="P50">
-        <v>-96.12150809368046</v>
+        <v>-25.91571929368046</v>
       </c>
       <c r="Q50">
-        <v>-95.22150809368048</v>
+        <v>-25.01571929368048</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1125613900691141</v>
+        <v>0.1099295409745399</v>
       </c>
       <c r="T50">
-        <v>0.9712403215359928</v>
+        <v>0.9331629606486966</v>
       </c>
       <c r="U50">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V50">
-        <v>0.179223182799715</v>
+        <v>0.2538735939938982</v>
       </c>
       <c r="W50">
-        <v>0.1926014263152037</v>
+        <v>0.1236014263152037</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.5974106093323834</v>
+        <v>0.8462453133129941</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1528691823494588</v>
+        <v>0.1176906208202802</v>
       </c>
       <c r="C51">
-        <v>-87.90894674674405</v>
+        <v>389.6108289336871</v>
       </c>
       <c r="D51">
-        <v>1114.709053253256</v>
+        <v>1592.228828933687</v>
       </c>
       <c r="E51">
         <v>635.518</v>
@@ -5475,45 +5475,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M51">
-        <v>348.1890048588396</v>
+        <v>245.8055628588396</v>
       </c>
       <c r="N51">
-        <v>-144.4223381921729</v>
+        <v>-42.03889619217293</v>
       </c>
       <c r="O51">
-        <v>-43.32670145765188</v>
+        <v>-12.61166885765188</v>
       </c>
       <c r="P51">
-        <v>-101.0956367345211</v>
+        <v>-29.42722733452105</v>
       </c>
       <c r="Q51">
-        <v>-100.1956367345211</v>
+        <v>-28.52722733452107</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1138704369332144</v>
+        <v>0.1111869829544329</v>
       </c>
       <c r="T51">
-        <v>0.9902842494092476</v>
+        <v>0.9514602736025927</v>
       </c>
       <c r="U51">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V51">
-        <v>0.1755655668242106</v>
+        <v>0.2486925002389207</v>
       </c>
       <c r="W51">
-        <v>0.1934597132928968</v>
+        <v>0.1244597132928968</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.5852185560807022</v>
+        <v>0.8289750007964023</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1547577572316804</v>
+        <v>0.1188891957025019</v>
       </c>
       <c r="C52">
-        <v>-135.858047481574</v>
+        <v>336.4185059753931</v>
       </c>
       <c r="D52">
-        <v>1097.041952518426</v>
+        <v>1569.318505975393</v>
       </c>
       <c r="E52">
         <v>665.8</v>
@@ -5557,45 +5557,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M52">
-        <v>355.2949029171833</v>
+        <v>250.8220029171833</v>
       </c>
       <c r="N52">
-        <v>-151.5282362505166</v>
+        <v>-47.05533625051658</v>
       </c>
       <c r="O52">
-        <v>-45.45847087515497</v>
+        <v>-14.11660087515497</v>
       </c>
       <c r="P52">
-        <v>-106.0697653753616</v>
+        <v>-32.9387353753616</v>
       </c>
       <c r="Q52">
-        <v>-105.1697653753616</v>
+        <v>-32.03873537536163</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1152318456718786</v>
+        <v>0.1124947226135215</v>
       </c>
       <c r="T52">
-        <v>1.010089934397433</v>
+        <v>0.9704894790746444</v>
       </c>
       <c r="U52">
-        <v>0.2346574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V52">
-        <v>0.1720542554877264</v>
+        <v>0.2437186502341423</v>
       </c>
       <c r="W52">
-        <v>0.1942836687914822</v>
+        <v>0.1252836687914822</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.5735141849590881</v>
+        <v>0.8123955007804743</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1566463321139021</v>
+        <v>0.1487654080771115</v>
       </c>
       <c r="C53">
-        <v>-183.2558712449211</v>
+        <v>-108.1354826206812</v>
       </c>
       <c r="D53">
-        <v>1079.926128755079</v>
+        <v>1155.046517379319</v>
       </c>
       <c r="E53">
         <v>696.0819999999999</v>
@@ -5639,37 +5639,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M53">
-        <v>362.4008009755269</v>
+        <v>339.2350709755269</v>
       </c>
       <c r="N53">
-        <v>-158.6341343088602</v>
+        <v>-135.4684043088602</v>
       </c>
       <c r="O53">
-        <v>-47.59024029265807</v>
+        <v>-40.64052129265806</v>
       </c>
       <c r="P53">
-        <v>-111.0438940162022</v>
+        <v>-94.82788301620212</v>
       </c>
       <c r="Q53">
-        <v>-110.1438940162022</v>
+        <v>-93.92788301620214</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1166488221141619</v>
+        <v>0.1161775485696912</v>
       </c>
       <c r="T53">
-        <v>1.030704014691258</v>
+        <v>1.024079084123861</v>
       </c>
       <c r="U53">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V53">
-        <v>0.1686806426350259</v>
+        <v>0.1801995289703111</v>
       </c>
       <c r="W53">
-        <v>0.195075312309731</v>
+        <v>0.180075312309731</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5622688087834197</v>
+        <v>0.6006650965677037</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1585349069961238</v>
+        <v>0.1505039829593331</v>
       </c>
       <c r="C54">
-        <v>-230.1278243832378</v>
+        <v>-155.8926356321795</v>
       </c>
       <c r="D54">
-        <v>1063.336175616762</v>
+        <v>1137.57136436782</v>
       </c>
       <c r="E54">
         <v>726.364</v>
@@ -5721,37 +5721,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M54">
-        <v>369.5066990338706</v>
+        <v>345.8867390338706</v>
       </c>
       <c r="N54">
-        <v>-165.7400323672039</v>
+        <v>-142.1200723672039</v>
       </c>
       <c r="O54">
-        <v>-49.72200971016117</v>
+        <v>-42.63602171016117</v>
       </c>
       <c r="P54">
-        <v>-116.0180226570427</v>
+        <v>-99.48405065704273</v>
       </c>
       <c r="Q54">
-        <v>-115.1180226570428</v>
+        <v>-98.58405065704275</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1181248392415402</v>
+        <v>0.1176437474982265</v>
       </c>
       <c r="T54">
-        <v>1.052177014997326</v>
+        <v>1.045414065043109</v>
       </c>
       <c r="U54">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V54">
-        <v>0.1654367841228139</v>
+        <v>0.1767341534131897</v>
       </c>
       <c r="W54">
-        <v>0.1958365080003547</v>
+        <v>0.1808365080003547</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5514559470760463</v>
+        <v>0.5891138447106324</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1604234818783455</v>
+        <v>0.1522425578415548</v>
       </c>
       <c r="C55">
-        <v>-276.4977756819533</v>
+        <v>-203.1288925604974</v>
       </c>
       <c r="D55">
-        <v>1047.248224318047</v>
+        <v>1120.617107439502</v>
       </c>
       <c r="E55">
         <v>756.646</v>
@@ -5803,37 +5803,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M55">
-        <v>376.6125970922142</v>
+        <v>352.5384070922142</v>
       </c>
       <c r="N55">
-        <v>-172.8459304255476</v>
+        <v>-148.7717404255476</v>
       </c>
       <c r="O55">
-        <v>-51.85377912766426</v>
+        <v>-44.63152212766427</v>
       </c>
       <c r="P55">
-        <v>-120.9921512978833</v>
+        <v>-104.1402182978833</v>
       </c>
       <c r="Q55">
-        <v>-120.0921512978833</v>
+        <v>-103.2402182978833</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1196636656083815</v>
+        <v>0.1191723378705291</v>
       </c>
       <c r="T55">
-        <v>1.074563759997269</v>
+        <v>1.067656917490834</v>
       </c>
       <c r="U55">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V55">
-        <v>0.1623153353657797</v>
+        <v>0.1733995467450163</v>
       </c>
       <c r="W55">
-        <v>0.1965689793252946</v>
+        <v>0.1815689793252946</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5410511178859322</v>
+        <v>0.5779984891500545</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1623120567605671</v>
+        <v>0.1539811327237765</v>
       </c>
       <c r="C56">
-        <v>-322.3881709460466</v>
+        <v>-249.8672015477925</v>
       </c>
       <c r="D56">
-        <v>1031.639829053953</v>
+        <v>1104.160798452207</v>
       </c>
       <c r="E56">
         <v>786.9280000000001</v>
@@ -5885,37 +5885,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M56">
-        <v>383.7184951505579</v>
+        <v>359.1900751505579</v>
       </c>
       <c r="N56">
-        <v>-179.9518284838913</v>
+        <v>-155.4234084838912</v>
       </c>
       <c r="O56">
-        <v>-53.98554854516738</v>
+        <v>-46.62702254516736</v>
       </c>
       <c r="P56">
-        <v>-125.9662799387239</v>
+        <v>-108.7963859387239</v>
       </c>
       <c r="Q56">
-        <v>-125.0662799387239</v>
+        <v>-107.8963859387239</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1212693974694333</v>
+        <v>0.1207673886938015</v>
       </c>
       <c r="T56">
-        <v>1.09792384173634</v>
+        <v>1.090866850479765</v>
       </c>
       <c r="U56">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V56">
-        <v>0.1593094958219689</v>
+        <v>0.170188444027516</v>
       </c>
       <c r="W56">
-        <v>0.1972743220826441</v>
+        <v>0.1822743220826441</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5310316527398964</v>
+        <v>0.5672948134250535</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1642006316427888</v>
+        <v>0.1557197076059982</v>
       </c>
       <c r="C57">
-        <v>-367.8201374846992</v>
+        <v>-296.1291822671446</v>
       </c>
       <c r="D57">
-        <v>1016.489862515301</v>
+        <v>1088.180817732855</v>
       </c>
       <c r="E57">
         <v>817.21</v>
@@ -5967,37 +5967,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M57">
-        <v>390.8243932089016</v>
+        <v>365.8417432089016</v>
       </c>
       <c r="N57">
-        <v>-187.0577265422349</v>
+        <v>-162.0750765422349</v>
       </c>
       <c r="O57">
-        <v>-56.11731796267048</v>
+        <v>-48.62252296267047</v>
       </c>
       <c r="P57">
-        <v>-130.9404085795644</v>
+        <v>-113.4525535795644</v>
       </c>
       <c r="Q57">
-        <v>-130.0404085795645</v>
+        <v>-112.5525535795644</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1229464951909763</v>
+        <v>0.1224333306647749</v>
       </c>
       <c r="T57">
-        <v>1.122322149330481</v>
+        <v>1.115108336045982</v>
       </c>
       <c r="U57">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V57">
-        <v>0.1564129595342968</v>
+        <v>0.1670941086815612</v>
       </c>
       <c r="W57">
-        <v>0.1979540160124536</v>
+        <v>0.1829540160124536</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5213765317809891</v>
+        <v>0.5569803622718708</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1660892065250105</v>
+        <v>0.1574582824882199</v>
       </c>
       <c r="C58">
-        <v>-412.8135795228484</v>
+        <v>-341.9352206825663</v>
       </c>
       <c r="D58">
-        <v>1001.778420477152</v>
+        <v>1072.656779317434</v>
       </c>
       <c r="E58">
         <v>847.4920000000002</v>
@@ -6049,37 +6049,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M58">
-        <v>397.9302912672453</v>
+        <v>372.4934112672453</v>
       </c>
       <c r="N58">
-        <v>-194.1636246005786</v>
+        <v>-168.7267446005786</v>
       </c>
       <c r="O58">
-        <v>-58.24908738017358</v>
+        <v>-50.61802338017358</v>
       </c>
       <c r="P58">
-        <v>-135.914537220405</v>
+        <v>-118.108721220405</v>
       </c>
       <c r="Q58">
-        <v>-135.0145372204051</v>
+        <v>-117.208721220405</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1246998246271349</v>
+        <v>0.1241749972707925</v>
       </c>
       <c r="T58">
-        <v>1.147829470906174</v>
+        <v>1.140451707319755</v>
       </c>
       <c r="U58">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V58">
-        <v>0.1536198709711843</v>
+        <v>0.1641102853122476</v>
       </c>
       <c r="W58">
-        <v>0.1986094351590556</v>
+        <v>0.1836094351590556</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5120662365706143</v>
+        <v>0.5470342843741587</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1679777814072322</v>
+        <v>0.1591968573704415</v>
       </c>
       <c r="C59">
-        <v>-457.3872654457052</v>
+        <v>-387.3045558119945</v>
       </c>
       <c r="D59">
-        <v>987.4867345542949</v>
+        <v>1057.569444188005</v>
       </c>
       <c r="E59">
         <v>877.7740000000001</v>
@@ -6131,37 +6131,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M59">
-        <v>405.036189325589</v>
+        <v>379.1450793255889</v>
       </c>
       <c r="N59">
-        <v>-201.2695226589223</v>
+        <v>-175.3784126589223</v>
       </c>
       <c r="O59">
-        <v>-60.38085679767669</v>
+        <v>-52.61352379767668</v>
       </c>
       <c r="P59">
-        <v>-140.8886658612456</v>
+        <v>-122.7648888612456</v>
       </c>
       <c r="Q59">
-        <v>-139.9886658612456</v>
+        <v>-121.8648888612456</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1265347042696263</v>
+        <v>0.1259976716259272</v>
       </c>
       <c r="T59">
-        <v>1.174523179531899</v>
+        <v>1.166973840048121</v>
       </c>
       <c r="U59">
-        <v>0.2346574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V59">
-        <v>0.1509247855155495</v>
+        <v>0.161231157499752</v>
       </c>
       <c r="W59">
-        <v>0.199241857142619</v>
+        <v>0.184241857142619</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5030826183851649</v>
+        <v>0.53743719166584</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1876367536643786</v>
+        <v>0.1609354322526632</v>
       </c>
       <c r="C60">
-        <v>-615.3534534047453</v>
+        <v>-432.2553592697088</v>
       </c>
       <c r="D60">
-        <v>859.8025465952545</v>
+        <v>1042.900640730291</v>
       </c>
       <c r="E60">
         <v>908.0559999999998</v>
@@ -6213,45 +6213,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M60">
-        <v>464.8327673839325</v>
+        <v>385.7967473839325</v>
       </c>
       <c r="N60">
-        <v>-261.0661007172658</v>
+        <v>-182.0300807172659</v>
       </c>
       <c r="O60">
-        <v>-78.31983021517975</v>
+        <v>-54.60902421517976</v>
       </c>
       <c r="P60">
-        <v>-182.7462705020861</v>
+        <v>-127.4210565020861</v>
       </c>
       <c r="Q60">
-        <v>-181.8462705020861</v>
+        <v>-126.5210565020861</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1293388576449145</v>
+        <v>0.1279071399979731</v>
       </c>
       <c r="T60">
-        <v>1.215317818814148</v>
+        <v>1.194758931477838</v>
       </c>
       <c r="U60">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V60">
-        <v>0.1315096617306868</v>
+        <v>0.1584513099566529</v>
       </c>
       <c r="W60">
-        <v>0.2298524714715767</v>
+        <v>0.1848524714715767</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.4383655391022894</v>
+        <v>0.528171033188843</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1898253285466002</v>
+        <v>0.1626740071348848</v>
       </c>
       <c r="C61">
-        <v>-657.836529920482</v>
+        <v>-476.8048082796538</v>
       </c>
       <c r="D61">
-        <v>847.6014700795178</v>
+        <v>1028.633191720346</v>
       </c>
       <c r="E61">
         <v>938.3379999999997</v>
@@ -6295,45 +6295,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M61">
-        <v>472.8471254422761</v>
+        <v>392.4484154422761</v>
       </c>
       <c r="N61">
-        <v>-269.0804587756095</v>
+        <v>-188.6817487756095</v>
       </c>
       <c r="O61">
-        <v>-80.72413763268284</v>
+        <v>-56.60452463268284</v>
       </c>
       <c r="P61">
-        <v>-188.3563211429266</v>
+        <v>-132.0772241429266</v>
       </c>
       <c r="Q61">
-        <v>-187.4563211429267</v>
+        <v>-131.1772241429267</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1313763907582051</v>
+        <v>0.1299097531686554</v>
       </c>
       <c r="T61">
-        <v>1.244959716834005</v>
+        <v>1.2238993932212</v>
       </c>
       <c r="U61">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V61">
-        <v>0.1292806844132176</v>
+        <v>0.1557656945336588</v>
       </c>
       <c r="W61">
-        <v>0.2304423870097223</v>
+        <v>0.1854423870097223</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.4309356147107252</v>
+        <v>0.5192189817788626</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1920139034288219</v>
+        <v>0.1644125820171065</v>
       </c>
       <c r="C62">
-        <v>-699.9781714600385</v>
+        <v>-520.9691527764626</v>
       </c>
       <c r="D62">
-        <v>835.7418285399613</v>
+        <v>1014.750847223537</v>
       </c>
       <c r="E62">
         <v>968.6199999999999</v>
@@ -6377,45 +6377,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M62">
-        <v>480.8614835006198</v>
+        <v>399.1000835006199</v>
       </c>
       <c r="N62">
-        <v>-277.0948168339531</v>
+        <v>-195.3334168339532</v>
       </c>
       <c r="O62">
-        <v>-83.12844505018593</v>
+        <v>-58.60002505018595</v>
       </c>
       <c r="P62">
-        <v>-193.9663717837672</v>
+        <v>-136.7333917837672</v>
       </c>
       <c r="Q62">
-        <v>-193.0663717837672</v>
+        <v>-135.8333917837672</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1335158005271602</v>
+        <v>0.1320124969978717</v>
       </c>
       <c r="T62">
-        <v>1.276083709754855</v>
+        <v>1.25449687805173</v>
       </c>
       <c r="U62">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V62">
-        <v>0.1271260063396639</v>
+        <v>0.1531695996247645</v>
       </c>
       <c r="W62">
-        <v>0.2310126386965964</v>
+        <v>0.1860126386965964</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y62">
-        <v>0.4237533544655465</v>
+        <v>0.5105653320825482</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1942024783110435</v>
+        <v>0.1661511568993282</v>
       </c>
       <c r="C63">
-        <v>-741.7925123328278</v>
+        <v>-564.7637771453053</v>
       </c>
       <c r="D63">
-        <v>824.2094876671721</v>
+        <v>1001.238222854694</v>
       </c>
       <c r="E63">
         <v>998.9019999999998</v>
@@ -6459,45 +6459,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M63">
-        <v>488.8758415589635</v>
+        <v>405.7517515589635</v>
       </c>
       <c r="N63">
-        <v>-285.1091748922968</v>
+        <v>-201.9850848922968</v>
       </c>
       <c r="O63">
-        <v>-85.53275246768904</v>
+        <v>-60.59552546768905</v>
       </c>
       <c r="P63">
-        <v>-199.5764224246078</v>
+        <v>-141.3895594246078</v>
       </c>
       <c r="Q63">
-        <v>-198.6764224246078</v>
+        <v>-140.4895594246078</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1357649236176002</v>
+        <v>0.134223073843971</v>
       </c>
       <c r="T63">
-        <v>1.308803804876775</v>
+        <v>1.286663464668441</v>
       </c>
       <c r="U63">
-        <v>0.2646574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V63">
-        <v>0.1250419734488498</v>
+        <v>0.1506586225817355</v>
       </c>
       <c r="W63">
-        <v>0.2315641936068516</v>
+        <v>0.1865641936068516</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.4168065781628326</v>
+        <v>0.5021954086057852</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1963910531932652</v>
+        <v>0.1900693910070264</v>
       </c>
       <c r="C64">
-        <v>-783.2929173137713</v>
+        <v>-750.0689852140624</v>
       </c>
       <c r="D64">
-        <v>812.9910826862287</v>
+        <v>846.2150147859376</v>
       </c>
       <c r="E64">
         <v>1029.184</v>
@@ -6541,37 +6541,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M64">
-        <v>496.8901996173072</v>
+        <v>478.1153596173071</v>
       </c>
       <c r="N64">
-        <v>-293.1235329506405</v>
+        <v>-274.3486929506405</v>
       </c>
       <c r="O64">
-        <v>-87.93705988519216</v>
+        <v>-82.30460788519214</v>
       </c>
       <c r="P64">
-        <v>-205.1864730654484</v>
+        <v>-192.0440850654484</v>
       </c>
       <c r="Q64">
-        <v>-204.2864730654484</v>
+        <v>-191.1440850654484</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1381324216075371</v>
+        <v>0.1378122579595401</v>
       </c>
       <c r="T64">
-        <v>1.343246010268269</v>
+        <v>1.338890466837807</v>
       </c>
       <c r="U64">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V64">
-        <v>0.1230251674254812</v>
+        <v>0.127856172721432</v>
       </c>
       <c r="W64">
-        <v>0.2320979564232277</v>
+        <v>0.2220979564232277</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4100838914182707</v>
+        <v>0.4261872424047733</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1985796280754869</v>
+        <v>0.1921579658892481</v>
       </c>
       <c r="C65">
-        <v>-824.492033311132</v>
+        <v>-791.6392865498017</v>
       </c>
       <c r="D65">
-        <v>802.0739666888678</v>
+        <v>834.9267134501982</v>
       </c>
       <c r="E65">
         <v>1059.466</v>
@@ -6623,37 +6623,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M65">
-        <v>504.9045576756508</v>
+        <v>485.8268976756508</v>
       </c>
       <c r="N65">
-        <v>-301.1378910089842</v>
+        <v>-282.0602310089841</v>
       </c>
       <c r="O65">
-        <v>-90.34136730269525</v>
+        <v>-84.61806930269525</v>
       </c>
       <c r="P65">
-        <v>-210.796523706289</v>
+        <v>-197.4421617062889</v>
       </c>
       <c r="Q65">
-        <v>-209.896523706289</v>
+        <v>-196.5421617062889</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1406278924617948</v>
+        <v>0.1402990757422304</v>
       </c>
       <c r="T65">
-        <v>1.379549956491736</v>
+        <v>1.375076695671261</v>
       </c>
       <c r="U65">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V65">
-        <v>0.1210723869901561</v>
+        <v>0.1258267096623616</v>
       </c>
       <c r="W65">
-        <v>0.2326147743882902</v>
+        <v>0.2226147743882902</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4035746233005204</v>
+        <v>0.4194223655412055</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2007682029577086</v>
+        <v>0.1942465407714697</v>
       </c>
       <c r="C66">
-        <v>-865.4018369266273</v>
+        <v>-832.9123861263161</v>
       </c>
       <c r="D66">
-        <v>791.4461630733728</v>
+        <v>823.935613873684</v>
       </c>
       <c r="E66">
         <v>1089.748</v>
@@ -6705,37 +6705,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M66">
-        <v>512.9189157339945</v>
+        <v>493.5384357339945</v>
       </c>
       <c r="N66">
-        <v>-309.1522490673278</v>
+        <v>-289.7717690673278</v>
       </c>
       <c r="O66">
-        <v>-92.74567472019835</v>
+        <v>-86.93153072019834</v>
       </c>
       <c r="P66">
-        <v>-216.4065743471295</v>
+        <v>-202.8402383471295</v>
       </c>
       <c r="Q66">
-        <v>-215.5065743471295</v>
+        <v>-201.9402383471295</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1432620005857335</v>
+        <v>0.1429240500684034</v>
       </c>
       <c r="T66">
-        <v>1.417870788616506</v>
+        <v>1.413273270551018</v>
       </c>
       <c r="U66">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V66">
-        <v>0.1191806309434349</v>
+        <v>0.1238606673238873</v>
       </c>
       <c r="W66">
-        <v>0.2331154417919445</v>
+        <v>0.2231154417919445</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3972687698114498</v>
+        <v>0.4128688910796242</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2029567778399302</v>
+        <v>0.1963351156536914</v>
       </c>
       <c r="C67">
-        <v>-906.0336782838451</v>
+        <v>-873.8998686652396</v>
       </c>
       <c r="D67">
-        <v>781.0963217161548</v>
+        <v>813.2301313347602</v>
       </c>
       <c r="E67">
         <v>1120.03</v>
@@ -6787,37 +6787,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M67">
-        <v>520.9332737923381</v>
+        <v>501.2499737923382</v>
       </c>
       <c r="N67">
-        <v>-317.1666071256715</v>
+        <v>-297.4833071256714</v>
       </c>
       <c r="O67">
-        <v>-95.14998213770144</v>
+        <v>-89.24499213770143</v>
       </c>
       <c r="P67">
-        <v>-222.01662498797</v>
+        <v>-208.23831498797</v>
       </c>
       <c r="Q67">
-        <v>-221.1166249879701</v>
+        <v>-207.33831498797</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1460466291738974</v>
+        <v>0.1456990229275007</v>
       </c>
       <c r="T67">
-        <v>1.458381382576978</v>
+        <v>1.453652506852476</v>
       </c>
       <c r="U67">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V67">
-        <v>0.1173470827750744</v>
+        <v>0.1219551185958274</v>
       </c>
       <c r="W67">
-        <v>0.2336007040447172</v>
+        <v>0.2236007040447172</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3911569425835814</v>
+        <v>0.4065170619860916</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2051453527221519</v>
+        <v>0.1984236905359131</v>
       </c>
       <c r="C68">
-        <v>-946.3983214621564</v>
+        <v>-914.6127245247828</v>
       </c>
       <c r="D68">
-        <v>771.0136785378437</v>
+        <v>802.7992754752172</v>
       </c>
       <c r="E68">
         <v>1150.312</v>
@@ -6869,37 +6869,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M68">
-        <v>528.9476318506819</v>
+        <v>508.9615118506819</v>
       </c>
       <c r="N68">
-        <v>-325.1809651840152</v>
+        <v>-305.1948451840152</v>
       </c>
       <c r="O68">
-        <v>-97.55428955520456</v>
+        <v>-91.55845355520457</v>
       </c>
       <c r="P68">
-        <v>-227.6266756288107</v>
+        <v>-213.6363916288107</v>
       </c>
       <c r="Q68">
-        <v>-226.7266756288107</v>
+        <v>-212.7363916288107</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1489950594437179</v>
+        <v>0.1486372294841919</v>
       </c>
       <c r="T68">
-        <v>1.501274952652771</v>
+        <v>1.496406992348137</v>
       </c>
       <c r="U68">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V68">
-        <v>0.1155690966724218</v>
+        <v>0.1201073137686179</v>
       </c>
       <c r="W68">
-        <v>0.2340712613807392</v>
+        <v>0.2240712613807392</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3852303222414057</v>
+        <v>0.4003577125620598</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2073339276043736</v>
+        <v>0.2005122654181347</v>
       </c>
       <c r="C69">
-        <v>-986.505981838922</v>
+        <v>-955.0613873348696</v>
       </c>
       <c r="D69">
-        <v>761.188018161078</v>
+        <v>792.6326126651304</v>
       </c>
       <c r="E69">
         <v>1180.594</v>
@@ -6951,37 +6951,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M69">
-        <v>536.9619899090255</v>
+        <v>516.6730499090255</v>
       </c>
       <c r="N69">
-        <v>-333.1953232423589</v>
+        <v>-312.9063832423589</v>
       </c>
       <c r="O69">
-        <v>-99.95859697270767</v>
+        <v>-93.87191497270766</v>
       </c>
       <c r="P69">
-        <v>-233.2367262696512</v>
+        <v>-219.0344682696512</v>
       </c>
       <c r="Q69">
-        <v>-232.3367262696513</v>
+        <v>-218.1344682696512</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1521221824571639</v>
+        <v>0.1517535091655311</v>
       </c>
       <c r="T69">
-        <v>1.546768133036189</v>
+        <v>1.54175265878293</v>
       </c>
       <c r="U69">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V69">
-        <v>0.1138441847817886</v>
+        <v>0.1183146672944595</v>
       </c>
       <c r="W69">
-        <v>0.2345277722291187</v>
+        <v>0.2245277722291187</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3794806159392953</v>
+        <v>0.3943822243148648</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2095225024865953</v>
+        <v>0.2026008403003564</v>
       </c>
       <c r="C70">
-        <v>-1026.366360612347</v>
+        <v>-995.2557688083677</v>
       </c>
       <c r="D70">
-        <v>751.6096393876534</v>
+        <v>782.7202311916321</v>
       </c>
       <c r="E70">
         <v>1210.876</v>
@@ -7033,37 +7033,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M70">
-        <v>544.9763479673692</v>
+        <v>524.3845879673692</v>
       </c>
       <c r="N70">
-        <v>-341.2096813007025</v>
+        <v>-320.6179213007025</v>
       </c>
       <c r="O70">
-        <v>-102.3629043902108</v>
+        <v>-96.18537639021075</v>
       </c>
       <c r="P70">
-        <v>-238.8467769104918</v>
+        <v>-224.4325449104917</v>
       </c>
       <c r="Q70">
-        <v>-237.9467769104918</v>
+        <v>-223.5325449104918</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1554447506589502</v>
+        <v>0.1550645563269539</v>
       </c>
       <c r="T70">
-        <v>1.59510463719357</v>
+        <v>1.589932429369896</v>
       </c>
       <c r="U70">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V70">
-        <v>0.1121700055938211</v>
+        <v>0.1165747457165998</v>
       </c>
       <c r="W70">
-        <v>0.23497085628784</v>
+        <v>0.22497085628784</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3739000186460704</v>
+        <v>0.3885824857219992</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2117110773688169</v>
+        <v>0.2046894151825781</v>
       </c>
       <c r="C71">
-        <v>-1065.988676750212</v>
+        <v>-1035.20529097256</v>
       </c>
       <c r="D71">
-        <v>742.269323249788</v>
+        <v>773.0527090274405</v>
       </c>
       <c r="E71">
         <v>1241.158</v>
@@ -7115,37 +7115,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M71">
-        <v>552.9907060257128</v>
+        <v>532.0961260257128</v>
       </c>
       <c r="N71">
-        <v>-349.2240393590462</v>
+        <v>-328.3294593590462</v>
       </c>
       <c r="O71">
-        <v>-104.7672118077138</v>
+        <v>-98.49883780771384</v>
       </c>
       <c r="P71">
-        <v>-244.4568275513323</v>
+        <v>-229.8306215513323</v>
       </c>
       <c r="Q71">
-        <v>-243.5568275513323</v>
+        <v>-228.9306215513323</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1589816780995616</v>
+        <v>0.158589219434275</v>
       </c>
       <c r="T71">
-        <v>1.646559625490137</v>
+        <v>1.641220572252796</v>
       </c>
       <c r="U71">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V71">
-        <v>0.1105443533388382</v>
+        <v>0.1148852566482433</v>
       </c>
       <c r="W71">
-        <v>0.2354010973303665</v>
+        <v>0.2254010973303665</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3684811777961273</v>
+        <v>0.3829508554941441</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2138996522510386</v>
+        <v>0.2067779900647998</v>
       </c>
       <c r="C72">
-        <v>-1105.381696585681</v>
+        <v>-1074.918916041171</v>
       </c>
       <c r="D72">
-        <v>733.158303414319</v>
+        <v>763.6210839588294</v>
       </c>
       <c r="E72">
         <v>1271.44</v>
@@ -7197,37 +7197,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M72">
-        <v>561.0050640840566</v>
+        <v>539.8076640840566</v>
       </c>
       <c r="N72">
-        <v>-357.2383974173899</v>
+        <v>-336.0409974173899</v>
       </c>
       <c r="O72">
-        <v>-107.171519225217</v>
+        <v>-100.812299225217</v>
       </c>
       <c r="P72">
-        <v>-250.066878192173</v>
+        <v>-235.2286981921729</v>
       </c>
       <c r="Q72">
-        <v>-249.166878192173</v>
+        <v>-234.328698192173</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1627544007028803</v>
+        <v>0.1623488600820842</v>
       </c>
       <c r="T72">
-        <v>1.701444946339808</v>
+        <v>1.695927924661222</v>
       </c>
       <c r="U72">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V72">
-        <v>0.1089651482911405</v>
+        <v>0.1132440386961255</v>
       </c>
       <c r="W72">
-        <v>0.2358190457716779</v>
+        <v>0.2258190457716779</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3632171609704683</v>
+        <v>0.3774801289870848</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2160882271332603</v>
+        <v>0.2088665649470214</v>
       </c>
       <c r="C73">
-        <v>-1144.553761259876</v>
+        <v>-1114.405174126038</v>
       </c>
       <c r="D73">
-        <v>724.2682387401244</v>
+        <v>754.4168258739616</v>
       </c>
       <c r="E73">
         <v>1301.722</v>
@@ -7279,37 +7279,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M73">
-        <v>569.0194221424001</v>
+        <v>547.5192021424001</v>
       </c>
       <c r="N73">
-        <v>-365.2527554757335</v>
+        <v>-343.7525354757335</v>
       </c>
       <c r="O73">
-        <v>-109.57582664272</v>
+        <v>-103.12576064272</v>
       </c>
       <c r="P73">
-        <v>-255.6769288330134</v>
+        <v>-240.6267748330134</v>
       </c>
       <c r="Q73">
-        <v>-254.7769288330135</v>
+        <v>-239.7267748330135</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1667873110719451</v>
+        <v>0.1663677862918112</v>
       </c>
       <c r="T73">
-        <v>1.760115461730835</v>
+        <v>1.754408197925402</v>
       </c>
       <c r="U73">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V73">
-        <v>0.1074304278926737</v>
+        <v>0.1116490522356167</v>
       </c>
       <c r="W73">
-        <v>0.2362252210174594</v>
+        <v>0.2262252210174594</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3581014263089125</v>
+        <v>0.3721635074520556</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2182768020154819</v>
+        <v>0.2109551398292431</v>
       </c>
       <c r="C74">
-        <v>-1183.512812191813</v>
+        <v>-1153.672188968523</v>
       </c>
       <c r="D74">
-        <v>715.5911878081869</v>
+        <v>745.431811031477</v>
       </c>
       <c r="E74">
         <v>1332.004</v>
@@ -7361,37 +7361,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M74">
-        <v>577.0337802007438</v>
+        <v>555.2307402007438</v>
       </c>
       <c r="N74">
-        <v>-373.2671135340771</v>
+        <v>-351.4640735340771</v>
       </c>
       <c r="O74">
-        <v>-111.9801340602231</v>
+        <v>-105.4392220602231</v>
       </c>
       <c r="P74">
-        <v>-261.286979473854</v>
+        <v>-246.024851473854</v>
       </c>
       <c r="Q74">
-        <v>-260.386979473854</v>
+        <v>-245.124851473854</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1711082864673717</v>
+        <v>0.1706737786593759</v>
       </c>
       <c r="T74">
-        <v>1.822976728221222</v>
+        <v>1.817065633565595</v>
       </c>
       <c r="U74">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V74">
-        <v>0.1059383386163866</v>
+        <v>0.1100983709545665</v>
       </c>
       <c r="W74">
-        <v>0.2366201136175248</v>
+        <v>0.2266201136175248</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3531277953879554</v>
+        <v>0.3669945698485548</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2204653768977036</v>
+        <v>0.2130437147114648</v>
       </c>
       <c r="C75">
-        <v>-1222.266414739166</v>
+        <v>-1192.72770185381</v>
       </c>
       <c r="D75">
-        <v>707.1195852608334</v>
+        <v>736.6582981461897</v>
       </c>
       <c r="E75">
         <v>1362.286</v>
@@ -7443,37 +7443,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M75">
-        <v>585.0481382590874</v>
+        <v>562.9422782590874</v>
       </c>
       <c r="N75">
-        <v>-381.2814715924208</v>
+        <v>-359.1756115924208</v>
       </c>
       <c r="O75">
-        <v>-114.3844414777262</v>
+        <v>-107.7526834777262</v>
       </c>
       <c r="P75">
-        <v>-266.8970301146945</v>
+        <v>-251.4229281146945</v>
       </c>
       <c r="Q75">
-        <v>-265.9970301146946</v>
+        <v>-250.5229281146945</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1757493341143114</v>
+        <v>0.1752987334245379</v>
       </c>
       <c r="T75">
-        <v>1.890494384822008</v>
+        <v>1.884364360734691</v>
       </c>
       <c r="U75">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V75">
-        <v>0.1044871284983539</v>
+        <v>0.1085901740921751</v>
       </c>
       <c r="W75">
-        <v>0.237004187242246</v>
+        <v>0.2270041872422459</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3482904283278464</v>
+        <v>0.3619672469739171</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2226539517799253</v>
+        <v>0.2151322895936865</v>
       </c>
       <c r="C76">
-        <v>-1260.821780198036</v>
+        <v>-1231.579093856077</v>
       </c>
       <c r="D76">
-        <v>698.8462198019639</v>
+        <v>728.0889061439226</v>
       </c>
       <c r="E76">
         <v>1392.568</v>
@@ -7525,37 +7525,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M76">
-        <v>593.0624963174312</v>
+        <v>570.6538163174312</v>
       </c>
       <c r="N76">
-        <v>-389.2958296507645</v>
+        <v>-366.8871496507645</v>
       </c>
       <c r="O76">
-        <v>-116.7887488952293</v>
+        <v>-110.0661448952294</v>
       </c>
       <c r="P76">
-        <v>-272.5070807555352</v>
+        <v>-256.8210047555352</v>
       </c>
       <c r="Q76">
-        <v>-271.6070807555352</v>
+        <v>-255.9210047555352</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1807473854264003</v>
+        <v>0.1802794539408663</v>
       </c>
       <c r="T76">
-        <v>1.963205707315162</v>
+        <v>1.956839913070641</v>
       </c>
       <c r="U76">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V76">
-        <v>0.1030751402754032</v>
+        <v>0.1071227393071457</v>
       </c>
       <c r="W76">
-        <v>0.2373778804987314</v>
+        <v>0.2273778804987314</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3435838009180106</v>
+        <v>0.3570757976904857</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2248425266621469</v>
+        <v>0.2172208644759081</v>
       </c>
       <c r="C77">
-        <v>-1299.185786276169</v>
+        <v>-1270.233406548868</v>
       </c>
       <c r="D77">
-        <v>690.7642137238303</v>
+        <v>719.716593451132</v>
       </c>
       <c r="E77">
         <v>1422.85</v>
@@ -7607,37 +7607,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M77">
-        <v>601.0768543757747</v>
+        <v>578.3653543757747</v>
       </c>
       <c r="N77">
-        <v>-397.310187709108</v>
+        <v>-374.598687709108</v>
       </c>
       <c r="O77">
-        <v>-119.1930563127324</v>
+        <v>-112.3796063127324</v>
       </c>
       <c r="P77">
-        <v>-278.1171313963756</v>
+        <v>-262.2190813963757</v>
       </c>
       <c r="Q77">
-        <v>-277.2171313963756</v>
+        <v>-261.3190813963757</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1861452808434563</v>
+        <v>0.185658632098501</v>
       </c>
       <c r="T77">
-        <v>2.041733935607769</v>
+        <v>2.035113509593466</v>
       </c>
       <c r="U77">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V77">
-        <v>0.1017008050717312</v>
+        <v>0.1056944361163838</v>
       </c>
       <c r="W77">
-        <v>0.2377416086017105</v>
+        <v>0.2277416086017105</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3390026835724371</v>
+        <v>0.3523147870546126</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2270311015443686</v>
+        <v>0.2193094393581298</v>
       </c>
       <c r="C78">
-        <v>-1337.36499616183</v>
+        <v>-1308.697361302821</v>
       </c>
       <c r="D78">
-        <v>682.8670038381696</v>
+        <v>711.5346386971784</v>
       </c>
       <c r="E78">
         <v>1453.132</v>
@@ -7689,37 +7689,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M78">
-        <v>609.0912124341185</v>
+        <v>586.0768924341185</v>
       </c>
       <c r="N78">
-        <v>-405.3245457674518</v>
+        <v>-382.3102257674518</v>
       </c>
       <c r="O78">
-        <v>-121.5973637302355</v>
+        <v>-114.6930677302355</v>
       </c>
       <c r="P78">
-        <v>-283.7271820372163</v>
+        <v>-267.6171580372163</v>
       </c>
       <c r="Q78">
-        <v>-282.8271820372163</v>
+        <v>-266.7171580372163</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1919930008786003</v>
+        <v>0.1914860751026052</v>
       </c>
       <c r="T78">
-        <v>2.12680618292476</v>
+        <v>2.119909905826528</v>
       </c>
       <c r="U78">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V78">
-        <v>0.1003626365839452</v>
+        <v>0.1043037198516945</v>
       </c>
       <c r="W78">
-        <v>0.238095764912506</v>
+        <v>0.228095764912506</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.334542121946484</v>
+        <v>0.347679066172315</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2292196764265903</v>
+        <v>0.2213980142403515</v>
       </c>
       <c r="C79">
-        <v>-1375.365676299403</v>
+        <v>-1346.977377281898</v>
       </c>
       <c r="D79">
-        <v>675.1483237005966</v>
+        <v>703.5366227181023</v>
       </c>
       <c r="E79">
         <v>1483.414</v>
@@ -7771,37 +7771,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M79">
-        <v>617.1055704924621</v>
+        <v>593.7884304924621</v>
       </c>
       <c r="N79">
-        <v>-413.3389038257955</v>
+        <v>-390.0217638257955</v>
       </c>
       <c r="O79">
-        <v>-124.0016711477386</v>
+        <v>-117.0065291477386</v>
       </c>
       <c r="P79">
-        <v>-289.3372326780568</v>
+        <v>-273.0152346780568</v>
       </c>
       <c r="Q79">
-        <v>-288.4372326780568</v>
+        <v>-272.1152346780568</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1983492183081047</v>
+        <v>0.1978202522809793</v>
       </c>
       <c r="T79">
-        <v>2.219276016964966</v>
+        <v>2.212079901732029</v>
       </c>
       <c r="U79">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V79">
-        <v>0.09905922571921866</v>
+        <v>0.1029491260873868</v>
       </c>
       <c r="W79">
-        <v>0.238440722358086</v>
+        <v>0.228440722358086</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3301974190640622</v>
+        <v>0.3431637536246227</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.231408251308812</v>
+        <v>0.2234865891225732</v>
       </c>
       <c r="C80">
-        <v>-1413.193812972932</v>
+        <v>-1385.079588239379</v>
       </c>
       <c r="D80">
-        <v>667.6021870270682</v>
+        <v>695.7164117606212</v>
       </c>
       <c r="E80">
         <v>1513.696</v>
@@ -7853,37 +7853,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M80">
-        <v>625.1199285508059</v>
+        <v>601.4999685508059</v>
       </c>
       <c r="N80">
-        <v>-421.3532618841392</v>
+        <v>-397.7333018841392</v>
       </c>
       <c r="O80">
-        <v>-126.4059785652418</v>
+        <v>-119.3199905652418</v>
       </c>
       <c r="P80">
-        <v>-294.9472833188975</v>
+        <v>-278.4133113188975</v>
       </c>
       <c r="Q80">
-        <v>-294.0472833188975</v>
+        <v>-277.5133113188975</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2052832736857458</v>
+        <v>0.2047302637482966</v>
       </c>
       <c r="T80">
-        <v>2.320152199554283</v>
+        <v>2.312628988174394</v>
       </c>
       <c r="U80">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V80">
-        <v>0.09778923564589533</v>
+        <v>0.1016292654965229</v>
       </c>
       <c r="W80">
-        <v>0.2387768347409588</v>
+        <v>0.2287768347409588</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.325964118819651</v>
+        <v>0.3387642183217429</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2335968261910336</v>
+        <v>0.2255751640047948</v>
       </c>
       <c r="C81">
-        <v>-1450.855127789829</v>
+        <v>-1423.009858205997</v>
       </c>
       <c r="D81">
-        <v>660.222872210171</v>
+        <v>688.0681417940029</v>
       </c>
       <c r="E81">
         <v>1543.978</v>
@@ -7935,37 +7935,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M81">
-        <v>633.1342866091494</v>
+        <v>609.2115066091494</v>
       </c>
       <c r="N81">
-        <v>-429.3676199424827</v>
+        <v>-405.4448399424828</v>
       </c>
       <c r="O81">
-        <v>-128.8102859827448</v>
+        <v>-121.6334519827448</v>
       </c>
       <c r="P81">
-        <v>-300.5573339597379</v>
+        <v>-283.8113879597379</v>
       </c>
       <c r="Q81">
-        <v>-299.6573339597379</v>
+        <v>-282.911387959738</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2128777152898289</v>
+        <v>0.2122983715458345</v>
       </c>
       <c r="T81">
-        <v>2.430635637628296</v>
+        <v>2.422754178087461</v>
       </c>
       <c r="U81">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V81">
-        <v>0.09655139721999793</v>
+        <v>0.1003428190978327</v>
       </c>
       <c r="W81">
-        <v>0.2391044379495817</v>
+        <v>0.2291044379495817</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3218379907333264</v>
+        <v>0.3344760636594424</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2357854010732553</v>
+        <v>0.2276637388870165</v>
       </c>
       <c r="C82">
-        <v>-1488.35509214892</v>
+        <v>-1460.773796154526</v>
       </c>
       <c r="D82">
-        <v>653.0049078510805</v>
+        <v>680.5862038454737</v>
       </c>
       <c r="E82">
         <v>1574.26</v>
@@ -8017,37 +8017,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M82">
-        <v>641.1486446674932</v>
+        <v>616.9230446674932</v>
       </c>
       <c r="N82">
-        <v>-437.3819780008265</v>
+        <v>-413.1563780008265</v>
       </c>
       <c r="O82">
-        <v>-131.2145934002479</v>
+        <v>-123.946913400248</v>
       </c>
       <c r="P82">
-        <v>-306.1673846005785</v>
+        <v>-289.2094646005786</v>
       </c>
       <c r="Q82">
-        <v>-305.2673846005786</v>
+        <v>-288.3094646005786</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2212316010543204</v>
+        <v>0.2206232901231263</v>
       </c>
       <c r="T82">
-        <v>2.552167419509712</v>
+        <v>2.543891886991834</v>
       </c>
       <c r="U82">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V82">
-        <v>0.09534450475474794</v>
+        <v>0.0990885338591098</v>
       </c>
       <c r="W82">
-        <v>0.2394238510779891</v>
+        <v>0.229423851077989</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3178150158491598</v>
+        <v>0.3302951128636993</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.237973975955477</v>
+        <v>0.2297523137692382</v>
       </c>
       <c r="C83">
-        <v>-1525.698940769702</v>
+        <v>-1498.376769717899</v>
       </c>
       <c r="D83">
-        <v>645.9430592302979</v>
+        <v>673.2652302821014</v>
       </c>
       <c r="E83">
         <v>1604.542</v>
@@ -8099,37 +8099,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M83">
-        <v>649.1630027258368</v>
+        <v>624.6345827258368</v>
       </c>
       <c r="N83">
-        <v>-445.3963360591702</v>
+        <v>-420.8679160591702</v>
       </c>
       <c r="O83">
-        <v>-133.618900817751</v>
+        <v>-126.260374817751</v>
       </c>
       <c r="P83">
-        <v>-311.7774352414191</v>
+        <v>-294.6075412414191</v>
       </c>
       <c r="Q83">
-        <v>-310.8774352414191</v>
+        <v>-293.7075412414192</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2304648432150741</v>
+        <v>0.2298245159190803</v>
       </c>
       <c r="T83">
-        <v>2.686492020536539</v>
+        <v>2.677780933675615</v>
       </c>
       <c r="U83">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V83">
-        <v>0.09416741210345476</v>
+        <v>0.09786521862628129</v>
       </c>
       <c r="W83">
-        <v>0.2397353774624851</v>
+        <v>0.2297353774624851</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3138913736781825</v>
+        <v>0.3262173954209375</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2401625508376987</v>
+        <v>0.2318408886514598</v>
       </c>
       <c r="C84">
-        <v>-1562.891684353141</v>
+        <v>-1535.823918031366</v>
       </c>
       <c r="D84">
-        <v>639.0323156468589</v>
+        <v>666.1000819686337</v>
       </c>
       <c r="E84">
         <v>1634.824</v>
@@ -8181,37 +8181,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M84">
-        <v>657.1773607841806</v>
+        <v>632.3461207841806</v>
       </c>
       <c r="N84">
-        <v>-453.4106941175139</v>
+        <v>-428.5794541175139</v>
       </c>
       <c r="O84">
-        <v>-136.0232082352542</v>
+        <v>-128.5738362352542</v>
       </c>
       <c r="P84">
-        <v>-317.3874858822597</v>
+        <v>-300.0056178822598</v>
       </c>
       <c r="Q84">
-        <v>-316.4874858822598</v>
+        <v>-299.1056178822598</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2407240011714672</v>
+        <v>0.240048100136807</v>
       </c>
       <c r="T84">
-        <v>2.835741577233013</v>
+        <v>2.826546541102038</v>
       </c>
       <c r="U84">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V84">
-        <v>0.09301902902902237</v>
+        <v>0.096671740350351</v>
       </c>
       <c r="W84">
-        <v>0.2400393056424812</v>
+        <v>0.2300393056424812</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3100634300967412</v>
+        <v>0.32223913450117</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2423511257199203</v>
+        <v>0.2339294635336815</v>
       </c>
       <c r="C85">
-        <v>-1599.938121438341</v>
+        <v>-1573.120163763265</v>
       </c>
       <c r="D85">
-        <v>632.2678785616587</v>
+        <v>659.0858362367348</v>
       </c>
       <c r="E85">
         <v>1665.106</v>
@@ -8263,37 +8263,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M85">
-        <v>665.1917188425241</v>
+        <v>640.0576588425241</v>
       </c>
       <c r="N85">
-        <v>-461.4250521758574</v>
+        <v>-436.2909921758575</v>
       </c>
       <c r="O85">
-        <v>-138.4275156527572</v>
+        <v>-130.8872976527572</v>
       </c>
       <c r="P85">
-        <v>-322.9975365231002</v>
+        <v>-305.4036945231002</v>
       </c>
       <c r="Q85">
-        <v>-322.0975365231002</v>
+        <v>-304.5036945231003</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2521901188874358</v>
+        <v>0.2514744589683838</v>
       </c>
       <c r="T85">
-        <v>3.002549905305544</v>
+        <v>2.992813984696276</v>
       </c>
       <c r="U85">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V85">
-        <v>0.09189831783590163</v>
+        <v>0.09550702058709377</v>
       </c>
       <c r="W85">
-        <v>0.240335910251875</v>
+        <v>0.230335910251875</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3063277261196721</v>
+        <v>0.3183567352903126</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.244539700602142</v>
+        <v>0.2360180384159031</v>
       </c>
       <c r="C86">
-        <v>-1636.842849514053</v>
+        <v>-1610.270224393576</v>
       </c>
       <c r="D86">
-        <v>625.6451504859463</v>
+        <v>652.2177756064242</v>
       </c>
       <c r="E86">
         <v>1695.388</v>
@@ -8345,37 +8345,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M86">
-        <v>673.2060769008677</v>
+        <v>647.7691969008677</v>
       </c>
       <c r="N86">
-        <v>-469.4394102342011</v>
+        <v>-444.002530234201</v>
       </c>
       <c r="O86">
-        <v>-140.8318230702603</v>
+        <v>-133.2007590702603</v>
       </c>
       <c r="P86">
-        <v>-328.6075871639408</v>
+        <v>-310.8017711639407</v>
       </c>
       <c r="Q86">
-        <v>-327.7075871639408</v>
+        <v>-309.9017711639407</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2650895013179004</v>
+        <v>0.2643291126539077</v>
       </c>
       <c r="T86">
-        <v>3.190209274387139</v>
+        <v>3.179864858739791</v>
       </c>
       <c r="U86">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V86">
-        <v>0.0908042902426171</v>
+        <v>0.09437003224677126</v>
       </c>
       <c r="W86">
-        <v>0.2406254528467594</v>
+        <v>0.2306254528467594</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3026809674753903</v>
+        <v>0.3145667741559042</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2467282754843637</v>
+        <v>0.2381066132981249</v>
       </c>
       <c r="C87">
-        <v>-1673.610275439104</v>
+        <v>-1647.278622794584</v>
       </c>
       <c r="D87">
-        <v>619.1597245608958</v>
+        <v>645.4913772054157</v>
       </c>
       <c r="E87">
         <v>1725.67</v>
@@ -8427,37 +8427,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M87">
-        <v>681.2204349592114</v>
+        <v>655.4807349592114</v>
       </c>
       <c r="N87">
-        <v>-477.4537682925447</v>
+        <v>-451.7140682925448</v>
       </c>
       <c r="O87">
-        <v>-143.2361304877634</v>
+        <v>-135.5142204877634</v>
       </c>
       <c r="P87">
-        <v>-334.2176378047814</v>
+        <v>-316.1998478047814</v>
       </c>
       <c r="Q87">
-        <v>-333.3176378047814</v>
+        <v>-315.2998478047814</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2797088014057604</v>
+        <v>0.2788977201641683</v>
       </c>
       <c r="T87">
-        <v>3.402889892679614</v>
+        <v>3.391855849322444</v>
       </c>
       <c r="U87">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V87">
-        <v>0.0897360044750569</v>
+        <v>0.09325979657327982</v>
       </c>
       <c r="W87">
-        <v>0.2409081826747054</v>
+        <v>0.2309081826747054</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2991200149168564</v>
+        <v>0.3108659885775994</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2489168503665853</v>
+        <v>0.2401951881803465</v>
       </c>
       <c r="C88">
-        <v>-1710.244625221348</v>
+        <v>-1684.1496971635</v>
       </c>
       <c r="D88">
-        <v>612.8073747786518</v>
+        <v>638.9023028365</v>
       </c>
       <c r="E88">
         <v>1755.952</v>
@@ -8509,37 +8509,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M88">
-        <v>689.2347930175551</v>
+        <v>663.1922730175551</v>
       </c>
       <c r="N88">
-        <v>-485.4681263508885</v>
+        <v>-459.4256063508884</v>
       </c>
       <c r="O88">
-        <v>-145.6404379052665</v>
+        <v>-137.8276819052665</v>
       </c>
       <c r="P88">
-        <v>-339.827688445622</v>
+        <v>-321.5979244456219</v>
       </c>
       <c r="Q88">
-        <v>-338.927688445622</v>
+        <v>-320.6979244456219</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2964165729347434</v>
+        <v>0.2955475573187517</v>
       </c>
       <c r="T88">
-        <v>3.645953456442444</v>
+        <v>3.63413126713119</v>
       </c>
       <c r="U88">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V88">
-        <v>0.08869256256255623</v>
+        <v>0.09217538033405563</v>
       </c>
       <c r="W88">
-        <v>0.2411843373903736</v>
+        <v>0.2311843373903736</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2956418752085207</v>
+        <v>0.3072512677801854</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.251105425248807</v>
+        <v>0.2422837630625682</v>
       </c>
       <c r="C89">
-        <v>-1746.749953200781</v>
+        <v>-1720.887610352889</v>
       </c>
       <c r="D89">
-        <v>606.5840467992191</v>
+        <v>632.4463896471107</v>
       </c>
       <c r="E89">
         <v>1786.234</v>
@@ -8591,37 +8591,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M89">
-        <v>697.2491510758987</v>
+        <v>670.9038110758987</v>
       </c>
       <c r="N89">
-        <v>-493.482484409232</v>
+        <v>-467.1371444092321</v>
       </c>
       <c r="O89">
-        <v>-148.0447453227696</v>
+        <v>-140.1411433227696</v>
       </c>
       <c r="P89">
-        <v>-345.4377390864624</v>
+        <v>-326.9960010864625</v>
       </c>
       <c r="Q89">
-        <v>-344.5377390864625</v>
+        <v>-326.0960010864625</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3156947708528006</v>
+        <v>0.3147589078817326</v>
       </c>
       <c r="T89">
-        <v>3.926411414630325</v>
+        <v>3.913679826141282</v>
       </c>
       <c r="U89">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V89">
-        <v>0.0876731078204579</v>
+        <v>0.09111589320377915</v>
       </c>
       <c r="W89">
-        <v>0.2414541437217735</v>
+        <v>0.2314541437217735</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2922436927348596</v>
+        <v>0.3037196440125971</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2532940001310287</v>
+        <v>0.2443723379447899</v>
       </c>
       <c r="C90">
-        <v>-1783.130150678715</v>
+        <v>-1757.496358641068</v>
       </c>
       <c r="D90">
-        <v>600.4858493212852</v>
+        <v>626.1196413589316</v>
       </c>
       <c r="E90">
         <v>1816.516</v>
@@ -8673,37 +8673,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M90">
-        <v>705.2635091342424</v>
+        <v>678.6153491342424</v>
       </c>
       <c r="N90">
-        <v>-501.4968424675758</v>
+        <v>-474.8486824675757</v>
       </c>
       <c r="O90">
-        <v>-150.4490527402727</v>
+        <v>-142.4546047402727</v>
       </c>
       <c r="P90">
-        <v>-351.0477897273031</v>
+        <v>-332.394077727303</v>
       </c>
       <c r="Q90">
-        <v>-350.1477897273031</v>
+        <v>-331.494077727303</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3381860017572006</v>
+        <v>0.3371721502052104</v>
       </c>
       <c r="T90">
-        <v>4.253612365849519</v>
+        <v>4.239819811653056</v>
       </c>
       <c r="U90">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V90">
-        <v>0.08667682250431633</v>
+        <v>0.09008048532646347</v>
       </c>
       <c r="W90">
-        <v>0.2417178180910962</v>
+        <v>0.2317178180910961</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2889227416810544</v>
+        <v>0.3002682844215449</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2554825750132504</v>
+        <v>0.2464609128270115</v>
       </c>
       <c r="C91">
-        <v>-1819.388954031628</v>
+        <v>-1793.979779981307</v>
       </c>
       <c r="D91">
-        <v>594.5090459683719</v>
+        <v>619.9182200186926</v>
       </c>
       <c r="E91">
         <v>1846.798</v>
@@ -8755,37 +8755,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M91">
-        <v>713.2778671925861</v>
+        <v>686.3268871925861</v>
       </c>
       <c r="N91">
-        <v>-509.5112005259194</v>
+        <v>-482.5602205259195</v>
       </c>
       <c r="O91">
-        <v>-152.8533601577758</v>
+        <v>-144.7680661577758</v>
       </c>
       <c r="P91">
-        <v>-356.6578403681436</v>
+        <v>-337.7921543681437</v>
       </c>
       <c r="Q91">
-        <v>-355.7578403681437</v>
+        <v>-336.8921543681437</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3647665473714917</v>
+        <v>0.3636605274965932</v>
       </c>
       <c r="T91">
-        <v>4.640304399108567</v>
+        <v>4.625257976348789</v>
       </c>
       <c r="U91">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V91">
-        <v>0.08570292562224535</v>
+        <v>0.08906834504189645</v>
       </c>
       <c r="W91">
-        <v>0.2419755671936925</v>
+        <v>0.2319755671936924</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2856764187408178</v>
+        <v>0.2968944834729881</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.257671149895472</v>
+        <v>0.2485494877092332</v>
       </c>
       <c r="C92">
-        <v>-1855.529952345231</v>
+        <v>-1830.341561765606</v>
       </c>
       <c r="D92">
-        <v>588.6500476547693</v>
+        <v>613.8384382343944</v>
       </c>
       <c r="E92">
         <v>1877.08</v>
@@ -8837,37 +8837,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M92">
-        <v>721.2922252509298</v>
+        <v>694.0384252509298</v>
       </c>
       <c r="N92">
-        <v>-517.5255585842632</v>
+        <v>-490.2717585842631</v>
       </c>
       <c r="O92">
-        <v>-155.257667575279</v>
+        <v>-147.0815275752789</v>
       </c>
       <c r="P92">
-        <v>-362.2678910089842</v>
+        <v>-343.1902310089842</v>
       </c>
       <c r="Q92">
-        <v>-361.3678910089843</v>
+        <v>-342.2902310089842</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3966632021086408</v>
+        <v>0.3954465802462526</v>
       </c>
       <c r="T92">
-        <v>5.104334839019423</v>
+        <v>5.087783773983668</v>
       </c>
       <c r="U92">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V92">
-        <v>0.08475067089310927</v>
+        <v>0.08807869676365315</v>
       </c>
       <c r="W92">
-        <v>0.2422275885384533</v>
+        <v>0.2322275885384533</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2825022363103642</v>
+        <v>0.2935956558788438</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2598597247776938</v>
+        <v>0.2506380625914549</v>
       </c>
       <c r="C93">
-        <v>-1891.556594601526</v>
+        <v>-1866.585248136058</v>
       </c>
       <c r="D93">
-        <v>582.9054053984743</v>
+        <v>607.8767518639418</v>
       </c>
       <c r="E93">
         <v>1907.362</v>
@@ -8919,37 +8919,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M93">
-        <v>729.3065833092734</v>
+        <v>701.7499633092734</v>
       </c>
       <c r="N93">
-        <v>-525.5399166426067</v>
+        <v>-497.9832966426068</v>
       </c>
       <c r="O93">
-        <v>-157.661974992782</v>
+        <v>-149.394988992782</v>
       </c>
       <c r="P93">
-        <v>-367.8779416498247</v>
+        <v>-348.5883076498247</v>
       </c>
       <c r="Q93">
-        <v>-366.9779416498247</v>
+        <v>-347.6883076498248</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4356480023429343</v>
+        <v>0.4342962002736139</v>
       </c>
       <c r="T93">
-        <v>5.671483154466027</v>
+        <v>5.653093082204076</v>
       </c>
       <c r="U93">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V93">
-        <v>0.08381934483933887</v>
+        <v>0.08711079899701961</v>
       </c>
       <c r="W93">
-        <v>0.24247407095256</v>
+        <v>0.23247407095256</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2793978161311295</v>
+        <v>0.2903693299900654</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2620482996599154</v>
+        <v>0.2527266374736765</v>
       </c>
       <c r="C94">
-        <v>-1927.472196449105</v>
+        <v>-1902.714246874261</v>
       </c>
       <c r="D94">
-        <v>577.2718035508944</v>
+        <v>602.0297531257391</v>
       </c>
       <c r="E94">
         <v>1937.644</v>
@@ -9001,37 +9001,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M94">
-        <v>737.3209413676171</v>
+        <v>709.4615013676171</v>
       </c>
       <c r="N94">
-        <v>-533.5542747009505</v>
+        <v>-505.6948347009504</v>
       </c>
       <c r="O94">
-        <v>-160.0662824102851</v>
+        <v>-151.7084504102851</v>
       </c>
       <c r="P94">
-        <v>-373.4879922906654</v>
+        <v>-353.9863842906653</v>
       </c>
       <c r="Q94">
-        <v>-372.5879922906654</v>
+        <v>-353.0863842906654</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4843790026358012</v>
+        <v>0.4828582253078158</v>
       </c>
       <c r="T94">
-        <v>6.380418548774282</v>
+        <v>6.359729717479587</v>
       </c>
       <c r="U94">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V94">
-        <v>0.08290826500412865</v>
+        <v>0.08616394248618243</v>
       </c>
       <c r="W94">
-        <v>0.2427151950533166</v>
+        <v>0.2327151950533166</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2763608833470954</v>
+        <v>0.2872131416206081</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2642368745421371</v>
+        <v>0.2548152123558982</v>
       </c>
       <c r="C95">
-        <v>-1963.279946584611</v>
+        <v>-1938.7318358969</v>
       </c>
       <c r="D95">
-        <v>571.7460534153888</v>
+        <v>596.2941641030998</v>
       </c>
       <c r="E95">
         <v>1967.926</v>
@@ -9083,37 +9083,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M95">
-        <v>745.3352994259608</v>
+        <v>717.1730394259608</v>
       </c>
       <c r="N95">
-        <v>-541.5686327592941</v>
+        <v>-513.4063727592942</v>
       </c>
       <c r="O95">
-        <v>-162.4705898277882</v>
+        <v>-154.0219118277882</v>
       </c>
       <c r="P95">
-        <v>-379.0980429315059</v>
+        <v>-359.3844609315059</v>
       </c>
       <c r="Q95">
-        <v>-378.1980429315059</v>
+        <v>-358.484460931506</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.547033145869487</v>
+        <v>0.5452951146375038</v>
       </c>
       <c r="T95">
-        <v>7.291906912884894</v>
+        <v>7.268262534262386</v>
       </c>
       <c r="U95">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V95">
-        <v>0.08201677828365415</v>
+        <v>0.08523744848095466</v>
       </c>
       <c r="W95">
-        <v>0.2429511336895408</v>
+        <v>0.2329511336895408</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2733892609455137</v>
+        <v>0.2841248282698489</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2664254494243587</v>
+        <v>0.2569037872381199</v>
       </c>
       <c r="C96">
-        <v>-1998.982912771155</v>
+        <v>-1974.641169383545</v>
       </c>
       <c r="D96">
-        <v>566.3250872288444</v>
+        <v>590.6668306164549</v>
       </c>
       <c r="E96">
         <v>1998.208</v>
@@ -9165,37 +9165,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M96">
-        <v>753.3496574843044</v>
+        <v>724.8845774843044</v>
       </c>
       <c r="N96">
-        <v>-549.5829908176378</v>
+        <v>-521.1179108176377</v>
       </c>
       <c r="O96">
-        <v>-164.8748972452913</v>
+        <v>-156.3353732452913</v>
       </c>
       <c r="P96">
-        <v>-384.7080935723465</v>
+        <v>-364.7825375723464</v>
       </c>
       <c r="Q96">
-        <v>-383.8080935723465</v>
+        <v>-363.8825375723465</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6305720035144017</v>
+        <v>0.6285443004104213</v>
       </c>
       <c r="T96">
-        <v>8.507224731699045</v>
+        <v>8.47963962330612</v>
       </c>
       <c r="U96">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V96">
-        <v>0.08114425936574293</v>
+        <v>0.084330667114136</v>
       </c>
       <c r="W96">
-        <v>0.2431820523547815</v>
+        <v>0.2331820523547815</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2704808645524764</v>
+        <v>0.2811022237137867</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2686140243065804</v>
+        <v>0.2589923621203416</v>
       </c>
       <c r="C97">
-        <v>-2034.584047517588</v>
+        <v>-2010.445283560706</v>
       </c>
       <c r="D97">
-        <v>561.005952482412</v>
+        <v>585.1447164392938</v>
       </c>
       <c r="E97">
         <v>2028.49</v>
@@ -9247,37 +9247,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M97">
-        <v>761.3640155426481</v>
+        <v>732.5961155426481</v>
       </c>
       <c r="N97">
-        <v>-557.5973488759814</v>
+        <v>-528.8294488759815</v>
       </c>
       <c r="O97">
-        <v>-167.2792046627944</v>
+        <v>-158.6488346627944</v>
       </c>
       <c r="P97">
-        <v>-390.318144213187</v>
+        <v>-370.180614213187</v>
       </c>
       <c r="Q97">
-        <v>-389.418144213187</v>
+        <v>-369.2806142131871</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7475264042172824</v>
+        <v>0.745093160492506</v>
       </c>
       <c r="T97">
-        <v>10.20866967803886</v>
+        <v>10.17556754796735</v>
       </c>
       <c r="U97">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V97">
-        <v>0.08029010926715617</v>
+        <v>0.08344297588135562</v>
       </c>
       <c r="W97">
-        <v>0.2434081095744382</v>
+        <v>0.2334081095744382</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2676336975571872</v>
+        <v>0.278143252937852</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2708025991888021</v>
+        <v>0.2610809370025632</v>
       </c>
       <c r="C98">
-        <v>-2070.086193440682</v>
+        <v>-2046.147102164452</v>
       </c>
       <c r="D98">
-        <v>555.7858065593177</v>
+        <v>579.7248978355477</v>
       </c>
       <c r="E98">
         <v>2058.772</v>
@@ -9329,37 +9329,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M98">
-        <v>769.3783736009917</v>
+        <v>740.3076536009917</v>
       </c>
       <c r="N98">
-        <v>-565.6117069343251</v>
+        <v>-536.540986934325</v>
       </c>
       <c r="O98">
-        <v>-169.6835120802975</v>
+        <v>-160.9622960802975</v>
       </c>
       <c r="P98">
-        <v>-395.9281948540275</v>
+        <v>-375.5786908540275</v>
       </c>
       <c r="Q98">
-        <v>-395.0281948540276</v>
+        <v>-374.6786908540275</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.922958005271601</v>
+        <v>0.9199164506156303</v>
       </c>
       <c r="T98">
-        <v>12.76083709754854</v>
+        <v>12.71945943495916</v>
       </c>
       <c r="U98">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V98">
-        <v>0.07945375396228996</v>
+        <v>0.08257377821592485</v>
       </c>
       <c r="W98">
-        <v>0.2436294572686854</v>
+        <v>0.2336294572686854</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2648458465409665</v>
+        <v>0.2752459273864161</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2729911740710237</v>
+        <v>0.2631695118847849</v>
       </c>
       <c r="C99">
-        <v>-2105.492088330717</v>
+        <v>-2081.749441602233</v>
       </c>
       <c r="D99">
-        <v>550.661911669283</v>
+        <v>574.4045583977671</v>
       </c>
       <c r="E99">
         <v>2089.054</v>
@@ -9411,37 +9411,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M99">
-        <v>777.3927316593354</v>
+        <v>748.0191916593354</v>
       </c>
       <c r="N99">
-        <v>-573.6260649926687</v>
+        <v>-544.2525249926688</v>
       </c>
       <c r="O99">
-        <v>-172.0878194978006</v>
+        <v>-163.2757574978006</v>
       </c>
       <c r="P99">
-        <v>-401.5382454948681</v>
+        <v>-380.9767674948681</v>
       </c>
       <c r="Q99">
-        <v>-400.6382454948681</v>
+        <v>-380.0767674948681</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.215344007028802</v>
+        <v>1.211288600820841</v>
       </c>
       <c r="T99">
-        <v>17.01444946339806</v>
+        <v>16.95927924661221</v>
       </c>
       <c r="U99">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V99">
-        <v>0.07863464309669935</v>
+        <v>0.08172250215184312</v>
       </c>
       <c r="W99">
-        <v>0.2438462410929481</v>
+        <v>0.2338462410929481</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2621154769889978</v>
+        <v>0.2724083405061437</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2751797489532454</v>
+        <v>0.2652580867670066</v>
       </c>
       <c r="C100">
-        <v>-2140.804369939411</v>
+        <v>-2117.255015833052</v>
       </c>
       <c r="D100">
-        <v>545.6316300605888</v>
+        <v>569.1809841669481</v>
       </c>
       <c r="E100">
         <v>2119.336</v>
@@ -9493,37 +9493,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M100">
-        <v>785.4070897176791</v>
+        <v>755.7307297176791</v>
       </c>
       <c r="N100">
-        <v>-581.6404230510125</v>
+        <v>-551.9640630510124</v>
       </c>
       <c r="O100">
-        <v>-174.4921269153037</v>
+        <v>-165.5892189153037</v>
       </c>
       <c r="P100">
-        <v>-407.1482961357087</v>
+        <v>-386.3748441357087</v>
       </c>
       <c r="Q100">
-        <v>-406.2482961357088</v>
+        <v>-385.4748441357087</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.800116010543202</v>
+        <v>1.794032901231261</v>
       </c>
       <c r="T100">
-        <v>25.52167419509709</v>
+        <v>25.43891886991831</v>
       </c>
       <c r="U100">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V100">
-        <v>0.07783224877938608</v>
+        <v>0.08088859906866107</v>
       </c>
       <c r="W100">
-        <v>0.244058600757532</v>
+        <v>0.234058600757532</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2594408292646202</v>
+        <v>0.2696286635622035</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2773683238354671</v>
+        <v>0.2673466616492282</v>
       </c>
       <c r="C101">
-        <v>-2176.02558050781</v>
+        <v>-2152.666440983766</v>
       </c>
       <c r="D101">
-        <v>540.6924194921892</v>
+        <v>564.0515590162335</v>
       </c>
       <c r="E101">
         <v>2149.617999999999</v>
@@ -9575,37 +9575,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M101">
-        <v>793.4214477760227</v>
+        <v>763.4422677760227</v>
       </c>
       <c r="N101">
-        <v>-589.654781109356</v>
+        <v>-559.6756011093561</v>
       </c>
       <c r="O101">
-        <v>-176.8964343328068</v>
+        <v>-167.9026803328068</v>
       </c>
       <c r="P101">
-        <v>-412.7583467765492</v>
+        <v>-391.7729207765493</v>
       </c>
       <c r="Q101">
-        <v>-411.8583467765492</v>
+        <v>-390.8729207765493</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.554432021086404</v>
+        <v>3.542265802462521</v>
       </c>
       <c r="T101">
-        <v>51.04334839019418</v>
+        <v>50.87783773983662</v>
       </c>
       <c r="U101">
-        <v>0.2646574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V101">
-        <v>0.07704606444828117</v>
+        <v>0.08007154251241196</v>
       </c>
       <c r="W101">
-        <v>0.2442666703278818</v>
+        <v>0.2342666703278818</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2568202148276039</v>
+        <v>0.2669051417080398</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/mexico/mexico_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_real_estate_operations_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08377496490093292</v>
+        <v>0.08368714242378529</v>
       </c>
       <c r="C2">
-        <v>2994.147261739984</v>
+        <v>2968.818966535154</v>
       </c>
       <c r="D2">
-        <v>2712.947261739984</v>
+        <v>2717.900966535154</v>
       </c>
       <c r="E2">
-        <v>-848.3</v>
+        <v>-818.0179999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30.282</v>
       </c>
       <c r="G2">
         <v>281.2</v>
@@ -1457,28 +1457,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.094227058343665</v>
       </c>
       <c r="N2">
-        <v>203.7666666666667</v>
+        <v>201.672439608323</v>
       </c>
       <c r="O2">
-        <v>61.13</v>
+        <v>60.5017318824969</v>
       </c>
       <c r="P2">
-        <v>142.6366666666667</v>
+        <v>141.1707077258261</v>
       </c>
       <c r="Q2">
-        <v>143.5366666666667</v>
+        <v>142.0707077258261</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08377496490093292</v>
+        <v>0.08404347475376781</v>
       </c>
       <c r="T2">
-        <v>0.5525820103960151</v>
+        <v>0.5564891559240677</v>
       </c>
       <c r="U2">
         <v>0.06915748822216712</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>97.299223527284</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08368714242378529</v>
+        <v>0.08359931994663766</v>
       </c>
       <c r="C3">
-        <v>2968.818966535154</v>
+        <v>2943.508794852912</v>
       </c>
       <c r="D3">
-        <v>2717.900966535154</v>
+        <v>2722.872794852912</v>
       </c>
       <c r="E3">
-        <v>-818.0179999999999</v>
+        <v>-787.736</v>
       </c>
       <c r="F3">
-        <v>30.282</v>
+        <v>60.564</v>
       </c>
       <c r="G3">
         <v>281.2</v>
@@ -1539,28 +1539,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M3">
-        <v>2.094227058343665</v>
+        <v>4.188454116687329</v>
       </c>
       <c r="N3">
-        <v>201.672439608323</v>
+        <v>199.5782125499794</v>
       </c>
       <c r="O3">
-        <v>60.5017318824969</v>
+        <v>59.8734637649938</v>
       </c>
       <c r="P3">
-        <v>141.1707077258261</v>
+        <v>139.7047487849856</v>
       </c>
       <c r="Q3">
-        <v>142.0707077258261</v>
+        <v>140.6047487849855</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08404347475376781</v>
+        <v>0.08431746439951768</v>
       </c>
       <c r="T3">
-        <v>0.5564891559240677</v>
+        <v>0.5604760391159581</v>
       </c>
       <c r="U3">
         <v>0.06915748822216712</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>97.299223527284</v>
+        <v>48.64961176364201</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08359931994663766</v>
+        <v>0.08351149746949005</v>
       </c>
       <c r="C4">
-        <v>2943.508794852912</v>
+        <v>2918.21684633505</v>
       </c>
       <c r="D4">
-        <v>2722.872794852912</v>
+        <v>2727.86284633505</v>
       </c>
       <c r="E4">
-        <v>-787.736</v>
+        <v>-757.454</v>
       </c>
       <c r="F4">
-        <v>60.564</v>
+        <v>90.84599999999999</v>
       </c>
       <c r="G4">
         <v>281.2</v>
@@ -1621,28 +1621,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M4">
-        <v>4.188454116687329</v>
+        <v>6.282681175030993</v>
       </c>
       <c r="N4">
-        <v>199.5782125499794</v>
+        <v>197.4839854916357</v>
       </c>
       <c r="O4">
-        <v>59.8734637649938</v>
+        <v>59.2451956474907</v>
       </c>
       <c r="P4">
-        <v>139.7047487849856</v>
+        <v>138.238789844145</v>
       </c>
       <c r="Q4">
-        <v>140.6047487849855</v>
+        <v>139.138789844145</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08431746439951768</v>
+        <v>0.08459710331631395</v>
       </c>
       <c r="T4">
-        <v>0.5604760391159581</v>
+        <v>0.564545126085001</v>
       </c>
       <c r="U4">
         <v>0.06915748822216712</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>48.64961176364201</v>
+        <v>32.43307450909467</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08351149746949005</v>
+        <v>0.08342367499234241</v>
       </c>
       <c r="C5">
-        <v>2918.21684633505</v>
+        <v>2892.943221355139</v>
       </c>
       <c r="D5">
-        <v>2727.86284633505</v>
+        <v>2732.871221355139</v>
       </c>
       <c r="E5">
-        <v>-757.454</v>
+        <v>-727.1719999999999</v>
       </c>
       <c r="F5">
-        <v>90.84599999999999</v>
+        <v>121.128</v>
       </c>
       <c r="G5">
         <v>281.2</v>
@@ -1703,28 +1703,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M5">
-        <v>6.282681175030993</v>
+        <v>8.376908233374659</v>
       </c>
       <c r="N5">
-        <v>197.4839854916357</v>
+        <v>195.389758433292</v>
       </c>
       <c r="O5">
-        <v>59.2451956474907</v>
+        <v>58.61692752998761</v>
       </c>
       <c r="P5">
-        <v>138.238789844145</v>
+        <v>136.7728309033044</v>
       </c>
       <c r="Q5">
-        <v>139.138789844145</v>
+        <v>137.6728309033044</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08459710331631395</v>
+        <v>0.0848825680438768</v>
       </c>
       <c r="T5">
-        <v>0.564545126085001</v>
+        <v>0.5686989856992322</v>
       </c>
       <c r="U5">
         <v>0.06915748822216712</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>32.43307450909467</v>
+        <v>24.324805881821</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08342367499234241</v>
+        <v>0.08333585251519479</v>
       </c>
       <c r="C6">
-        <v>2892.943221355139</v>
+        <v>2867.688021025244</v>
       </c>
       <c r="D6">
-        <v>2732.871221355139</v>
+        <v>2737.898021025244</v>
       </c>
       <c r="E6">
-        <v>-727.1719999999999</v>
+        <v>-696.89</v>
       </c>
       <c r="F6">
-        <v>121.128</v>
+        <v>151.41</v>
       </c>
       <c r="G6">
         <v>281.2</v>
@@ -1785,28 +1785,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M6">
-        <v>8.376908233374659</v>
+        <v>10.47113529171832</v>
       </c>
       <c r="N6">
-        <v>195.389758433292</v>
+        <v>193.2955313749484</v>
       </c>
       <c r="O6">
-        <v>58.61692752998761</v>
+        <v>57.9886594124845</v>
       </c>
       <c r="P6">
-        <v>136.7728309033044</v>
+        <v>135.3068719624638</v>
       </c>
       <c r="Q6">
-        <v>137.6728309033044</v>
+        <v>136.2068719624638</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0848825680438768</v>
+        <v>0.08517404255517783</v>
       </c>
       <c r="T6">
-        <v>0.5686989856992322</v>
+        <v>0.5729402949895525</v>
       </c>
       <c r="U6">
         <v>0.06915748822216712</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>24.324805881821</v>
+        <v>19.4598447054568</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08333585251519479</v>
+        <v>0.08324803003804715</v>
       </c>
       <c r="C7">
-        <v>2867.688021025244</v>
+        <v>2842.451347202744</v>
       </c>
       <c r="D7">
-        <v>2737.898021025244</v>
+        <v>2742.943347202744</v>
       </c>
       <c r="E7">
-        <v>-696.89</v>
+        <v>-666.6079999999999</v>
       </c>
       <c r="F7">
-        <v>151.41</v>
+        <v>181.692</v>
       </c>
       <c r="G7">
         <v>281.2</v>
@@ -1867,28 +1867,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M7">
-        <v>10.47113529171832</v>
+        <v>12.56536235006199</v>
       </c>
       <c r="N7">
-        <v>193.2955313749484</v>
+        <v>191.2013043166047</v>
       </c>
       <c r="O7">
-        <v>57.9886594124845</v>
+        <v>57.36039129498141</v>
       </c>
       <c r="P7">
-        <v>135.3068719624638</v>
+        <v>133.8409130216233</v>
       </c>
       <c r="Q7">
-        <v>136.2068719624638</v>
+        <v>134.7409130216233</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08517404255517783</v>
+        <v>0.08547171865182568</v>
       </c>
       <c r="T7">
-        <v>0.5729402949895525</v>
+        <v>0.577271844903071</v>
       </c>
       <c r="U7">
         <v>0.06915748822216712</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>19.4598447054568</v>
+        <v>16.21653725454733</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08324803003804715</v>
+        <v>0.08316020756089952</v>
       </c>
       <c r="C8">
-        <v>2842.451347202744</v>
+        <v>2817.233302497199</v>
       </c>
       <c r="D8">
-        <v>2742.943347202744</v>
+        <v>2748.007302497199</v>
       </c>
       <c r="E8">
-        <v>-666.6079999999999</v>
+        <v>-636.326</v>
       </c>
       <c r="F8">
-        <v>181.692</v>
+        <v>211.974</v>
       </c>
       <c r="G8">
         <v>281.2</v>
@@ -1949,28 +1949,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M8">
-        <v>12.56536235006199</v>
+        <v>14.65958940840565</v>
       </c>
       <c r="N8">
-        <v>191.2013043166047</v>
+        <v>189.107077258261</v>
       </c>
       <c r="O8">
-        <v>57.36039129498141</v>
+        <v>56.73212317747831</v>
       </c>
       <c r="P8">
-        <v>133.8409130216233</v>
+        <v>132.3749540807827</v>
       </c>
       <c r="Q8">
-        <v>134.7409130216233</v>
+        <v>133.2749540807827</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08547171865182568</v>
+        <v>0.08577579638496058</v>
       </c>
       <c r="T8">
-        <v>0.577271844903071</v>
+        <v>0.5816965464276331</v>
       </c>
       <c r="U8">
         <v>0.06915748822216712</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.21653725454734</v>
+        <v>13.89988907532629</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08316020756089952</v>
+        <v>0.08315638508375189</v>
       </c>
       <c r="C9">
-        <v>2817.233302497199</v>
+        <v>2787.172136030777</v>
       </c>
       <c r="D9">
-        <v>2748.007302497199</v>
+        <v>2748.228136030777</v>
       </c>
       <c r="E9">
-        <v>-636.3259999999999</v>
+        <v>-606.044</v>
       </c>
       <c r="F9">
-        <v>211.974</v>
+        <v>242.256</v>
       </c>
       <c r="G9">
         <v>281.2</v>
@@ -2031,45 +2031,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M9">
-        <v>14.65958940840565</v>
+        <v>17.11720046674931</v>
       </c>
       <c r="N9">
-        <v>189.107077258261</v>
+        <v>186.6494661999174</v>
       </c>
       <c r="O9">
-        <v>56.73212317747831</v>
+        <v>55.99483985997521</v>
       </c>
       <c r="P9">
-        <v>132.3749540807827</v>
+        <v>130.6546263399422</v>
       </c>
       <c r="Q9">
-        <v>133.2749540807827</v>
+        <v>131.5546263399421</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08577579638496058</v>
+        <v>0.0860864845035984</v>
       </c>
       <c r="T9">
-        <v>0.5816965464276331</v>
+        <v>0.5862174371157726</v>
       </c>
       <c r="U9">
-        <v>0.06915748822216712</v>
+        <v>0.07065748822216711</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.04841024175551698</v>
+        <v>0.04946024175551697</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.89988907532629</v>
+        <v>11.90420519187642</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08315638508375189</v>
+        <v>0.08307906260660426</v>
       </c>
       <c r="C10">
-        <v>2787.172136030777</v>
+        <v>2761.364871189102</v>
       </c>
       <c r="D10">
-        <v>2748.228136030777</v>
+        <v>2752.702871189102</v>
       </c>
       <c r="E10">
-        <v>-606.044</v>
+        <v>-575.7619999999999</v>
       </c>
       <c r="F10">
-        <v>242.256</v>
+        <v>272.538</v>
       </c>
       <c r="G10">
         <v>281.2</v>
@@ -2113,28 +2113,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M10">
-        <v>17.11720046674931</v>
+        <v>19.25685052509298</v>
       </c>
       <c r="N10">
-        <v>186.6494661999174</v>
+        <v>184.5098161415737</v>
       </c>
       <c r="O10">
-        <v>55.99483985997521</v>
+        <v>55.35294484247211</v>
       </c>
       <c r="P10">
-        <v>130.6546263399422</v>
+        <v>129.1568712991016</v>
       </c>
       <c r="Q10">
-        <v>131.5546263399421</v>
+        <v>130.0568712991016</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0860864845035984</v>
+        <v>0.08640400093253597</v>
       </c>
       <c r="T10">
-        <v>0.5862174371157726</v>
+        <v>0.5908376880388161</v>
       </c>
       <c r="U10">
         <v>0.07065748822216711</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.90420519187642</v>
+        <v>10.58151572611238</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08307906260660426</v>
+        <v>0.08312074012945664</v>
       </c>
       <c r="C11">
-        <v>2761.364871189102</v>
+        <v>2728.669139190138</v>
       </c>
       <c r="D11">
-        <v>2752.702871189102</v>
+        <v>2750.289139190138</v>
       </c>
       <c r="E11">
-        <v>-575.7619999999999</v>
+        <v>-545.48</v>
       </c>
       <c r="F11">
-        <v>272.538</v>
+        <v>302.8199999999999</v>
       </c>
       <c r="G11">
         <v>281.2</v>
@@ -2195,45 +2195,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M11">
-        <v>19.25685052509298</v>
+        <v>21.91129458343664</v>
       </c>
       <c r="N11">
-        <v>184.5098161415737</v>
+        <v>181.85537208323</v>
       </c>
       <c r="O11">
-        <v>55.35294484247211</v>
+        <v>54.55661162496901</v>
       </c>
       <c r="P11">
-        <v>129.1568712991016</v>
+        <v>127.298760458261</v>
       </c>
       <c r="Q11">
-        <v>130.0568712991016</v>
+        <v>128.198760458261</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08640400093253597</v>
+        <v>0.0867285732821166</v>
       </c>
       <c r="T11">
-        <v>0.5908376880388161</v>
+        <v>0.595560611204594</v>
       </c>
       <c r="U11">
-        <v>0.07065748822216711</v>
+        <v>0.07235748822216712</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.04946024175551697</v>
+        <v>0.05065024175551698</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.58151572611238</v>
+        <v>9.299617870169094</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08312074012945664</v>
+        <v>0.083055317652309</v>
       </c>
       <c r="C12">
-        <v>2728.669139190138</v>
+        <v>2702.177943279116</v>
       </c>
       <c r="D12">
-        <v>2750.289139190138</v>
+        <v>2754.079943279116</v>
       </c>
       <c r="E12">
-        <v>-545.48</v>
+        <v>-515.198</v>
       </c>
       <c r="F12">
-        <v>302.82</v>
+        <v>333.102</v>
       </c>
       <c r="G12">
         <v>281.2</v>
@@ -2277,28 +2277,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M12">
-        <v>21.91129458343665</v>
+        <v>24.10242404178031</v>
       </c>
       <c r="N12">
-        <v>181.85537208323</v>
+        <v>179.6642426248864</v>
       </c>
       <c r="O12">
-        <v>54.55661162496901</v>
+        <v>53.8992727874659</v>
       </c>
       <c r="P12">
-        <v>127.298760458261</v>
+        <v>125.7649698374205</v>
       </c>
       <c r="Q12">
-        <v>128.198760458261</v>
+        <v>126.6649698374204</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0867285732821166</v>
+        <v>0.08706043939236195</v>
       </c>
       <c r="T12">
-        <v>0.595560611204594</v>
+        <v>0.6003896674752208</v>
       </c>
       <c r="U12">
         <v>0.07235748822216712</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>9.299617870169092</v>
+        <v>8.454198063790084</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.083055317652309</v>
+        <v>0.08298989517516138</v>
       </c>
       <c r="C13">
-        <v>2702.177943279116</v>
+        <v>2675.697211744101</v>
       </c>
       <c r="D13">
-        <v>2754.079943279116</v>
+        <v>2757.881211744101</v>
       </c>
       <c r="E13">
-        <v>-515.198</v>
+        <v>-484.916</v>
       </c>
       <c r="F13">
-        <v>333.102</v>
+        <v>363.384</v>
       </c>
       <c r="G13">
         <v>281.2</v>
@@ -2359,28 +2359,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M13">
-        <v>24.10242404178031</v>
+        <v>26.29355350012397</v>
       </c>
       <c r="N13">
-        <v>179.6642426248864</v>
+        <v>177.4731131665427</v>
       </c>
       <c r="O13">
-        <v>53.8992727874659</v>
+        <v>53.24193394996281</v>
       </c>
       <c r="P13">
-        <v>125.7649698374205</v>
+        <v>124.2311792165799</v>
       </c>
       <c r="Q13">
-        <v>126.6649698374204</v>
+        <v>125.1311792165799</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08706043939236195</v>
+        <v>0.0873998479142038</v>
       </c>
       <c r="T13">
-        <v>0.6003896674752208</v>
+        <v>0.6053284750247256</v>
       </c>
       <c r="U13">
         <v>0.07235748822216712</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>8.454198063790084</v>
+        <v>7.749681558474244</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08298989517516138</v>
+        <v>0.08299727269801374</v>
       </c>
       <c r="C14">
-        <v>2675.697211744101</v>
+        <v>2644.986027722242</v>
       </c>
       <c r="D14">
-        <v>2757.881211744101</v>
+        <v>2757.452027722242</v>
       </c>
       <c r="E14">
-        <v>-484.916</v>
+        <v>-454.634</v>
       </c>
       <c r="F14">
-        <v>363.384</v>
+        <v>393.666</v>
       </c>
       <c r="G14">
         <v>281.2</v>
@@ -2441,45 +2441,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M14">
-        <v>26.29355350012397</v>
+        <v>28.79961575846764</v>
       </c>
       <c r="N14">
-        <v>177.4731131665427</v>
+        <v>174.967050908199</v>
       </c>
       <c r="O14">
-        <v>53.24193394996281</v>
+        <v>52.49011527245971</v>
       </c>
       <c r="P14">
-        <v>124.2311792165799</v>
+        <v>122.4769356357393</v>
       </c>
       <c r="Q14">
-        <v>125.1311792165799</v>
+        <v>123.3769356357393</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0873998479142038</v>
+        <v>0.08774705893080062</v>
       </c>
       <c r="T14">
-        <v>0.6053284750247256</v>
+        <v>0.6103808183799661</v>
       </c>
       <c r="U14">
-        <v>0.07235748822216712</v>
+        <v>0.07315748822216711</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.05065024175551698</v>
+        <v>0.05121024175551697</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>7.749681558474244</v>
+        <v>7.075325878497368</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08299727269801374</v>
+        <v>0.08293745022086611</v>
       </c>
       <c r="C15">
-        <v>2644.986027722242</v>
+        <v>2618.188027847925</v>
       </c>
       <c r="D15">
-        <v>2757.452027722242</v>
+        <v>2760.936027847925</v>
       </c>
       <c r="E15">
-        <v>-454.634</v>
+        <v>-424.3519999999999</v>
       </c>
       <c r="F15">
-        <v>393.666</v>
+        <v>423.948</v>
       </c>
       <c r="G15">
         <v>281.2</v>
@@ -2523,28 +2523,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M15">
-        <v>28.79961575846764</v>
+        <v>31.01497081681131</v>
       </c>
       <c r="N15">
-        <v>174.967050908199</v>
+        <v>172.7516958498554</v>
       </c>
       <c r="O15">
-        <v>52.49011527245971</v>
+        <v>51.82550875495661</v>
       </c>
       <c r="P15">
-        <v>122.4769356357393</v>
+        <v>120.9261870948988</v>
       </c>
       <c r="Q15">
-        <v>123.3769356357393</v>
+        <v>121.8261870948987</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08774705893080062</v>
+        <v>0.08810234462220203</v>
       </c>
       <c r="T15">
-        <v>0.6103808183799661</v>
+        <v>0.6155506580923051</v>
       </c>
       <c r="U15">
         <v>0.07315748822216711</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.075325878497368</v>
+        <v>6.569945458604698</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08293745022086611</v>
+        <v>0.0828776277437185</v>
       </c>
       <c r="C16">
-        <v>2618.188027847925</v>
+        <v>2591.398843077308</v>
       </c>
       <c r="D16">
-        <v>2760.936027847925</v>
+        <v>2764.428843077308</v>
       </c>
       <c r="E16">
-        <v>-424.3519999999999</v>
+        <v>-394.0699999999999</v>
       </c>
       <c r="F16">
-        <v>423.948</v>
+        <v>454.23</v>
       </c>
       <c r="G16">
         <v>281.2</v>
@@ -2605,28 +2605,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M16">
-        <v>31.01497081681131</v>
+        <v>33.23032587515497</v>
       </c>
       <c r="N16">
-        <v>172.7516958498554</v>
+        <v>170.5363407915117</v>
       </c>
       <c r="O16">
-        <v>51.82550875495661</v>
+        <v>51.16090223745351</v>
       </c>
       <c r="P16">
-        <v>120.9261870948988</v>
+        <v>119.3754385540582</v>
       </c>
       <c r="Q16">
-        <v>121.8261870948987</v>
+        <v>120.2754385540582</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08810234462220203</v>
+        <v>0.08846598997693053</v>
       </c>
       <c r="T16">
-        <v>0.6155506580923051</v>
+        <v>0.6208421410919934</v>
       </c>
       <c r="U16">
         <v>0.07315748822216711</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>6.569945458604698</v>
+        <v>6.131949094697719</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0828776277437185</v>
+        <v>0.08292980526657086</v>
       </c>
       <c r="C17">
-        <v>2591.398843077308</v>
+        <v>2558.069896737541</v>
       </c>
       <c r="D17">
-        <v>2764.428843077308</v>
+        <v>2761.381896737541</v>
       </c>
       <c r="E17">
-        <v>-394.07</v>
+        <v>-363.788</v>
       </c>
       <c r="F17">
-        <v>454.23</v>
+        <v>484.512</v>
       </c>
       <c r="G17">
         <v>281.2</v>
@@ -2687,45 +2687,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M17">
-        <v>33.23032587515496</v>
+        <v>35.93019293349863</v>
       </c>
       <c r="N17">
-        <v>170.5363407915117</v>
+        <v>167.836473733168</v>
       </c>
       <c r="O17">
-        <v>51.16090223745351</v>
+        <v>50.35094211995041</v>
       </c>
       <c r="P17">
-        <v>119.3754385540582</v>
+        <v>117.4855316132176</v>
       </c>
       <c r="Q17">
-        <v>120.2754385540582</v>
+        <v>118.3855316132176</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08846598997693053</v>
+        <v>0.08883829355439064</v>
       </c>
       <c r="T17">
-        <v>0.6208421410919934</v>
+        <v>0.6262596117821504</v>
       </c>
       <c r="U17">
-        <v>0.07315748822216711</v>
+        <v>0.07415748822216711</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.05121024175551697</v>
+        <v>0.05191024175551698</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.13194909469772</v>
+        <v>5.671182090332998</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08292980526657086</v>
+        <v>0.08287698278942324</v>
       </c>
       <c r="C18">
-        <v>2558.069896737541</v>
+        <v>2530.872547748165</v>
       </c>
       <c r="D18">
-        <v>2761.381896737541</v>
+        <v>2764.466547748165</v>
       </c>
       <c r="E18">
-        <v>-363.788</v>
+        <v>-333.506</v>
       </c>
       <c r="F18">
-        <v>484.512</v>
+        <v>514.794</v>
       </c>
       <c r="G18">
         <v>281.2</v>
@@ -2769,28 +2769,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M18">
-        <v>35.93019293349863</v>
+        <v>38.17582999184229</v>
       </c>
       <c r="N18">
-        <v>167.836473733168</v>
+        <v>165.5908366748244</v>
       </c>
       <c r="O18">
-        <v>50.35094211995041</v>
+        <v>49.67725100244732</v>
       </c>
       <c r="P18">
-        <v>117.4855316132176</v>
+        <v>115.9135856723771</v>
       </c>
       <c r="Q18">
-        <v>118.3855316132176</v>
+        <v>116.8135856723771</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08883829355439064</v>
+        <v>0.08921956830239199</v>
       </c>
       <c r="T18">
-        <v>0.6262596117821504</v>
+        <v>0.6318076239347209</v>
       </c>
       <c r="U18">
         <v>0.07415748822216711</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.671182090332998</v>
+        <v>5.337583143842823</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08287698278942324</v>
+        <v>0.0828241603122756</v>
       </c>
       <c r="C19">
-        <v>2530.872547748165</v>
+        <v>2503.682097994811</v>
       </c>
       <c r="D19">
-        <v>2764.466547748165</v>
+        <v>2767.558097994811</v>
       </c>
       <c r="E19">
-        <v>-333.506</v>
+        <v>-303.2239999999999</v>
       </c>
       <c r="F19">
-        <v>514.794</v>
+        <v>545.076</v>
       </c>
       <c r="G19">
         <v>281.2</v>
@@ -2851,28 +2851,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M19">
-        <v>38.17582999184229</v>
+        <v>40.42146705018596</v>
       </c>
       <c r="N19">
-        <v>165.5908366748244</v>
+        <v>163.3451996164807</v>
       </c>
       <c r="O19">
-        <v>49.67725100244732</v>
+        <v>49.00355988494422</v>
       </c>
       <c r="P19">
-        <v>115.9135856723771</v>
+        <v>114.3416397315365</v>
       </c>
       <c r="Q19">
-        <v>116.8135856723771</v>
+        <v>115.2416397315365</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08921956830239199</v>
+        <v>0.08961014243449091</v>
       </c>
       <c r="T19">
-        <v>0.6318076239347209</v>
+        <v>0.6374909534568661</v>
       </c>
       <c r="U19">
         <v>0.07415748822216711</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.337583143842823</v>
+        <v>5.041050746962665</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0828241603122756</v>
+        <v>0.08277133783512797</v>
       </c>
       <c r="C20">
-        <v>2503.682097994811</v>
+        <v>2476.498570649993</v>
       </c>
       <c r="D20">
-        <v>2767.558097994811</v>
+        <v>2770.656570649993</v>
       </c>
       <c r="E20">
-        <v>-303.224</v>
+        <v>-272.942</v>
       </c>
       <c r="F20">
-        <v>545.0759999999999</v>
+        <v>575.3579999999999</v>
       </c>
       <c r="G20">
         <v>281.2</v>
@@ -2933,28 +2933,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M20">
-        <v>40.42146705018595</v>
+        <v>42.66710410852962</v>
       </c>
       <c r="N20">
-        <v>163.3451996164807</v>
+        <v>161.0995625581371</v>
       </c>
       <c r="O20">
-        <v>49.00355988494422</v>
+        <v>48.32986876744111</v>
       </c>
       <c r="P20">
-        <v>114.3416397315365</v>
+        <v>112.7696937906959</v>
       </c>
       <c r="Q20">
-        <v>115.2416397315365</v>
+        <v>113.6696937906959</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08961014243449091</v>
+        <v>0.09001036037232067</v>
       </c>
       <c r="T20">
-        <v>0.6374909534568661</v>
+        <v>0.643314612103015</v>
       </c>
       <c r="U20">
         <v>0.07415748822216711</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.041050746962666</v>
+        <v>4.77573228659621</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08277133783512797</v>
+        <v>0.08271851535798035</v>
       </c>
       <c r="C21">
-        <v>2476.498570649993</v>
+        <v>2449.321988990115</v>
       </c>
       <c r="D21">
-        <v>2770.656570649993</v>
+        <v>2773.761988990115</v>
       </c>
       <c r="E21">
-        <v>-272.942</v>
+        <v>-242.66</v>
       </c>
       <c r="F21">
-        <v>575.3579999999999</v>
+        <v>605.64</v>
       </c>
       <c r="G21">
         <v>281.2</v>
@@ -3015,28 +3015,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M21">
-        <v>42.66710410852962</v>
+        <v>44.91274116687329</v>
       </c>
       <c r="N21">
-        <v>161.0995625581371</v>
+        <v>158.8539254997934</v>
       </c>
       <c r="O21">
-        <v>48.32986876744111</v>
+        <v>47.65617764993801</v>
       </c>
       <c r="P21">
-        <v>112.7696937906959</v>
+        <v>111.1977478498554</v>
       </c>
       <c r="Q21">
-        <v>113.6696937906959</v>
+        <v>112.0977478498554</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09001036037232067</v>
+        <v>0.09042058375859618</v>
       </c>
       <c r="T21">
-        <v>0.643314612103015</v>
+        <v>0.6492838622153178</v>
       </c>
       <c r="U21">
         <v>0.07415748822216711</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.77573228659621</v>
+        <v>4.536945672266398</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08271851535798035</v>
+        <v>0.08303319288083273</v>
       </c>
       <c r="C22">
-        <v>2449.321988990115</v>
+        <v>2400.642294557548</v>
       </c>
       <c r="D22">
-        <v>2773.761988990115</v>
+        <v>2755.364294557548</v>
       </c>
       <c r="E22">
-        <v>-242.66</v>
+        <v>-212.3779999999999</v>
       </c>
       <c r="F22">
-        <v>605.64</v>
+        <v>635.922</v>
       </c>
       <c r="G22">
         <v>281.2</v>
@@ -3097,45 +3097,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M22">
-        <v>44.91274116687329</v>
+        <v>48.74818322521696</v>
       </c>
       <c r="N22">
-        <v>158.8539254997934</v>
+        <v>155.0184834414497</v>
       </c>
       <c r="O22">
-        <v>47.65617764993801</v>
+        <v>46.50554503243492</v>
       </c>
       <c r="P22">
-        <v>111.1977478498554</v>
+        <v>108.5129384090148</v>
       </c>
       <c r="Q22">
-        <v>112.0977478498554</v>
+        <v>109.4129384090148</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09042058375859618</v>
+        <v>0.09084119254705589</v>
       </c>
       <c r="T22">
-        <v>0.6492838622153178</v>
+        <v>0.655404232583628</v>
       </c>
       <c r="U22">
-        <v>0.07415748822216711</v>
+        <v>0.07665748822216711</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.05191024175551698</v>
+        <v>0.05366024175551698</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.536945672266398</v>
+        <v>4.179984836055596</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08303319288083272</v>
+        <v>0.08353687040368508</v>
       </c>
       <c r="C23">
-        <v>2400.642294557549</v>
+        <v>2341.415284708909</v>
       </c>
       <c r="D23">
-        <v>2755.364294557549</v>
+        <v>2726.419284708909</v>
       </c>
       <c r="E23">
-        <v>-212.378</v>
+        <v>-182.096</v>
       </c>
       <c r="F23">
-        <v>635.9219999999999</v>
+        <v>666.204</v>
       </c>
       <c r="G23">
         <v>281.2</v>
@@ -3179,45 +3179,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M23">
-        <v>48.74818322521695</v>
+        <v>53.40123928356062</v>
       </c>
       <c r="N23">
-        <v>155.0184834414497</v>
+        <v>150.3654273831061</v>
       </c>
       <c r="O23">
-        <v>46.50554503243492</v>
+        <v>45.10962821493182</v>
       </c>
       <c r="P23">
-        <v>108.5129384090148</v>
+        <v>105.2557991681742</v>
       </c>
       <c r="Q23">
-        <v>109.4129384090148</v>
+        <v>106.1557991681742</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09084119254705589</v>
+        <v>0.09127258617624531</v>
       </c>
       <c r="T23">
-        <v>0.6554042325836279</v>
+        <v>0.6616815355254847</v>
       </c>
       <c r="U23">
-        <v>0.07665748822216711</v>
+        <v>0.08015748822216712</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.05366024175551698</v>
+        <v>0.05611024175551698</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>4.179984836055597</v>
+        <v>3.815766626401038</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08353687040368508</v>
+        <v>0.08352604792653745</v>
       </c>
       <c r="C24">
-        <v>2341.415284708909</v>
+        <v>2311.748829225829</v>
       </c>
       <c r="D24">
-        <v>2726.419284708909</v>
+        <v>2727.034829225829</v>
       </c>
       <c r="E24">
-        <v>-182.096</v>
+        <v>-151.814</v>
       </c>
       <c r="F24">
-        <v>666.204</v>
+        <v>696.486</v>
       </c>
       <c r="G24">
         <v>281.2</v>
@@ -3261,28 +3261,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M24">
-        <v>53.40123928356062</v>
+        <v>55.82856834190429</v>
       </c>
       <c r="N24">
-        <v>150.3654273831061</v>
+        <v>147.9380983247624</v>
       </c>
       <c r="O24">
-        <v>45.10962821493182</v>
+        <v>44.38142949742872</v>
       </c>
       <c r="P24">
-        <v>105.2557991681742</v>
+        <v>103.5566688273337</v>
       </c>
       <c r="Q24">
-        <v>106.1557991681742</v>
+        <v>104.4566688273337</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09127258617624531</v>
+        <v>0.09171518483476435</v>
       </c>
       <c r="T24">
-        <v>0.6616815355254847</v>
+        <v>0.668121885297</v>
       </c>
       <c r="U24">
         <v>0.08015748822216712</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.815766626401038</v>
+        <v>3.649863729600992</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08352604792653745</v>
+        <v>0.08398562544938983</v>
       </c>
       <c r="C25">
-        <v>2311.748829225829</v>
+        <v>2255.57005289673</v>
       </c>
       <c r="D25">
-        <v>2727.034829225829</v>
+        <v>2701.138052896731</v>
       </c>
       <c r="E25">
-        <v>-151.814</v>
+        <v>-121.5319999999999</v>
       </c>
       <c r="F25">
-        <v>696.486</v>
+        <v>726.768</v>
       </c>
       <c r="G25">
         <v>281.2</v>
@@ -3343,45 +3343,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M25">
-        <v>55.82856834190429</v>
+        <v>60.29084780024795</v>
       </c>
       <c r="N25">
-        <v>147.9380983247624</v>
+        <v>143.4758188664187</v>
       </c>
       <c r="O25">
-        <v>44.38142949742872</v>
+        <v>43.04274565992562</v>
       </c>
       <c r="P25">
-        <v>103.5566688273337</v>
+        <v>100.4330732064931</v>
       </c>
       <c r="Q25">
-        <v>104.4566688273337</v>
+        <v>101.3330732064931</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09171518483476435</v>
+        <v>0.0921694308264023</v>
       </c>
       <c r="T25">
-        <v>0.668121885297</v>
+        <v>0.6747317179572394</v>
       </c>
       <c r="U25">
-        <v>0.08015748822216712</v>
+        <v>0.08295748822216711</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.05611024175551698</v>
+        <v>0.05807024175551698</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.649863729600992</v>
+        <v>3.379728003523425</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08398562544938983</v>
+        <v>0.0839944029722422</v>
       </c>
       <c r="C26">
-        <v>2255.57005289673</v>
+        <v>2224.798233217225</v>
       </c>
       <c r="D26">
-        <v>2701.138052896731</v>
+        <v>2700.648233217225</v>
       </c>
       <c r="E26">
-        <v>-121.532</v>
+        <v>-91.25</v>
       </c>
       <c r="F26">
-        <v>726.7679999999999</v>
+        <v>757.05</v>
       </c>
       <c r="G26">
         <v>281.2</v>
@@ -3425,28 +3425,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M26">
-        <v>60.29084780024795</v>
+        <v>62.80296645859161</v>
       </c>
       <c r="N26">
-        <v>143.4758188664187</v>
+        <v>140.9637002080751</v>
       </c>
       <c r="O26">
-        <v>43.04274565992562</v>
+        <v>42.28911006242252</v>
       </c>
       <c r="P26">
-        <v>100.4330732064931</v>
+        <v>98.67459014565256</v>
       </c>
       <c r="Q26">
-        <v>101.3330732064931</v>
+        <v>99.57459014565254</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0921694308264023</v>
+        <v>0.09263579004448394</v>
       </c>
       <c r="T26">
-        <v>0.6747317179572394</v>
+        <v>0.6815178128217519</v>
       </c>
       <c r="U26">
         <v>0.08295748822216711</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.379728003523425</v>
+        <v>3.244538883382488</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0839944029722422</v>
+        <v>0.08400318049509456</v>
       </c>
       <c r="C27">
-        <v>2224.798233217225</v>
+        <v>2194.026591151611</v>
       </c>
       <c r="D27">
-        <v>2700.648233217225</v>
+        <v>2700.158591151611</v>
       </c>
       <c r="E27">
-        <v>-91.25</v>
+        <v>-60.96799999999996</v>
       </c>
       <c r="F27">
-        <v>757.05</v>
+        <v>787.332</v>
       </c>
       <c r="G27">
         <v>281.2</v>
@@ -3507,28 +3507,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M27">
-        <v>62.80296645859161</v>
+        <v>65.31508511693528</v>
       </c>
       <c r="N27">
-        <v>140.9637002080751</v>
+        <v>138.4515815497314</v>
       </c>
       <c r="O27">
-        <v>42.28911006242252</v>
+        <v>41.53547446491942</v>
       </c>
       <c r="P27">
-        <v>98.67459014565256</v>
+        <v>96.91610708481198</v>
       </c>
       <c r="Q27">
-        <v>99.57459014565254</v>
+        <v>97.81610708481196</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09263579004448394</v>
+        <v>0.09311475356575696</v>
       </c>
       <c r="T27">
-        <v>0.6815178128217519</v>
+        <v>0.6884873156555755</v>
       </c>
       <c r="U27">
         <v>0.08295748822216711</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.244538883382488</v>
+        <v>3.119748926329315</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08400318049509456</v>
+        <v>0.08401195801794693</v>
       </c>
       <c r="C28">
-        <v>2194.026591151611</v>
+        <v>2163.255126603297</v>
       </c>
       <c r="D28">
-        <v>2700.158591151611</v>
+        <v>2699.669126603297</v>
       </c>
       <c r="E28">
-        <v>-60.96799999999996</v>
+        <v>-30.68599999999992</v>
       </c>
       <c r="F28">
-        <v>787.332</v>
+        <v>817.614</v>
       </c>
       <c r="G28">
         <v>281.2</v>
@@ -3589,28 +3589,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M28">
-        <v>65.31508511693528</v>
+        <v>67.82720377527895</v>
       </c>
       <c r="N28">
-        <v>138.4515815497314</v>
+        <v>135.9394628913877</v>
       </c>
       <c r="O28">
-        <v>41.53547446491942</v>
+        <v>40.78183886741632</v>
       </c>
       <c r="P28">
-        <v>96.91610708481198</v>
+        <v>95.15762402397141</v>
       </c>
       <c r="Q28">
-        <v>97.81610708481196</v>
+        <v>96.05762402397139</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09311475356575696</v>
+        <v>0.09360683937528405</v>
       </c>
       <c r="T28">
-        <v>0.6884873156555755</v>
+        <v>0.6956477637725177</v>
       </c>
       <c r="U28">
         <v>0.08295748822216711</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.119748926329315</v>
+        <v>3.0042026697986</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08401195801794693</v>
+        <v>0.0855495355407993</v>
       </c>
       <c r="C29">
-        <v>2163.255126603297</v>
+        <v>2049.886439280837</v>
       </c>
       <c r="D29">
-        <v>2699.669126603297</v>
+        <v>2616.582439280837</v>
       </c>
       <c r="E29">
-        <v>-30.68599999999992</v>
+        <v>-0.4039999999998827</v>
       </c>
       <c r="F29">
-        <v>817.614</v>
+        <v>847.8960000000001</v>
       </c>
       <c r="G29">
         <v>281.2</v>
@@ -3671,45 +3671,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M29">
-        <v>67.82720377527895</v>
+        <v>76.95291123362261</v>
       </c>
       <c r="N29">
-        <v>135.9394628913877</v>
+        <v>126.8137554330441</v>
       </c>
       <c r="O29">
-        <v>40.78183886741632</v>
+        <v>38.04412662991322</v>
       </c>
       <c r="P29">
-        <v>95.15762402397141</v>
+        <v>88.76962880313084</v>
       </c>
       <c r="Q29">
-        <v>96.05762402397139</v>
+        <v>89.66962880313082</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09360683937528405</v>
+        <v>0.09411259423507577</v>
       </c>
       <c r="T29">
-        <v>0.6956477637725177</v>
+        <v>0.7030071132260414</v>
       </c>
       <c r="U29">
-        <v>0.08295748822216711</v>
+        <v>0.09075748822216712</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.05807024175551698</v>
+        <v>0.06353024175551698</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.0042026697986</v>
+        <v>2.647939673757736</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0855495355407993</v>
+        <v>0.08561291306365169</v>
       </c>
       <c r="C30">
-        <v>2049.886439280837</v>
+        <v>2016.289290869649</v>
       </c>
       <c r="D30">
-        <v>2616.582439280837</v>
+        <v>2613.267290869649</v>
       </c>
       <c r="E30">
-        <v>-0.4039999999998827</v>
+        <v>29.87800000000016</v>
       </c>
       <c r="F30">
-        <v>847.8960000000001</v>
+        <v>878.1780000000001</v>
       </c>
       <c r="G30">
         <v>281.2</v>
@@ -3753,28 +3753,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M30">
-        <v>76.95291123362261</v>
+        <v>79.70122949196629</v>
       </c>
       <c r="N30">
-        <v>126.8137554330441</v>
+        <v>124.0654371747004</v>
       </c>
       <c r="O30">
-        <v>38.04412662991322</v>
+        <v>37.21963115241012</v>
       </c>
       <c r="P30">
-        <v>88.76962880313084</v>
+        <v>86.84580602229028</v>
       </c>
       <c r="Q30">
-        <v>89.66962880313082</v>
+        <v>87.74580602229025</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09411259423507577</v>
+        <v>0.09463259571063629</v>
       </c>
       <c r="T30">
-        <v>0.7030071132260414</v>
+        <v>0.7105737682979744</v>
       </c>
       <c r="U30">
         <v>0.09075748822216712</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.647939673757736</v>
+        <v>2.5566314091454</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08561291306365168</v>
+        <v>0.08649529058650404</v>
       </c>
       <c r="C31">
-        <v>2016.28929086965</v>
+        <v>1940.709441775547</v>
       </c>
       <c r="D31">
-        <v>2613.26729086965</v>
+        <v>2567.969441775547</v>
       </c>
       <c r="E31">
-        <v>29.87799999999993</v>
+        <v>60.15999999999997</v>
       </c>
       <c r="F31">
-        <v>878.1779999999999</v>
+        <v>908.4599999999999</v>
       </c>
       <c r="G31">
         <v>281.2</v>
@@ -3835,45 +3835,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M31">
-        <v>79.70122949196626</v>
+        <v>85.99254175030993</v>
       </c>
       <c r="N31">
-        <v>124.0654371747004</v>
+        <v>117.7741249163568</v>
       </c>
       <c r="O31">
-        <v>37.21963115241012</v>
+        <v>35.33223747490702</v>
       </c>
       <c r="P31">
-        <v>86.8458060222903</v>
+        <v>82.44188744144972</v>
       </c>
       <c r="Q31">
-        <v>87.74580602229028</v>
+        <v>83.3418874414497</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09463259571063629</v>
+        <v>0.0951674543712128</v>
       </c>
       <c r="T31">
-        <v>0.7105737682979744</v>
+        <v>0.7183566135148196</v>
       </c>
       <c r="U31">
-        <v>0.09075748822216712</v>
+        <v>0.09465748822216712</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.06353024175551698</v>
+        <v>0.06626024175551698</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.556631409145401</v>
+        <v>2.36958534448637</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08649529058650404</v>
+        <v>0.08658596810935641</v>
       </c>
       <c r="C32">
-        <v>1940.709441775547</v>
+        <v>1905.861231717268</v>
       </c>
       <c r="D32">
-        <v>2567.969441775547</v>
+        <v>2563.403231717268</v>
       </c>
       <c r="E32">
-        <v>60.15999999999997</v>
+        <v>90.44200000000001</v>
       </c>
       <c r="F32">
-        <v>908.4599999999999</v>
+        <v>938.742</v>
       </c>
       <c r="G32">
         <v>281.2</v>
@@ -3917,28 +3917,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M32">
-        <v>85.99254175030993</v>
+        <v>88.85895980865359</v>
       </c>
       <c r="N32">
-        <v>117.7741249163568</v>
+        <v>114.9077068580131</v>
       </c>
       <c r="O32">
-        <v>35.33223747490702</v>
+        <v>34.47231205740393</v>
       </c>
       <c r="P32">
-        <v>82.44188744144972</v>
+        <v>80.43539480060916</v>
       </c>
       <c r="Q32">
-        <v>83.3418874414497</v>
+        <v>81.33539480060914</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0951674543712128</v>
+        <v>0.09571781618137125</v>
       </c>
       <c r="T32">
-        <v>0.7183566135148196</v>
+        <v>0.7263650484480951</v>
       </c>
       <c r="U32">
         <v>0.09465748822216712</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.36958534448637</v>
+        <v>2.293147107567455</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08658596810935641</v>
+        <v>0.08667664563220878</v>
       </c>
       <c r="C33">
-        <v>1905.861231717268</v>
+        <v>1871.029231560127</v>
       </c>
       <c r="D33">
-        <v>2563.403231717268</v>
+        <v>2558.853231560127</v>
       </c>
       <c r="E33">
-        <v>90.44200000000001</v>
+        <v>120.724</v>
       </c>
       <c r="F33">
-        <v>938.742</v>
+        <v>969.024</v>
       </c>
       <c r="G33">
         <v>281.2</v>
@@ -3999,28 +3999,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M33">
-        <v>88.85895980865359</v>
+        <v>91.72537786699726</v>
       </c>
       <c r="N33">
-        <v>114.9077068580131</v>
+        <v>112.0412887996694</v>
       </c>
       <c r="O33">
-        <v>34.47231205740393</v>
+        <v>33.61238663990083</v>
       </c>
       <c r="P33">
-        <v>80.43539480060916</v>
+        <v>78.4289021597686</v>
       </c>
       <c r="Q33">
-        <v>81.33539480060914</v>
+        <v>79.32890215976857</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09571781618137125</v>
+        <v>0.09628436510359317</v>
       </c>
       <c r="T33">
-        <v>0.7263650484480951</v>
+        <v>0.7346090255852906</v>
       </c>
       <c r="U33">
         <v>0.09465748822216712</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.293147107567455</v>
+        <v>2.221486260455972</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08667664563220878</v>
+        <v>0.08676732315506117</v>
       </c>
       <c r="C34">
-        <v>1871.029231560127</v>
+        <v>1836.213355140111</v>
       </c>
       <c r="D34">
-        <v>2558.853231560127</v>
+        <v>2554.319355140111</v>
       </c>
       <c r="E34">
-        <v>120.724</v>
+        <v>151.0060000000001</v>
       </c>
       <c r="F34">
-        <v>969.024</v>
+        <v>999.306</v>
       </c>
       <c r="G34">
         <v>281.2</v>
@@ -4081,28 +4081,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M34">
-        <v>91.72537786699726</v>
+        <v>94.59179592534093</v>
       </c>
       <c r="N34">
-        <v>112.0412887996694</v>
+        <v>109.1748707413257</v>
       </c>
       <c r="O34">
-        <v>33.61238663990083</v>
+        <v>32.75246122239772</v>
       </c>
       <c r="P34">
-        <v>78.4289021597686</v>
+        <v>76.42240951892802</v>
       </c>
       <c r="Q34">
-        <v>79.32890215976857</v>
+        <v>77.322409518928</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09628436510359317</v>
+        <v>0.09686782593394114</v>
       </c>
       <c r="T34">
-        <v>0.7346090255852906</v>
+        <v>0.7430990915922532</v>
       </c>
       <c r="U34">
         <v>0.09465748822216712</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.221486260455972</v>
+        <v>2.154168494987609</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08676732315506117</v>
+        <v>0.08685800067791352</v>
       </c>
       <c r="C35">
-        <v>1836.213355140111</v>
+        <v>1801.413516902802</v>
       </c>
       <c r="D35">
-        <v>2554.319355140111</v>
+        <v>2549.801516902802</v>
       </c>
       <c r="E35">
-        <v>151.0060000000001</v>
+        <v>181.288</v>
       </c>
       <c r="F35">
-        <v>999.306</v>
+        <v>1029.588</v>
       </c>
       <c r="G35">
         <v>281.2</v>
@@ -4163,28 +4163,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M35">
-        <v>94.59179592534093</v>
+        <v>97.45821398368459</v>
       </c>
       <c r="N35">
-        <v>109.1748707413257</v>
+        <v>106.3084526829821</v>
       </c>
       <c r="O35">
-        <v>32.75246122239772</v>
+        <v>31.89253580489463</v>
       </c>
       <c r="P35">
-        <v>76.42240951892802</v>
+        <v>74.41591687808747</v>
       </c>
       <c r="Q35">
-        <v>77.322409518928</v>
+        <v>75.31591687808745</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09686782593394114</v>
+        <v>0.09746896739551175</v>
       </c>
       <c r="T35">
-        <v>0.7430990915922532</v>
+        <v>0.7518464323266992</v>
       </c>
       <c r="U35">
         <v>0.09465748822216712</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.154168494987609</v>
+        <v>2.090810598076208</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08685800067791352</v>
+        <v>0.08694867820076591</v>
       </c>
       <c r="C36">
-        <v>1801.413516902802</v>
+        <v>1766.629631897992</v>
       </c>
       <c r="D36">
-        <v>2549.801516902802</v>
+        <v>2545.299631897993</v>
       </c>
       <c r="E36">
-        <v>181.288</v>
+        <v>211.5700000000002</v>
       </c>
       <c r="F36">
-        <v>1029.588</v>
+        <v>1059.87</v>
       </c>
       <c r="G36">
         <v>281.2</v>
@@ -4245,28 +4245,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M36">
-        <v>97.45821398368459</v>
+        <v>100.3246320420283</v>
       </c>
       <c r="N36">
-        <v>106.3084526829821</v>
+        <v>103.4420346246384</v>
       </c>
       <c r="O36">
-        <v>31.89253580489463</v>
+        <v>31.03261038739152</v>
       </c>
       <c r="P36">
-        <v>74.41591687808747</v>
+        <v>72.4094242372469</v>
       </c>
       <c r="Q36">
-        <v>75.31591687808745</v>
+        <v>73.30942423724687</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09746896739551175</v>
+        <v>0.09808860551743841</v>
       </c>
       <c r="T36">
-        <v>0.7518464323266992</v>
+        <v>0.7608629220068207</v>
       </c>
       <c r="U36">
         <v>0.09465748822216712</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.090810598076208</v>
+        <v>2.031073152416888</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08694867820076591</v>
+        <v>0.09061775572361827</v>
       </c>
       <c r="C37">
-        <v>1766.629631897992</v>
+        <v>1566.634258131023</v>
       </c>
       <c r="D37">
-        <v>2545.299631897993</v>
+        <v>2375.586258131023</v>
       </c>
       <c r="E37">
-        <v>211.5700000000002</v>
+        <v>241.8520000000001</v>
       </c>
       <c r="F37">
-        <v>1059.87</v>
+        <v>1090.152</v>
       </c>
       <c r="G37">
         <v>281.2</v>
@@ -4327,45 +4327,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M37">
-        <v>100.3246320420283</v>
+        <v>118.6712085003719</v>
       </c>
       <c r="N37">
-        <v>103.4420346246384</v>
+        <v>85.09545816629475</v>
       </c>
       <c r="O37">
-        <v>31.03261038739152</v>
+        <v>25.52863744988842</v>
       </c>
       <c r="P37">
-        <v>72.4094242372469</v>
+        <v>59.56682071640633</v>
       </c>
       <c r="Q37">
-        <v>73.30942423724687</v>
+        <v>60.4668207164063</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09808860551743841</v>
+        <v>0.09872760733067526</v>
       </c>
       <c r="T37">
-        <v>0.7608629220068207</v>
+        <v>0.770161176989446</v>
       </c>
       <c r="U37">
-        <v>0.09465748822216712</v>
+        <v>0.1088574882221671</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.06626024175551698</v>
+        <v>0.07620024175551698</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>2.031073152416888</v>
+        <v>1.7170691125643</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09061775572361828</v>
+        <v>0.09080783324647065</v>
       </c>
       <c r="C38">
-        <v>1566.634258131023</v>
+        <v>1528.174688233369</v>
       </c>
       <c r="D38">
-        <v>2375.586258131023</v>
+        <v>2367.408688233369</v>
       </c>
       <c r="E38">
-        <v>241.8519999999999</v>
+        <v>272.134</v>
       </c>
       <c r="F38">
-        <v>1090.152</v>
+        <v>1120.434</v>
       </c>
       <c r="G38">
         <v>281.2</v>
@@ -4409,28 +4409,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M38">
-        <v>118.6712085003719</v>
+        <v>121.9676309587156</v>
       </c>
       <c r="N38">
-        <v>85.09545816629478</v>
+        <v>81.79903570795109</v>
       </c>
       <c r="O38">
-        <v>25.52863744988843</v>
+        <v>24.53971071238533</v>
       </c>
       <c r="P38">
-        <v>59.56682071640634</v>
+        <v>57.25932499556576</v>
       </c>
       <c r="Q38">
-        <v>60.46682071640632</v>
+        <v>58.15932499556574</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09872760733067526</v>
+        <v>0.0993868949157609</v>
       </c>
       <c r="T38">
-        <v>0.770161176989446</v>
+        <v>0.7797546146699323</v>
       </c>
       <c r="U38">
         <v>0.1088574882221671</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>1.717069112564301</v>
+        <v>1.670661839251752</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09080783324647065</v>
+        <v>0.09099791076932304</v>
       </c>
       <c r="C39">
-        <v>1528.174688233369</v>
+        <v>1489.771225109921</v>
       </c>
       <c r="D39">
-        <v>2367.408688233369</v>
+        <v>2359.287225109922</v>
       </c>
       <c r="E39">
-        <v>272.134</v>
+        <v>302.4159999999999</v>
       </c>
       <c r="F39">
-        <v>1120.434</v>
+        <v>1150.716</v>
       </c>
       <c r="G39">
         <v>281.2</v>
@@ -4491,28 +4491,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M39">
-        <v>121.9676309587156</v>
+        <v>125.2640534170592</v>
       </c>
       <c r="N39">
-        <v>81.79903570795109</v>
+        <v>78.50261324960744</v>
       </c>
       <c r="O39">
-        <v>24.53971071238533</v>
+        <v>23.55078397488223</v>
       </c>
       <c r="P39">
-        <v>57.25932499556576</v>
+        <v>54.95182927472521</v>
       </c>
       <c r="Q39">
-        <v>58.15932499556574</v>
+        <v>55.85182927472518</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0993868949157609</v>
+        <v>0.1000674498423009</v>
       </c>
       <c r="T39">
-        <v>0.7797546146699323</v>
+        <v>0.7896575180820473</v>
       </c>
       <c r="U39">
         <v>0.1088574882221671</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>1.670661839251752</v>
+        <v>1.626697054008285</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09099791076932304</v>
+        <v>0.09118798829217539</v>
       </c>
       <c r="C40">
-        <v>1489.771225109921</v>
+        <v>1451.423293307118</v>
       </c>
       <c r="D40">
-        <v>2359.287225109922</v>
+        <v>2351.221293307118</v>
       </c>
       <c r="E40">
-        <v>302.4159999999999</v>
+        <v>332.6980000000001</v>
       </c>
       <c r="F40">
-        <v>1150.716</v>
+        <v>1180.998</v>
       </c>
       <c r="G40">
         <v>281.2</v>
@@ -4573,28 +4573,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M40">
-        <v>125.2640534170592</v>
+        <v>128.5604758754029</v>
       </c>
       <c r="N40">
-        <v>78.50261324960744</v>
+        <v>75.20619079126374</v>
       </c>
       <c r="O40">
-        <v>23.55078397488223</v>
+        <v>22.56185723737912</v>
       </c>
       <c r="P40">
-        <v>54.95182927472521</v>
+        <v>52.64433355388462</v>
       </c>
       <c r="Q40">
-        <v>55.85182927472518</v>
+        <v>53.5443335538846</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1000674498423009</v>
+        <v>0.1007703180451209</v>
       </c>
       <c r="T40">
-        <v>0.7896575180820473</v>
+        <v>0.7998851068519366</v>
       </c>
       <c r="U40">
         <v>0.1088574882221671</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>1.626697054008285</v>
+        <v>1.584986873136277</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09118798829217539</v>
+        <v>0.09137806581502776</v>
       </c>
       <c r="C41">
-        <v>1451.423293307118</v>
+        <v>1413.130325214022</v>
       </c>
       <c r="D41">
-        <v>2351.221293307118</v>
+        <v>2343.210325214022</v>
       </c>
       <c r="E41">
-        <v>332.6980000000001</v>
+        <v>362.98</v>
       </c>
       <c r="F41">
-        <v>1180.998</v>
+        <v>1211.28</v>
       </c>
       <c r="G41">
         <v>281.2</v>
@@ -4655,28 +4655,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M41">
-        <v>128.5604758754029</v>
+        <v>131.8568983337466</v>
       </c>
       <c r="N41">
-        <v>75.20619079126374</v>
+        <v>71.90976833292009</v>
       </c>
       <c r="O41">
-        <v>22.56185723737912</v>
+        <v>21.57293049987603</v>
       </c>
       <c r="P41">
-        <v>52.64433355388462</v>
+        <v>50.33683783304407</v>
       </c>
       <c r="Q41">
-        <v>53.5443335538846</v>
+        <v>51.23683783304405</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1007703180451209</v>
+        <v>0.101496615188035</v>
       </c>
       <c r="T41">
-        <v>0.7998851068519366</v>
+        <v>0.8104536152474888</v>
       </c>
       <c r="U41">
         <v>0.1088574882221671</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>1.584986873136277</v>
+        <v>1.54536220130787</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09137806581502776</v>
+        <v>0.09156814333788013</v>
       </c>
       <c r="C42">
-        <v>1413.130325214022</v>
+        <v>1374.891760929181</v>
       </c>
       <c r="D42">
-        <v>2343.210325214022</v>
+        <v>2335.253760929182</v>
       </c>
       <c r="E42">
-        <v>362.98</v>
+        <v>393.2620000000002</v>
       </c>
       <c r="F42">
-        <v>1211.28</v>
+        <v>1241.562</v>
       </c>
       <c r="G42">
         <v>281.2</v>
@@ -4737,28 +4737,28 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M42">
-        <v>131.8568983337466</v>
+        <v>135.1533207920903</v>
       </c>
       <c r="N42">
-        <v>71.90976833292009</v>
+        <v>68.61334587457642</v>
       </c>
       <c r="O42">
-        <v>21.57293049987603</v>
+        <v>20.58400376237293</v>
       </c>
       <c r="P42">
-        <v>50.33683783304407</v>
+        <v>48.02934211220349</v>
       </c>
       <c r="Q42">
-        <v>51.23683783304405</v>
+        <v>48.92934211220347</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.101496615188035</v>
+        <v>0.1022475325730816</v>
       </c>
       <c r="T42">
-        <v>0.8104536152474888</v>
+        <v>0.821380378164924</v>
       </c>
       <c r="U42">
         <v>0.1088574882221671</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.54536220130787</v>
+        <v>1.507670440300361</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09156814333788013</v>
+        <v>0.1093005966447285</v>
       </c>
       <c r="C43">
-        <v>1374.891760929181</v>
+        <v>782.8190937030949</v>
       </c>
       <c r="D43">
-        <v>2335.253760929182</v>
+        <v>1773.463093703095</v>
       </c>
       <c r="E43">
-        <v>393.2620000000002</v>
+        <v>423.5440000000001</v>
       </c>
       <c r="F43">
-        <v>1241.562</v>
+        <v>1271.844</v>
       </c>
       <c r="G43">
         <v>281.2</v>
@@ -4819,45 +4819,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M43">
-        <v>135.1533207920903</v>
+        <v>210.690482450434</v>
       </c>
       <c r="N43">
-        <v>68.61334587457642</v>
+        <v>-6.923815783767282</v>
       </c>
       <c r="O43">
-        <v>20.58400376237293</v>
+        <v>-2.077144735130184</v>
       </c>
       <c r="P43">
-        <v>48.02934211220349</v>
+        <v>-4.846671048637097</v>
       </c>
       <c r="Q43">
-        <v>48.92934211220347</v>
+        <v>-3.946671048637119</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1022475325730816</v>
+        <v>0.1032954505288979</v>
       </c>
       <c r="T43">
-        <v>0.821380378164924</v>
+        <v>0.8366288612712454</v>
       </c>
       <c r="U43">
-        <v>0.1088574882221671</v>
+        <v>0.1656574882221671</v>
       </c>
       <c r="V43">
-        <v>0.3</v>
+        <v>0.2901412502787408</v>
       </c>
       <c r="W43">
-        <v>0.07620024175551698</v>
+        <v>0.1175934174713518</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.507670440300361</v>
+        <v>0.967137500929136</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1093005966447285</v>
+        <v>0.1104991715269502</v>
       </c>
       <c r="C44">
-        <v>782.8190937030952</v>
+        <v>724.1609189290361</v>
       </c>
       <c r="D44">
-        <v>1773.463093703095</v>
+        <v>1745.086918929036</v>
       </c>
       <c r="E44">
-        <v>423.5439999999999</v>
+        <v>453.826</v>
       </c>
       <c r="F44">
-        <v>1271.844</v>
+        <v>1302.126</v>
       </c>
       <c r="G44">
         <v>281.2</v>
@@ -4901,37 +4901,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M44">
-        <v>210.6904824504339</v>
+        <v>215.7069225087776</v>
       </c>
       <c r="N44">
-        <v>-6.923815783767225</v>
+        <v>-11.94025584211093</v>
       </c>
       <c r="O44">
-        <v>-2.077144735130168</v>
+        <v>-3.582076752633279</v>
       </c>
       <c r="P44">
-        <v>-4.846671048637058</v>
+        <v>-8.35817908947765</v>
       </c>
       <c r="Q44">
-        <v>-3.94667104863708</v>
+        <v>-7.458179089477673</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1032954505288979</v>
+        <v>0.10430414264344</v>
       </c>
       <c r="T44">
-        <v>0.8366288612712454</v>
+        <v>0.8513065605917934</v>
       </c>
       <c r="U44">
         <v>0.1656574882221671</v>
       </c>
       <c r="V44">
-        <v>0.2901412502787408</v>
+        <v>0.2833937793420259</v>
       </c>
       <c r="W44">
-        <v>0.1175934174713518</v>
+        <v>0.1187111865585801</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.9671375009291362</v>
+        <v>0.9446459311400863</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1104991715269502</v>
+        <v>0.1116977464091719</v>
       </c>
       <c r="C45">
-        <v>724.1609189290361</v>
+        <v>666.3965056673337</v>
       </c>
       <c r="D45">
-        <v>1745.086918929036</v>
+        <v>1717.604505667334</v>
       </c>
       <c r="E45">
-        <v>453.826</v>
+        <v>484.1079999999999</v>
       </c>
       <c r="F45">
-        <v>1302.126</v>
+        <v>1332.408</v>
       </c>
       <c r="G45">
         <v>281.2</v>
@@ -4983,37 +4983,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M45">
-        <v>215.7069225087776</v>
+        <v>220.7233625671213</v>
       </c>
       <c r="N45">
-        <v>-11.94025584211093</v>
+        <v>-16.95669590045458</v>
       </c>
       <c r="O45">
-        <v>-3.582076752633279</v>
+        <v>-5.087008770136372</v>
       </c>
       <c r="P45">
-        <v>-8.35817908947765</v>
+        <v>-11.8696871303182</v>
       </c>
       <c r="Q45">
-        <v>-7.458179089477673</v>
+        <v>-10.96968713031823</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.10430414264344</v>
+        <v>0.1053488594763585</v>
       </c>
       <c r="T45">
-        <v>0.8513065605917934</v>
+        <v>0.8665084634595041</v>
       </c>
       <c r="U45">
         <v>0.1656574882221671</v>
       </c>
       <c r="V45">
-        <v>0.2833937793420259</v>
+        <v>0.2769530116297071</v>
       </c>
       <c r="W45">
-        <v>0.1187111865585801</v>
+        <v>0.1197781479600252</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.9446459311400863</v>
+        <v>0.9231767054323572</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1116977464091719</v>
+        <v>0.1128963212913935</v>
       </c>
       <c r="C46">
-        <v>666.3965056673337</v>
+        <v>609.4842825287149</v>
       </c>
       <c r="D46">
-        <v>1717.604505667334</v>
+        <v>1690.974282528715</v>
       </c>
       <c r="E46">
-        <v>484.1079999999999</v>
+        <v>514.3900000000001</v>
       </c>
       <c r="F46">
-        <v>1332.408</v>
+        <v>1362.69</v>
       </c>
       <c r="G46">
         <v>281.2</v>
@@ -5065,37 +5065,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M46">
-        <v>220.7233625671213</v>
+        <v>225.7398026254649</v>
       </c>
       <c r="N46">
-        <v>-16.95669590045458</v>
+        <v>-21.97313595879825</v>
       </c>
       <c r="O46">
-        <v>-5.087008770136372</v>
+        <v>-6.591940787639476</v>
       </c>
       <c r="P46">
-        <v>-11.8696871303182</v>
+        <v>-15.38119517115878</v>
       </c>
       <c r="Q46">
-        <v>-10.96968713031823</v>
+        <v>-14.4811951711588</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1053488594763585</v>
+        <v>0.1064315660122923</v>
       </c>
       <c r="T46">
-        <v>0.8665084634595041</v>
+        <v>0.8822631627951313</v>
       </c>
       <c r="U46">
         <v>0.1656574882221671</v>
       </c>
       <c r="V46">
-        <v>0.2769530116297071</v>
+        <v>0.2707985002601581</v>
       </c>
       <c r="W46">
-        <v>0.1197781479600252</v>
+        <v>0.1207976888547395</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.9231767054323572</v>
+        <v>0.9026616675338603</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1128963212913935</v>
+        <v>0.1140948961736152</v>
       </c>
       <c r="C47">
-        <v>609.4842825287149</v>
+        <v>553.3852169000354</v>
       </c>
       <c r="D47">
-        <v>1690.974282528715</v>
+        <v>1665.157216900035</v>
       </c>
       <c r="E47">
-        <v>514.3900000000001</v>
+        <v>544.672</v>
       </c>
       <c r="F47">
-        <v>1362.69</v>
+        <v>1392.972</v>
       </c>
       <c r="G47">
         <v>281.2</v>
@@ -5147,37 +5147,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M47">
-        <v>225.7398026254649</v>
+        <v>230.7562426838086</v>
       </c>
       <c r="N47">
-        <v>-21.97313595879825</v>
+        <v>-26.98957601714193</v>
       </c>
       <c r="O47">
-        <v>-6.591940787639476</v>
+        <v>-8.096872805142578</v>
       </c>
       <c r="P47">
-        <v>-15.38119517115878</v>
+        <v>-18.89270321199935</v>
       </c>
       <c r="Q47">
-        <v>-14.4811951711588</v>
+        <v>-17.99270321199937</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1064315660122923</v>
+        <v>0.1075543727902977</v>
       </c>
       <c r="T47">
-        <v>0.8822631627951313</v>
+        <v>0.8986013695135597</v>
       </c>
       <c r="U47">
         <v>0.1656574882221671</v>
       </c>
       <c r="V47">
-        <v>0.2707985002601581</v>
+        <v>0.264911576341459</v>
       </c>
       <c r="W47">
-        <v>0.1207976888547395</v>
+        <v>0.1217729018844662</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9026616675338603</v>
+        <v>0.8830385878048633</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1140948961736152</v>
+        <v>0.1152934710558369</v>
       </c>
       <c r="C48">
-        <v>553.3852169000354</v>
+        <v>498.0626240540159</v>
       </c>
       <c r="D48">
-        <v>1665.157216900035</v>
+        <v>1640.116624054016</v>
       </c>
       <c r="E48">
-        <v>544.672</v>
+        <v>574.954</v>
       </c>
       <c r="F48">
-        <v>1392.972</v>
+        <v>1423.254</v>
       </c>
       <c r="G48">
         <v>281.2</v>
@@ -5229,37 +5229,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M48">
-        <v>230.7562426838086</v>
+        <v>235.7726827421523</v>
       </c>
       <c r="N48">
-        <v>-26.98957601714193</v>
+        <v>-32.00601607548558</v>
       </c>
       <c r="O48">
-        <v>-8.096872805142578</v>
+        <v>-9.601804822645672</v>
       </c>
       <c r="P48">
-        <v>-18.89270321199935</v>
+        <v>-22.4042112528399</v>
       </c>
       <c r="Q48">
-        <v>-17.99270321199937</v>
+        <v>-21.50421125283993</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1075543727902977</v>
+        <v>0.1087195496353977</v>
       </c>
       <c r="T48">
-        <v>0.8986013695135597</v>
+        <v>0.9155561123345702</v>
       </c>
       <c r="U48">
         <v>0.1656574882221671</v>
       </c>
       <c r="V48">
-        <v>0.264911576341459</v>
+        <v>0.2592751598235556</v>
       </c>
       <c r="W48">
-        <v>0.1217729018844662</v>
+        <v>0.122706616487396</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8830385878048633</v>
+        <v>0.8642505327451855</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1152934710558369</v>
+        <v>0.1164920459380586</v>
       </c>
       <c r="C49">
-        <v>498.0626240540159</v>
+        <v>443.481993227429</v>
       </c>
       <c r="D49">
-        <v>1640.116624054016</v>
+        <v>1615.817993227429</v>
       </c>
       <c r="E49">
-        <v>574.954</v>
+        <v>605.2360000000001</v>
       </c>
       <c r="F49">
-        <v>1423.254</v>
+        <v>1453.536</v>
       </c>
       <c r="G49">
         <v>281.2</v>
@@ -5311,37 +5311,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M49">
-        <v>235.7726827421523</v>
+        <v>240.7891228004959</v>
       </c>
       <c r="N49">
-        <v>-32.00601607548558</v>
+        <v>-37.02245613382925</v>
       </c>
       <c r="O49">
-        <v>-9.601804822645672</v>
+        <v>-11.10673684014878</v>
       </c>
       <c r="P49">
-        <v>-22.4042112528399</v>
+        <v>-25.91571929368047</v>
       </c>
       <c r="Q49">
-        <v>-21.50421125283993</v>
+        <v>-25.0157192936805</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1087195496353977</v>
+        <v>0.1099295409745399</v>
       </c>
       <c r="T49">
-        <v>0.9155561123345702</v>
+        <v>0.9331629606486966</v>
       </c>
       <c r="U49">
         <v>0.1656574882221671</v>
       </c>
       <c r="V49">
-        <v>0.2592751598235556</v>
+        <v>0.2538735939938982</v>
       </c>
       <c r="W49">
-        <v>0.122706616487396</v>
+        <v>0.1236014263152037</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8642505327451855</v>
+        <v>0.846245313312994</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1164920459380585</v>
+        <v>0.1176906208202802</v>
       </c>
       <c r="C50">
-        <v>443.4819932274297</v>
+        <v>389.6108289336871</v>
       </c>
       <c r="D50">
-        <v>1615.817993227429</v>
+        <v>1592.228828933687</v>
       </c>
       <c r="E50">
-        <v>605.2359999999999</v>
+        <v>635.518</v>
       </c>
       <c r="F50">
-        <v>1453.536</v>
+        <v>1483.818</v>
       </c>
       <c r="G50">
         <v>281.2</v>
@@ -5393,37 +5393,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M50">
-        <v>240.7891228004959</v>
+        <v>245.8055628588396</v>
       </c>
       <c r="N50">
-        <v>-37.02245613382922</v>
+        <v>-42.03889619217293</v>
       </c>
       <c r="O50">
-        <v>-11.10673684014877</v>
+        <v>-12.61166885765188</v>
       </c>
       <c r="P50">
-        <v>-25.91571929368046</v>
+        <v>-29.42722733452105</v>
       </c>
       <c r="Q50">
-        <v>-25.01571929368048</v>
+        <v>-28.52722733452107</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1099295409745399</v>
+        <v>0.1111869829544329</v>
       </c>
       <c r="T50">
-        <v>0.9331629606486966</v>
+        <v>0.9514602736025927</v>
       </c>
       <c r="U50">
         <v>0.1656574882221671</v>
       </c>
       <c r="V50">
-        <v>0.2538735939938982</v>
+        <v>0.2486925002389207</v>
       </c>
       <c r="W50">
-        <v>0.1236014263152037</v>
+        <v>0.1244597132928968</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8462453133129941</v>
+        <v>0.8289750007964023</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1176906208202802</v>
+        <v>0.1188891957025019</v>
       </c>
       <c r="C51">
-        <v>389.6108289336871</v>
+        <v>336.4185059753931</v>
       </c>
       <c r="D51">
-        <v>1592.228828933687</v>
+        <v>1569.318505975393</v>
       </c>
       <c r="E51">
-        <v>635.518</v>
+        <v>665.8</v>
       </c>
       <c r="F51">
-        <v>1483.818</v>
+        <v>1514.1</v>
       </c>
       <c r="G51">
         <v>281.2</v>
@@ -5475,37 +5475,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M51">
-        <v>245.8055628588396</v>
+        <v>250.8220029171833</v>
       </c>
       <c r="N51">
-        <v>-42.03889619217293</v>
+        <v>-47.05533625051658</v>
       </c>
       <c r="O51">
-        <v>-12.61166885765188</v>
+        <v>-14.11660087515497</v>
       </c>
       <c r="P51">
-        <v>-29.42722733452105</v>
+        <v>-32.9387353753616</v>
       </c>
       <c r="Q51">
-        <v>-28.52722733452107</v>
+        <v>-32.03873537536163</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1111869829544329</v>
+        <v>0.1124947226135215</v>
       </c>
       <c r="T51">
-        <v>0.9514602736025927</v>
+        <v>0.9704894790746444</v>
       </c>
       <c r="U51">
         <v>0.1656574882221671</v>
       </c>
       <c r="V51">
-        <v>0.2486925002389207</v>
+        <v>0.2437186502341423</v>
       </c>
       <c r="W51">
-        <v>0.1244597132928968</v>
+        <v>0.1252836687914822</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8289750007964023</v>
+        <v>0.8123955007804743</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1188891957025019</v>
+        <v>0.1487654080771115</v>
       </c>
       <c r="C52">
-        <v>336.4185059753931</v>
+        <v>-108.1354826206812</v>
       </c>
       <c r="D52">
-        <v>1569.318505975393</v>
+        <v>1155.046517379319</v>
       </c>
       <c r="E52">
-        <v>665.8</v>
+        <v>696.0819999999999</v>
       </c>
       <c r="F52">
-        <v>1514.1</v>
+        <v>1544.382</v>
       </c>
       <c r="G52">
         <v>281.2</v>
@@ -5557,45 +5557,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M52">
-        <v>250.8220029171833</v>
+        <v>339.2350709755269</v>
       </c>
       <c r="N52">
-        <v>-47.05533625051658</v>
+        <v>-135.4684043088602</v>
       </c>
       <c r="O52">
-        <v>-14.11660087515497</v>
+        <v>-40.64052129265806</v>
       </c>
       <c r="P52">
-        <v>-32.9387353753616</v>
+        <v>-94.82788301620212</v>
       </c>
       <c r="Q52">
-        <v>-32.03873537536163</v>
+        <v>-93.92788301620214</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1124947226135215</v>
+        <v>0.1161775485696912</v>
       </c>
       <c r="T52">
-        <v>0.9704894790746444</v>
+        <v>1.024079084123861</v>
       </c>
       <c r="U52">
-        <v>0.1656574882221671</v>
+        <v>0.2196574882221671</v>
       </c>
       <c r="V52">
-        <v>0.2437186502341423</v>
+        <v>0.1801995289703111</v>
       </c>
       <c r="W52">
-        <v>0.1252836687914822</v>
+        <v>0.180075312309731</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8123955007804743</v>
+        <v>0.6006650965677037</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1487654080771115</v>
+        <v>0.1505039829593331</v>
       </c>
       <c r="C53">
-        <v>-108.1354826206812</v>
+        <v>-155.8926356321795</v>
       </c>
       <c r="D53">
-        <v>1155.046517379319</v>
+        <v>1137.57136436782</v>
       </c>
       <c r="E53">
-        <v>696.0819999999999</v>
+        <v>726.364</v>
       </c>
       <c r="F53">
-        <v>1544.382</v>
+        <v>1574.664</v>
       </c>
       <c r="G53">
         <v>281.2</v>
@@ -5639,37 +5639,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M53">
-        <v>339.2350709755269</v>
+        <v>345.8867390338706</v>
       </c>
       <c r="N53">
-        <v>-135.4684043088602</v>
+        <v>-142.1200723672039</v>
       </c>
       <c r="O53">
-        <v>-40.64052129265806</v>
+        <v>-42.63602171016117</v>
       </c>
       <c r="P53">
-        <v>-94.82788301620212</v>
+        <v>-99.48405065704273</v>
       </c>
       <c r="Q53">
-        <v>-93.92788301620214</v>
+        <v>-98.58405065704275</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1161775485696912</v>
+        <v>0.1176437474982265</v>
       </c>
       <c r="T53">
-        <v>1.024079084123861</v>
+        <v>1.045414065043109</v>
       </c>
       <c r="U53">
         <v>0.2196574882221671</v>
       </c>
       <c r="V53">
-        <v>0.1801995289703111</v>
+        <v>0.1767341534131897</v>
       </c>
       <c r="W53">
-        <v>0.180075312309731</v>
+        <v>0.1808365080003547</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.6006650965677037</v>
+        <v>0.5891138447106324</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1505039829593331</v>
+        <v>0.1522425578415548</v>
       </c>
       <c r="C54">
-        <v>-155.8926356321795</v>
+        <v>-203.1288925604974</v>
       </c>
       <c r="D54">
-        <v>1137.57136436782</v>
+        <v>1120.617107439502</v>
       </c>
       <c r="E54">
-        <v>726.364</v>
+        <v>756.646</v>
       </c>
       <c r="F54">
-        <v>1574.664</v>
+        <v>1604.946</v>
       </c>
       <c r="G54">
         <v>281.2</v>
@@ -5721,37 +5721,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M54">
-        <v>345.8867390338706</v>
+        <v>352.5384070922142</v>
       </c>
       <c r="N54">
-        <v>-142.1200723672039</v>
+        <v>-148.7717404255476</v>
       </c>
       <c r="O54">
-        <v>-42.63602171016117</v>
+        <v>-44.63152212766427</v>
       </c>
       <c r="P54">
-        <v>-99.48405065704273</v>
+        <v>-104.1402182978833</v>
       </c>
       <c r="Q54">
-        <v>-98.58405065704275</v>
+        <v>-103.2402182978833</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1176437474982265</v>
+        <v>0.1191723378705291</v>
       </c>
       <c r="T54">
-        <v>1.045414065043109</v>
+        <v>1.067656917490834</v>
       </c>
       <c r="U54">
         <v>0.2196574882221671</v>
       </c>
       <c r="V54">
-        <v>0.1767341534131897</v>
+        <v>0.1733995467450163</v>
       </c>
       <c r="W54">
-        <v>0.1808365080003547</v>
+        <v>0.1815689793252946</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5891138447106324</v>
+        <v>0.5779984891500545</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1522425578415548</v>
+        <v>0.1539811327237765</v>
       </c>
       <c r="C55">
-        <v>-203.1288925604974</v>
+        <v>-249.8672015477925</v>
       </c>
       <c r="D55">
-        <v>1120.617107439502</v>
+        <v>1104.160798452207</v>
       </c>
       <c r="E55">
-        <v>756.646</v>
+        <v>786.9280000000001</v>
       </c>
       <c r="F55">
-        <v>1604.946</v>
+        <v>1635.228</v>
       </c>
       <c r="G55">
         <v>281.2</v>
@@ -5803,37 +5803,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M55">
-        <v>352.5384070922142</v>
+        <v>359.1900751505579</v>
       </c>
       <c r="N55">
-        <v>-148.7717404255476</v>
+        <v>-155.4234084838912</v>
       </c>
       <c r="O55">
-        <v>-44.63152212766427</v>
+        <v>-46.62702254516736</v>
       </c>
       <c r="P55">
-        <v>-104.1402182978833</v>
+        <v>-108.7963859387239</v>
       </c>
       <c r="Q55">
-        <v>-103.2402182978833</v>
+        <v>-107.8963859387239</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1191723378705291</v>
+        <v>0.1207673886938015</v>
       </c>
       <c r="T55">
-        <v>1.067656917490834</v>
+        <v>1.090866850479765</v>
       </c>
       <c r="U55">
         <v>0.2196574882221671</v>
       </c>
       <c r="V55">
-        <v>0.1733995467450163</v>
+        <v>0.170188444027516</v>
       </c>
       <c r="W55">
-        <v>0.1815689793252946</v>
+        <v>0.1822743220826441</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5779984891500545</v>
+        <v>0.5672948134250535</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1539811327237765</v>
+        <v>0.1557197076059982</v>
       </c>
       <c r="C56">
-        <v>-249.8672015477925</v>
+        <v>-296.1291822671446</v>
       </c>
       <c r="D56">
-        <v>1104.160798452207</v>
+        <v>1088.180817732855</v>
       </c>
       <c r="E56">
-        <v>786.9280000000001</v>
+        <v>817.21</v>
       </c>
       <c r="F56">
-        <v>1635.228</v>
+        <v>1665.51</v>
       </c>
       <c r="G56">
         <v>281.2</v>
@@ -5885,37 +5885,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M56">
-        <v>359.1900751505579</v>
+        <v>365.8417432089016</v>
       </c>
       <c r="N56">
-        <v>-155.4234084838912</v>
+        <v>-162.0750765422349</v>
       </c>
       <c r="O56">
-        <v>-46.62702254516736</v>
+        <v>-48.62252296267047</v>
       </c>
       <c r="P56">
-        <v>-108.7963859387239</v>
+        <v>-113.4525535795644</v>
       </c>
       <c r="Q56">
-        <v>-107.8963859387239</v>
+        <v>-112.5525535795644</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1207673886938015</v>
+        <v>0.1224333306647749</v>
       </c>
       <c r="T56">
-        <v>1.090866850479765</v>
+        <v>1.115108336045982</v>
       </c>
       <c r="U56">
         <v>0.2196574882221671</v>
       </c>
       <c r="V56">
-        <v>0.170188444027516</v>
+        <v>0.1670941086815612</v>
       </c>
       <c r="W56">
-        <v>0.1822743220826441</v>
+        <v>0.1829540160124536</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5672948134250535</v>
+        <v>0.5569803622718708</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1557197076059982</v>
+        <v>0.1574582824882199</v>
       </c>
       <c r="C57">
-        <v>-296.1291822671446</v>
+        <v>-341.9352206825663</v>
       </c>
       <c r="D57">
-        <v>1088.180817732855</v>
+        <v>1072.656779317434</v>
       </c>
       <c r="E57">
-        <v>817.21</v>
+        <v>847.4920000000002</v>
       </c>
       <c r="F57">
-        <v>1665.51</v>
+        <v>1695.792</v>
       </c>
       <c r="G57">
         <v>281.2</v>
@@ -5967,37 +5967,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M57">
-        <v>365.8417432089016</v>
+        <v>372.4934112672453</v>
       </c>
       <c r="N57">
-        <v>-162.0750765422349</v>
+        <v>-168.7267446005786</v>
       </c>
       <c r="O57">
-        <v>-48.62252296267047</v>
+        <v>-50.61802338017358</v>
       </c>
       <c r="P57">
-        <v>-113.4525535795644</v>
+        <v>-118.108721220405</v>
       </c>
       <c r="Q57">
-        <v>-112.5525535795644</v>
+        <v>-117.208721220405</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1224333306647749</v>
+        <v>0.1241749972707925</v>
       </c>
       <c r="T57">
-        <v>1.115108336045982</v>
+        <v>1.140451707319755</v>
       </c>
       <c r="U57">
         <v>0.2196574882221671</v>
       </c>
       <c r="V57">
-        <v>0.1670941086815612</v>
+        <v>0.1641102853122476</v>
       </c>
       <c r="W57">
-        <v>0.1829540160124536</v>
+        <v>0.1836094351590556</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5569803622718708</v>
+        <v>0.5470342843741587</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1574582824882199</v>
+        <v>0.1591968573704415</v>
       </c>
       <c r="C58">
-        <v>-341.9352206825663</v>
+        <v>-387.3045558119945</v>
       </c>
       <c r="D58">
-        <v>1072.656779317434</v>
+        <v>1057.569444188005</v>
       </c>
       <c r="E58">
-        <v>847.4920000000002</v>
+        <v>877.7740000000001</v>
       </c>
       <c r="F58">
-        <v>1695.792</v>
+        <v>1726.074</v>
       </c>
       <c r="G58">
         <v>281.2</v>
@@ -6049,37 +6049,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M58">
-        <v>372.4934112672453</v>
+        <v>379.1450793255889</v>
       </c>
       <c r="N58">
-        <v>-168.7267446005786</v>
+        <v>-175.3784126589223</v>
       </c>
       <c r="O58">
-        <v>-50.61802338017358</v>
+        <v>-52.61352379767668</v>
       </c>
       <c r="P58">
-        <v>-118.108721220405</v>
+        <v>-122.7648888612456</v>
       </c>
       <c r="Q58">
-        <v>-117.208721220405</v>
+        <v>-121.8648888612456</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1241749972707925</v>
+        <v>0.1259976716259272</v>
       </c>
       <c r="T58">
-        <v>1.140451707319755</v>
+        <v>1.166973840048121</v>
       </c>
       <c r="U58">
         <v>0.2196574882221671</v>
       </c>
       <c r="V58">
-        <v>0.1641102853122476</v>
+        <v>0.161231157499752</v>
       </c>
       <c r="W58">
-        <v>0.1836094351590556</v>
+        <v>0.184241857142619</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5470342843741587</v>
+        <v>0.53743719166584</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1591968573704415</v>
+        <v>0.1609354322526632</v>
       </c>
       <c r="C59">
-        <v>-387.3045558119945</v>
+        <v>-432.2553592697095</v>
       </c>
       <c r="D59">
-        <v>1057.569444188005</v>
+        <v>1042.900640730291</v>
       </c>
       <c r="E59">
-        <v>877.7740000000001</v>
+        <v>908.0560000000003</v>
       </c>
       <c r="F59">
-        <v>1726.074</v>
+        <v>1756.356</v>
       </c>
       <c r="G59">
         <v>281.2</v>
@@ -6131,37 +6131,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M59">
-        <v>379.1450793255889</v>
+        <v>385.7967473839326</v>
       </c>
       <c r="N59">
-        <v>-175.3784126589223</v>
+        <v>-182.0300807172659</v>
       </c>
       <c r="O59">
-        <v>-52.61352379767668</v>
+        <v>-54.60902421517977</v>
       </c>
       <c r="P59">
-        <v>-122.7648888612456</v>
+        <v>-127.4210565020861</v>
       </c>
       <c r="Q59">
-        <v>-121.8648888612456</v>
+        <v>-126.5210565020862</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1259976716259272</v>
+        <v>0.1279071399979731</v>
       </c>
       <c r="T59">
-        <v>1.166973840048121</v>
+        <v>1.194758931477838</v>
       </c>
       <c r="U59">
         <v>0.2196574882221671</v>
       </c>
       <c r="V59">
-        <v>0.161231157499752</v>
+        <v>0.1584513099566529</v>
       </c>
       <c r="W59">
-        <v>0.184241857142619</v>
+        <v>0.1848524714715767</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.53743719166584</v>
+        <v>0.5281710331888428</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1609354322526632</v>
+        <v>0.1626740071348848</v>
       </c>
       <c r="C60">
-        <v>-432.2553592697088</v>
+        <v>-476.8048082796538</v>
       </c>
       <c r="D60">
-        <v>1042.900640730291</v>
+        <v>1028.633191720346</v>
       </c>
       <c r="E60">
-        <v>908.0559999999998</v>
+        <v>938.3379999999997</v>
       </c>
       <c r="F60">
-        <v>1756.356</v>
+        <v>1786.638</v>
       </c>
       <c r="G60">
         <v>281.2</v>
@@ -6213,37 +6213,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M60">
-        <v>385.7967473839325</v>
+        <v>392.4484154422761</v>
       </c>
       <c r="N60">
-        <v>-182.0300807172659</v>
+        <v>-188.6817487756095</v>
       </c>
       <c r="O60">
-        <v>-54.60902421517976</v>
+        <v>-56.60452463268284</v>
       </c>
       <c r="P60">
-        <v>-127.4210565020861</v>
+        <v>-132.0772241429266</v>
       </c>
       <c r="Q60">
-        <v>-126.5210565020861</v>
+        <v>-131.1772241429267</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1279071399979731</v>
+        <v>0.1299097531686554</v>
       </c>
       <c r="T60">
-        <v>1.194758931477838</v>
+        <v>1.2238993932212</v>
       </c>
       <c r="U60">
         <v>0.2196574882221671</v>
       </c>
       <c r="V60">
-        <v>0.1584513099566529</v>
+        <v>0.1557656945336588</v>
       </c>
       <c r="W60">
-        <v>0.1848524714715767</v>
+        <v>0.1854423870097223</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.528171033188843</v>
+        <v>0.5192189817788626</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1626740071348848</v>
+        <v>0.1644125820171065</v>
       </c>
       <c r="C61">
-        <v>-476.8048082796538</v>
+        <v>-520.9691527764626</v>
       </c>
       <c r="D61">
-        <v>1028.633191720346</v>
+        <v>1014.750847223537</v>
       </c>
       <c r="E61">
-        <v>938.3379999999997</v>
+        <v>968.6199999999999</v>
       </c>
       <c r="F61">
-        <v>1786.638</v>
+        <v>1816.92</v>
       </c>
       <c r="G61">
         <v>281.2</v>
@@ -6295,37 +6295,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M61">
-        <v>392.4484154422761</v>
+        <v>399.1000835006199</v>
       </c>
       <c r="N61">
-        <v>-188.6817487756095</v>
+        <v>-195.3334168339532</v>
       </c>
       <c r="O61">
-        <v>-56.60452463268284</v>
+        <v>-58.60002505018595</v>
       </c>
       <c r="P61">
-        <v>-132.0772241429266</v>
+        <v>-136.7333917837672</v>
       </c>
       <c r="Q61">
-        <v>-131.1772241429267</v>
+        <v>-135.8333917837672</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1299097531686554</v>
+        <v>0.1320124969978717</v>
       </c>
       <c r="T61">
-        <v>1.2238993932212</v>
+        <v>1.25449687805173</v>
       </c>
       <c r="U61">
         <v>0.2196574882221671</v>
       </c>
       <c r="V61">
-        <v>0.1557656945336588</v>
+        <v>0.1531695996247645</v>
       </c>
       <c r="W61">
-        <v>0.1854423870097223</v>
+        <v>0.1860126386965964</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5192189817788626</v>
+        <v>0.5105653320825482</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1644125820171065</v>
+        <v>0.1661511568993282</v>
       </c>
       <c r="C62">
-        <v>-520.9691527764626</v>
+        <v>-564.7637771453053</v>
       </c>
       <c r="D62">
-        <v>1014.750847223537</v>
+        <v>1001.238222854694</v>
       </c>
       <c r="E62">
-        <v>968.6199999999999</v>
+        <v>998.9019999999998</v>
       </c>
       <c r="F62">
-        <v>1816.92</v>
+        <v>1847.202</v>
       </c>
       <c r="G62">
         <v>281.2</v>
@@ -6377,37 +6377,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M62">
-        <v>399.1000835006199</v>
+        <v>405.7517515589635</v>
       </c>
       <c r="N62">
-        <v>-195.3334168339532</v>
+        <v>-201.9850848922968</v>
       </c>
       <c r="O62">
-        <v>-58.60002505018595</v>
+        <v>-60.59552546768905</v>
       </c>
       <c r="P62">
-        <v>-136.7333917837672</v>
+        <v>-141.3895594246078</v>
       </c>
       <c r="Q62">
-        <v>-135.8333917837672</v>
+        <v>-140.4895594246078</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1320124969978717</v>
+        <v>0.134223073843971</v>
       </c>
       <c r="T62">
-        <v>1.25449687805173</v>
+        <v>1.286663464668441</v>
       </c>
       <c r="U62">
         <v>0.2196574882221671</v>
       </c>
       <c r="V62">
-        <v>0.1531695996247645</v>
+        <v>0.1506586225817355</v>
       </c>
       <c r="W62">
-        <v>0.1860126386965964</v>
+        <v>0.1865641936068516</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5105653320825482</v>
+        <v>0.5021954086057852</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1661511568993282</v>
+        <v>0.1900693910070264</v>
       </c>
       <c r="C63">
-        <v>-564.7637771453053</v>
+        <v>-750.0689852140624</v>
       </c>
       <c r="D63">
-        <v>1001.238222854694</v>
+        <v>846.2150147859376</v>
       </c>
       <c r="E63">
-        <v>998.9019999999998</v>
+        <v>1029.184</v>
       </c>
       <c r="F63">
-        <v>1847.202</v>
+        <v>1877.484</v>
       </c>
       <c r="G63">
         <v>281.2</v>
@@ -6459,45 +6459,45 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M63">
-        <v>405.7517515589635</v>
+        <v>478.1153596173071</v>
       </c>
       <c r="N63">
-        <v>-201.9850848922968</v>
+        <v>-274.3486929506405</v>
       </c>
       <c r="O63">
-        <v>-60.59552546768905</v>
+        <v>-82.30460788519214</v>
       </c>
       <c r="P63">
-        <v>-141.3895594246078</v>
+        <v>-192.0440850654484</v>
       </c>
       <c r="Q63">
-        <v>-140.4895594246078</v>
+        <v>-191.1440850654484</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.134223073843971</v>
+        <v>0.1378122579595401</v>
       </c>
       <c r="T63">
-        <v>1.286663464668441</v>
+        <v>1.338890466837807</v>
       </c>
       <c r="U63">
-        <v>0.2196574882221671</v>
+        <v>0.2546574882221671</v>
       </c>
       <c r="V63">
-        <v>0.1506586225817355</v>
+        <v>0.127856172721432</v>
       </c>
       <c r="W63">
-        <v>0.1865641936068516</v>
+        <v>0.2220979564232277</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5021954086057852</v>
+        <v>0.4261872424047733</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1900693910070264</v>
+        <v>0.1921579658892481</v>
       </c>
       <c r="C64">
-        <v>-750.0689852140624</v>
+        <v>-791.6392865498017</v>
       </c>
       <c r="D64">
-        <v>846.2150147859376</v>
+        <v>834.9267134501982</v>
       </c>
       <c r="E64">
-        <v>1029.184</v>
+        <v>1059.466</v>
       </c>
       <c r="F64">
-        <v>1877.484</v>
+        <v>1907.766</v>
       </c>
       <c r="G64">
         <v>281.2</v>
@@ -6541,37 +6541,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M64">
-        <v>478.1153596173071</v>
+        <v>485.8268976756508</v>
       </c>
       <c r="N64">
-        <v>-274.3486929506405</v>
+        <v>-282.0602310089841</v>
       </c>
       <c r="O64">
-        <v>-82.30460788519214</v>
+        <v>-84.61806930269525</v>
       </c>
       <c r="P64">
-        <v>-192.0440850654484</v>
+        <v>-197.4421617062889</v>
       </c>
       <c r="Q64">
-        <v>-191.1440850654484</v>
+        <v>-196.5421617062889</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1378122579595401</v>
+        <v>0.1402990757422304</v>
       </c>
       <c r="T64">
-        <v>1.338890466837807</v>
+        <v>1.375076695671261</v>
       </c>
       <c r="U64">
         <v>0.2546574882221671</v>
       </c>
       <c r="V64">
-        <v>0.127856172721432</v>
+        <v>0.1258267096623616</v>
       </c>
       <c r="W64">
-        <v>0.2220979564232277</v>
+        <v>0.2226147743882902</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4261872424047733</v>
+        <v>0.4194223655412055</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1921579658892481</v>
+        <v>0.1942465407714697</v>
       </c>
       <c r="C65">
-        <v>-791.6392865498017</v>
+        <v>-832.9123861263161</v>
       </c>
       <c r="D65">
-        <v>834.9267134501982</v>
+        <v>823.935613873684</v>
       </c>
       <c r="E65">
-        <v>1059.466</v>
+        <v>1089.748</v>
       </c>
       <c r="F65">
-        <v>1907.766</v>
+        <v>1938.048</v>
       </c>
       <c r="G65">
         <v>281.2</v>
@@ -6623,37 +6623,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M65">
-        <v>485.8268976756508</v>
+        <v>493.5384357339945</v>
       </c>
       <c r="N65">
-        <v>-282.0602310089841</v>
+        <v>-289.7717690673278</v>
       </c>
       <c r="O65">
-        <v>-84.61806930269525</v>
+        <v>-86.93153072019834</v>
       </c>
       <c r="P65">
-        <v>-197.4421617062889</v>
+        <v>-202.8402383471295</v>
       </c>
       <c r="Q65">
-        <v>-196.5421617062889</v>
+        <v>-201.9402383471295</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1402990757422304</v>
+        <v>0.1429240500684034</v>
       </c>
       <c r="T65">
-        <v>1.375076695671261</v>
+        <v>1.413273270551018</v>
       </c>
       <c r="U65">
         <v>0.2546574882221671</v>
       </c>
       <c r="V65">
-        <v>0.1258267096623616</v>
+        <v>0.1238606673238873</v>
       </c>
       <c r="W65">
-        <v>0.2226147743882902</v>
+        <v>0.2231154417919445</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4194223655412055</v>
+        <v>0.4128688910796242</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1942465407714697</v>
+        <v>0.1963351156536914</v>
       </c>
       <c r="C66">
-        <v>-832.9123861263161</v>
+        <v>-873.8998686652396</v>
       </c>
       <c r="D66">
-        <v>823.935613873684</v>
+        <v>813.2301313347602</v>
       </c>
       <c r="E66">
-        <v>1089.748</v>
+        <v>1120.03</v>
       </c>
       <c r="F66">
-        <v>1938.048</v>
+        <v>1968.33</v>
       </c>
       <c r="G66">
         <v>281.2</v>
@@ -6705,37 +6705,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M66">
-        <v>493.5384357339945</v>
+        <v>501.2499737923382</v>
       </c>
       <c r="N66">
-        <v>-289.7717690673278</v>
+        <v>-297.4833071256714</v>
       </c>
       <c r="O66">
-        <v>-86.93153072019834</v>
+        <v>-89.24499213770143</v>
       </c>
       <c r="P66">
-        <v>-202.8402383471295</v>
+        <v>-208.23831498797</v>
       </c>
       <c r="Q66">
-        <v>-201.9402383471295</v>
+        <v>-207.33831498797</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1429240500684034</v>
+        <v>0.1456990229275007</v>
       </c>
       <c r="T66">
-        <v>1.413273270551018</v>
+        <v>1.453652506852476</v>
       </c>
       <c r="U66">
         <v>0.2546574882221671</v>
       </c>
       <c r="V66">
-        <v>0.1238606673238873</v>
+        <v>0.1219551185958274</v>
       </c>
       <c r="W66">
-        <v>0.2231154417919445</v>
+        <v>0.2236007040447172</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4128688910796242</v>
+        <v>0.4065170619860916</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1963351156536914</v>
+        <v>0.1984236905359131</v>
       </c>
       <c r="C67">
-        <v>-873.8998686652396</v>
+        <v>-914.6127245247828</v>
       </c>
       <c r="D67">
-        <v>813.2301313347602</v>
+        <v>802.7992754752172</v>
       </c>
       <c r="E67">
-        <v>1120.03</v>
+        <v>1150.312</v>
       </c>
       <c r="F67">
-        <v>1968.33</v>
+        <v>1998.612</v>
       </c>
       <c r="G67">
         <v>281.2</v>
@@ -6787,37 +6787,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M67">
-        <v>501.2499737923382</v>
+        <v>508.9615118506819</v>
       </c>
       <c r="N67">
-        <v>-297.4833071256714</v>
+        <v>-305.1948451840152</v>
       </c>
       <c r="O67">
-        <v>-89.24499213770143</v>
+        <v>-91.55845355520457</v>
       </c>
       <c r="P67">
-        <v>-208.23831498797</v>
+        <v>-213.6363916288107</v>
       </c>
       <c r="Q67">
-        <v>-207.33831498797</v>
+        <v>-212.7363916288107</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1456990229275007</v>
+        <v>0.1486372294841919</v>
       </c>
       <c r="T67">
-        <v>1.453652506852476</v>
+        <v>1.496406992348137</v>
       </c>
       <c r="U67">
         <v>0.2546574882221671</v>
       </c>
       <c r="V67">
-        <v>0.1219551185958274</v>
+        <v>0.1201073137686179</v>
       </c>
       <c r="W67">
-        <v>0.2236007040447172</v>
+        <v>0.2240712613807392</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4065170619860916</v>
+        <v>0.4003577125620598</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1984236905359131</v>
+        <v>0.2005122654181347</v>
       </c>
       <c r="C68">
-        <v>-914.6127245247828</v>
+        <v>-955.0613873348696</v>
       </c>
       <c r="D68">
-        <v>802.7992754752172</v>
+        <v>792.6326126651304</v>
       </c>
       <c r="E68">
-        <v>1150.312</v>
+        <v>1180.594</v>
       </c>
       <c r="F68">
-        <v>1998.612</v>
+        <v>2028.894</v>
       </c>
       <c r="G68">
         <v>281.2</v>
@@ -6869,37 +6869,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M68">
-        <v>508.9615118506819</v>
+        <v>516.6730499090255</v>
       </c>
       <c r="N68">
-        <v>-305.1948451840152</v>
+        <v>-312.9063832423589</v>
       </c>
       <c r="O68">
-        <v>-91.55845355520457</v>
+        <v>-93.87191497270766</v>
       </c>
       <c r="P68">
-        <v>-213.6363916288107</v>
+        <v>-219.0344682696512</v>
       </c>
       <c r="Q68">
-        <v>-212.7363916288107</v>
+        <v>-218.1344682696512</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1486372294841919</v>
+        <v>0.1517535091655311</v>
       </c>
       <c r="T68">
-        <v>1.496406992348137</v>
+        <v>1.54175265878293</v>
       </c>
       <c r="U68">
         <v>0.2546574882221671</v>
       </c>
       <c r="V68">
-        <v>0.1201073137686179</v>
+        <v>0.1183146672944595</v>
       </c>
       <c r="W68">
-        <v>0.2240712613807392</v>
+        <v>0.2245277722291187</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4003577125620598</v>
+        <v>0.3943822243148648</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2005122654181347</v>
+        <v>0.2026008403003564</v>
       </c>
       <c r="C69">
-        <v>-955.0613873348696</v>
+        <v>-995.2557688083677</v>
       </c>
       <c r="D69">
-        <v>792.6326126651304</v>
+        <v>782.7202311916321</v>
       </c>
       <c r="E69">
-        <v>1180.594</v>
+        <v>1210.876</v>
       </c>
       <c r="F69">
-        <v>2028.894</v>
+        <v>2059.176</v>
       </c>
       <c r="G69">
         <v>281.2</v>
@@ -6951,37 +6951,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M69">
-        <v>516.6730499090255</v>
+        <v>524.3845879673692</v>
       </c>
       <c r="N69">
-        <v>-312.9063832423589</v>
+        <v>-320.6179213007025</v>
       </c>
       <c r="O69">
-        <v>-93.87191497270766</v>
+        <v>-96.18537639021075</v>
       </c>
       <c r="P69">
-        <v>-219.0344682696512</v>
+        <v>-224.4325449104917</v>
       </c>
       <c r="Q69">
-        <v>-218.1344682696512</v>
+        <v>-223.5325449104918</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1517535091655311</v>
+        <v>0.1550645563269539</v>
       </c>
       <c r="T69">
-        <v>1.54175265878293</v>
+        <v>1.589932429369896</v>
       </c>
       <c r="U69">
         <v>0.2546574882221671</v>
       </c>
       <c r="V69">
-        <v>0.1183146672944595</v>
+        <v>0.1165747457165998</v>
       </c>
       <c r="W69">
-        <v>0.2245277722291187</v>
+        <v>0.22497085628784</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3943822243148648</v>
+        <v>0.3885824857219992</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2026008403003564</v>
+        <v>0.2046894151825781</v>
       </c>
       <c r="C70">
-        <v>-995.2557688083677</v>
+        <v>-1035.20529097256</v>
       </c>
       <c r="D70">
-        <v>782.7202311916321</v>
+        <v>773.0527090274405</v>
       </c>
       <c r="E70">
-        <v>1210.876</v>
+        <v>1241.158</v>
       </c>
       <c r="F70">
-        <v>2059.176</v>
+        <v>2089.458</v>
       </c>
       <c r="G70">
         <v>281.2</v>
@@ -7033,37 +7033,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M70">
-        <v>524.3845879673692</v>
+        <v>532.0961260257128</v>
       </c>
       <c r="N70">
-        <v>-320.6179213007025</v>
+        <v>-328.3294593590462</v>
       </c>
       <c r="O70">
-        <v>-96.18537639021075</v>
+        <v>-98.49883780771384</v>
       </c>
       <c r="P70">
-        <v>-224.4325449104917</v>
+        <v>-229.8306215513323</v>
       </c>
       <c r="Q70">
-        <v>-223.5325449104918</v>
+        <v>-228.9306215513323</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1550645563269539</v>
+        <v>0.158589219434275</v>
       </c>
       <c r="T70">
-        <v>1.589932429369896</v>
+        <v>1.641220572252796</v>
       </c>
       <c r="U70">
         <v>0.2546574882221671</v>
       </c>
       <c r="V70">
-        <v>0.1165747457165998</v>
+        <v>0.1148852566482433</v>
       </c>
       <c r="W70">
-        <v>0.22497085628784</v>
+        <v>0.2254010973303665</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3885824857219992</v>
+        <v>0.3829508554941441</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2046894151825781</v>
+        <v>0.2067779900647998</v>
       </c>
       <c r="C71">
-        <v>-1035.20529097256</v>
+        <v>-1074.918916041171</v>
       </c>
       <c r="D71">
-        <v>773.0527090274405</v>
+        <v>763.6210839588294</v>
       </c>
       <c r="E71">
-        <v>1241.158</v>
+        <v>1271.44</v>
       </c>
       <c r="F71">
-        <v>2089.458</v>
+        <v>2119.74</v>
       </c>
       <c r="G71">
         <v>281.2</v>
@@ -7115,37 +7115,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M71">
-        <v>532.0961260257128</v>
+        <v>539.8076640840566</v>
       </c>
       <c r="N71">
-        <v>-328.3294593590462</v>
+        <v>-336.0409974173899</v>
       </c>
       <c r="O71">
-        <v>-98.49883780771384</v>
+        <v>-100.812299225217</v>
       </c>
       <c r="P71">
-        <v>-229.8306215513323</v>
+        <v>-235.2286981921729</v>
       </c>
       <c r="Q71">
-        <v>-228.9306215513323</v>
+        <v>-234.328698192173</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.158589219434275</v>
+        <v>0.1623488600820842</v>
       </c>
       <c r="T71">
-        <v>1.641220572252796</v>
+        <v>1.695927924661222</v>
       </c>
       <c r="U71">
         <v>0.2546574882221671</v>
       </c>
       <c r="V71">
-        <v>0.1148852566482433</v>
+        <v>0.1132440386961255</v>
       </c>
       <c r="W71">
-        <v>0.2254010973303665</v>
+        <v>0.2258190457716779</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3829508554941441</v>
+        <v>0.3774801289870848</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2067779900647998</v>
+        <v>0.2088665649470215</v>
       </c>
       <c r="C72">
-        <v>-1074.918916041171</v>
+        <v>-1114.405174126039</v>
       </c>
       <c r="D72">
-        <v>763.6210839588294</v>
+        <v>754.4168258739613</v>
       </c>
       <c r="E72">
-        <v>1271.44</v>
+        <v>1301.722</v>
       </c>
       <c r="F72">
-        <v>2119.74</v>
+        <v>2150.022</v>
       </c>
       <c r="G72">
         <v>281.2</v>
@@ -7197,37 +7197,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M72">
-        <v>539.8076640840566</v>
+        <v>547.5192021424001</v>
       </c>
       <c r="N72">
-        <v>-336.0409974173899</v>
+        <v>-343.7525354757335</v>
       </c>
       <c r="O72">
-        <v>-100.812299225217</v>
+        <v>-103.12576064272</v>
       </c>
       <c r="P72">
-        <v>-235.2286981921729</v>
+        <v>-240.6267748330134</v>
       </c>
       <c r="Q72">
-        <v>-234.328698192173</v>
+        <v>-239.7267748330135</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1623488600820842</v>
+        <v>0.1663677862918112</v>
       </c>
       <c r="T72">
-        <v>1.695927924661222</v>
+        <v>1.754408197925403</v>
       </c>
       <c r="U72">
         <v>0.2546574882221671</v>
       </c>
       <c r="V72">
-        <v>0.1132440386961255</v>
+        <v>0.1116490522356167</v>
       </c>
       <c r="W72">
-        <v>0.2258190457716779</v>
+        <v>0.2262252210174594</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3774801289870848</v>
+        <v>0.3721635074520556</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2088665649470214</v>
+        <v>0.2109551398292431</v>
       </c>
       <c r="C73">
-        <v>-1114.405174126038</v>
+        <v>-1153.672188968523</v>
       </c>
       <c r="D73">
-        <v>754.4168258739616</v>
+        <v>745.431811031477</v>
       </c>
       <c r="E73">
-        <v>1301.722</v>
+        <v>1332.004</v>
       </c>
       <c r="F73">
-        <v>2150.022</v>
+        <v>2180.304</v>
       </c>
       <c r="G73">
         <v>281.2</v>
@@ -7279,37 +7279,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M73">
-        <v>547.5192021424001</v>
+        <v>555.2307402007438</v>
       </c>
       <c r="N73">
-        <v>-343.7525354757335</v>
+        <v>-351.4640735340771</v>
       </c>
       <c r="O73">
-        <v>-103.12576064272</v>
+        <v>-105.4392220602231</v>
       </c>
       <c r="P73">
-        <v>-240.6267748330134</v>
+        <v>-246.024851473854</v>
       </c>
       <c r="Q73">
-        <v>-239.7267748330135</v>
+        <v>-245.124851473854</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1663677862918112</v>
+        <v>0.1706737786593759</v>
       </c>
       <c r="T73">
-        <v>1.754408197925402</v>
+        <v>1.817065633565595</v>
       </c>
       <c r="U73">
         <v>0.2546574882221671</v>
       </c>
       <c r="V73">
-        <v>0.1116490522356167</v>
+        <v>0.1100983709545665</v>
       </c>
       <c r="W73">
-        <v>0.2262252210174594</v>
+        <v>0.2266201136175248</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3721635074520556</v>
+        <v>0.3669945698485548</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2109551398292431</v>
+        <v>0.2130437147114648</v>
       </c>
       <c r="C74">
-        <v>-1153.672188968523</v>
+        <v>-1192.72770185381</v>
       </c>
       <c r="D74">
-        <v>745.431811031477</v>
+        <v>736.6582981461897</v>
       </c>
       <c r="E74">
-        <v>1332.004</v>
+        <v>1362.286</v>
       </c>
       <c r="F74">
-        <v>2180.304</v>
+        <v>2210.586</v>
       </c>
       <c r="G74">
         <v>281.2</v>
@@ -7361,37 +7361,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M74">
-        <v>555.2307402007438</v>
+        <v>562.9422782590874</v>
       </c>
       <c r="N74">
-        <v>-351.4640735340771</v>
+        <v>-359.1756115924208</v>
       </c>
       <c r="O74">
-        <v>-105.4392220602231</v>
+        <v>-107.7526834777262</v>
       </c>
       <c r="P74">
-        <v>-246.024851473854</v>
+        <v>-251.4229281146945</v>
       </c>
       <c r="Q74">
-        <v>-245.124851473854</v>
+        <v>-250.5229281146945</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1706737786593759</v>
+        <v>0.1752987334245379</v>
       </c>
       <c r="T74">
-        <v>1.817065633565595</v>
+        <v>1.884364360734691</v>
       </c>
       <c r="U74">
         <v>0.2546574882221671</v>
       </c>
       <c r="V74">
-        <v>0.1100983709545665</v>
+        <v>0.1085901740921751</v>
       </c>
       <c r="W74">
-        <v>0.2266201136175248</v>
+        <v>0.2270041872422459</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3669945698485548</v>
+        <v>0.3619672469739171</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2130437147114648</v>
+        <v>0.2151322895936865</v>
       </c>
       <c r="C75">
-        <v>-1192.72770185381</v>
+        <v>-1231.579093856077</v>
       </c>
       <c r="D75">
-        <v>736.6582981461897</v>
+        <v>728.0889061439226</v>
       </c>
       <c r="E75">
-        <v>1362.286</v>
+        <v>1392.568</v>
       </c>
       <c r="F75">
-        <v>2210.586</v>
+        <v>2240.868</v>
       </c>
       <c r="G75">
         <v>281.2</v>
@@ -7443,37 +7443,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M75">
-        <v>562.9422782590874</v>
+        <v>570.6538163174312</v>
       </c>
       <c r="N75">
-        <v>-359.1756115924208</v>
+        <v>-366.8871496507645</v>
       </c>
       <c r="O75">
-        <v>-107.7526834777262</v>
+        <v>-110.0661448952294</v>
       </c>
       <c r="P75">
-        <v>-251.4229281146945</v>
+        <v>-256.8210047555352</v>
       </c>
       <c r="Q75">
-        <v>-250.5229281146945</v>
+        <v>-255.9210047555352</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1752987334245379</v>
+        <v>0.1802794539408663</v>
       </c>
       <c r="T75">
-        <v>1.884364360734691</v>
+        <v>1.956839913070641</v>
       </c>
       <c r="U75">
         <v>0.2546574882221671</v>
       </c>
       <c r="V75">
-        <v>0.1085901740921751</v>
+        <v>0.1071227393071457</v>
       </c>
       <c r="W75">
-        <v>0.2270041872422459</v>
+        <v>0.2273778804987314</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3619672469739171</v>
+        <v>0.3570757976904857</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2151322895936865</v>
+        <v>0.2172208644759081</v>
       </c>
       <c r="C76">
-        <v>-1231.579093856077</v>
+        <v>-1270.233406548868</v>
       </c>
       <c r="D76">
-        <v>728.0889061439226</v>
+        <v>719.716593451132</v>
       </c>
       <c r="E76">
-        <v>1392.568</v>
+        <v>1422.85</v>
       </c>
       <c r="F76">
-        <v>2240.868</v>
+        <v>2271.15</v>
       </c>
       <c r="G76">
         <v>281.2</v>
@@ -7525,37 +7525,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M76">
-        <v>570.6538163174312</v>
+        <v>578.3653543757747</v>
       </c>
       <c r="N76">
-        <v>-366.8871496507645</v>
+        <v>-374.598687709108</v>
       </c>
       <c r="O76">
-        <v>-110.0661448952294</v>
+        <v>-112.3796063127324</v>
       </c>
       <c r="P76">
-        <v>-256.8210047555352</v>
+        <v>-262.2190813963757</v>
       </c>
       <c r="Q76">
-        <v>-255.9210047555352</v>
+        <v>-261.3190813963757</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1802794539408663</v>
+        <v>0.185658632098501</v>
       </c>
       <c r="T76">
-        <v>1.956839913070641</v>
+        <v>2.035113509593466</v>
       </c>
       <c r="U76">
         <v>0.2546574882221671</v>
       </c>
       <c r="V76">
-        <v>0.1071227393071457</v>
+        <v>0.1056944361163838</v>
       </c>
       <c r="W76">
-        <v>0.2273778804987314</v>
+        <v>0.2277416086017105</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3570757976904857</v>
+        <v>0.3523147870546126</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2172208644759081</v>
+        <v>0.2193094393581298</v>
       </c>
       <c r="C77">
-        <v>-1270.233406548868</v>
+        <v>-1308.697361302821</v>
       </c>
       <c r="D77">
-        <v>719.716593451132</v>
+        <v>711.5346386971784</v>
       </c>
       <c r="E77">
-        <v>1422.85</v>
+        <v>1453.132</v>
       </c>
       <c r="F77">
-        <v>2271.15</v>
+        <v>2301.432</v>
       </c>
       <c r="G77">
         <v>281.2</v>
@@ -7607,37 +7607,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M77">
-        <v>578.3653543757747</v>
+        <v>586.0768924341185</v>
       </c>
       <c r="N77">
-        <v>-374.598687709108</v>
+        <v>-382.3102257674518</v>
       </c>
       <c r="O77">
-        <v>-112.3796063127324</v>
+        <v>-114.6930677302355</v>
       </c>
       <c r="P77">
-        <v>-262.2190813963757</v>
+        <v>-267.6171580372163</v>
       </c>
       <c r="Q77">
-        <v>-261.3190813963757</v>
+        <v>-266.7171580372163</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.185658632098501</v>
+        <v>0.1914860751026052</v>
       </c>
       <c r="T77">
-        <v>2.035113509593466</v>
+        <v>2.119909905826528</v>
       </c>
       <c r="U77">
         <v>0.2546574882221671</v>
       </c>
       <c r="V77">
-        <v>0.1056944361163838</v>
+        <v>0.1043037198516945</v>
       </c>
       <c r="W77">
-        <v>0.2277416086017105</v>
+        <v>0.228095764912506</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3523147870546126</v>
+        <v>0.347679066172315</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2193094393581298</v>
+        <v>0.2213980142403515</v>
       </c>
       <c r="C78">
-        <v>-1308.697361302821</v>
+        <v>-1346.977377281898</v>
       </c>
       <c r="D78">
-        <v>711.5346386971784</v>
+        <v>703.5366227181023</v>
       </c>
       <c r="E78">
-        <v>1453.132</v>
+        <v>1483.414</v>
       </c>
       <c r="F78">
-        <v>2301.432</v>
+        <v>2331.714</v>
       </c>
       <c r="G78">
         <v>281.2</v>
@@ -7689,37 +7689,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M78">
-        <v>586.0768924341185</v>
+        <v>593.7884304924621</v>
       </c>
       <c r="N78">
-        <v>-382.3102257674518</v>
+        <v>-390.0217638257955</v>
       </c>
       <c r="O78">
-        <v>-114.6930677302355</v>
+        <v>-117.0065291477386</v>
       </c>
       <c r="P78">
-        <v>-267.6171580372163</v>
+        <v>-273.0152346780568</v>
       </c>
       <c r="Q78">
-        <v>-266.7171580372163</v>
+        <v>-272.1152346780568</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1914860751026052</v>
+        <v>0.1978202522809793</v>
       </c>
       <c r="T78">
-        <v>2.119909905826528</v>
+        <v>2.212079901732029</v>
       </c>
       <c r="U78">
         <v>0.2546574882221671</v>
       </c>
       <c r="V78">
-        <v>0.1043037198516945</v>
+        <v>0.1029491260873868</v>
       </c>
       <c r="W78">
-        <v>0.228095764912506</v>
+        <v>0.228440722358086</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.347679066172315</v>
+        <v>0.3431637536246227</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2213980142403515</v>
+        <v>0.2234865891225732</v>
       </c>
       <c r="C79">
-        <v>-1346.977377281898</v>
+        <v>-1385.079588239379</v>
       </c>
       <c r="D79">
-        <v>703.5366227181023</v>
+        <v>695.7164117606212</v>
       </c>
       <c r="E79">
-        <v>1483.414</v>
+        <v>1513.696</v>
       </c>
       <c r="F79">
-        <v>2331.714</v>
+        <v>2361.996</v>
       </c>
       <c r="G79">
         <v>281.2</v>
@@ -7771,37 +7771,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M79">
-        <v>593.7884304924621</v>
+        <v>601.4999685508059</v>
       </c>
       <c r="N79">
-        <v>-390.0217638257955</v>
+        <v>-397.7333018841392</v>
       </c>
       <c r="O79">
-        <v>-117.0065291477386</v>
+        <v>-119.3199905652418</v>
       </c>
       <c r="P79">
-        <v>-273.0152346780568</v>
+        <v>-278.4133113188975</v>
       </c>
       <c r="Q79">
-        <v>-272.1152346780568</v>
+        <v>-277.5133113188975</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1978202522809793</v>
+        <v>0.2047302637482966</v>
       </c>
       <c r="T79">
-        <v>2.212079901732029</v>
+        <v>2.312628988174394</v>
       </c>
       <c r="U79">
         <v>0.2546574882221671</v>
       </c>
       <c r="V79">
-        <v>0.1029491260873868</v>
+        <v>0.1016292654965229</v>
       </c>
       <c r="W79">
-        <v>0.228440722358086</v>
+        <v>0.2287768347409588</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3431637536246227</v>
+        <v>0.3387642183217429</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2234865891225732</v>
+        <v>0.2255751640047948</v>
       </c>
       <c r="C80">
-        <v>-1385.079588239379</v>
+        <v>-1423.009858205997</v>
       </c>
       <c r="D80">
-        <v>695.7164117606212</v>
+        <v>688.0681417940029</v>
       </c>
       <c r="E80">
-        <v>1513.696</v>
+        <v>1543.978</v>
       </c>
       <c r="F80">
-        <v>2361.996</v>
+        <v>2392.278</v>
       </c>
       <c r="G80">
         <v>281.2</v>
@@ -7853,37 +7853,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M80">
-        <v>601.4999685508059</v>
+        <v>609.2115066091494</v>
       </c>
       <c r="N80">
-        <v>-397.7333018841392</v>
+        <v>-405.4448399424828</v>
       </c>
       <c r="O80">
-        <v>-119.3199905652418</v>
+        <v>-121.6334519827448</v>
       </c>
       <c r="P80">
-        <v>-278.4133113188975</v>
+        <v>-283.8113879597379</v>
       </c>
       <c r="Q80">
-        <v>-277.5133113188975</v>
+        <v>-282.911387959738</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2047302637482966</v>
+        <v>0.2122983715458345</v>
       </c>
       <c r="T80">
-        <v>2.312628988174394</v>
+        <v>2.422754178087461</v>
       </c>
       <c r="U80">
         <v>0.2546574882221671</v>
       </c>
       <c r="V80">
-        <v>0.1016292654965229</v>
+        <v>0.1003428190978327</v>
       </c>
       <c r="W80">
-        <v>0.2287768347409588</v>
+        <v>0.2291044379495817</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3387642183217429</v>
+        <v>0.3344760636594424</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2255751640047948</v>
+        <v>0.2276637388870165</v>
       </c>
       <c r="C81">
-        <v>-1423.009858205997</v>
+        <v>-1460.773796154526</v>
       </c>
       <c r="D81">
-        <v>688.0681417940029</v>
+        <v>680.5862038454737</v>
       </c>
       <c r="E81">
-        <v>1543.978</v>
+        <v>1574.26</v>
       </c>
       <c r="F81">
-        <v>2392.278</v>
+        <v>2422.56</v>
       </c>
       <c r="G81">
         <v>281.2</v>
@@ -7935,37 +7935,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M81">
-        <v>609.2115066091494</v>
+        <v>616.9230446674932</v>
       </c>
       <c r="N81">
-        <v>-405.4448399424828</v>
+        <v>-413.1563780008265</v>
       </c>
       <c r="O81">
-        <v>-121.6334519827448</v>
+        <v>-123.946913400248</v>
       </c>
       <c r="P81">
-        <v>-283.8113879597379</v>
+        <v>-289.2094646005786</v>
       </c>
       <c r="Q81">
-        <v>-282.911387959738</v>
+        <v>-288.3094646005786</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2122983715458345</v>
+        <v>0.2206232901231263</v>
       </c>
       <c r="T81">
-        <v>2.422754178087461</v>
+        <v>2.543891886991834</v>
       </c>
       <c r="U81">
         <v>0.2546574882221671</v>
       </c>
       <c r="V81">
-        <v>0.1003428190978327</v>
+        <v>0.0990885338591098</v>
       </c>
       <c r="W81">
-        <v>0.2291044379495817</v>
+        <v>0.229423851077989</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3344760636594424</v>
+        <v>0.3302951128636993</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2276637388870165</v>
+        <v>0.2297523137692382</v>
       </c>
       <c r="C82">
-        <v>-1460.773796154526</v>
+        <v>-1498.376769717899</v>
       </c>
       <c r="D82">
-        <v>680.5862038454737</v>
+        <v>673.2652302821014</v>
       </c>
       <c r="E82">
-        <v>1574.26</v>
+        <v>1604.542</v>
       </c>
       <c r="F82">
-        <v>2422.56</v>
+        <v>2452.842</v>
       </c>
       <c r="G82">
         <v>281.2</v>
@@ -8017,37 +8017,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M82">
-        <v>616.9230446674932</v>
+        <v>624.6345827258368</v>
       </c>
       <c r="N82">
-        <v>-413.1563780008265</v>
+        <v>-420.8679160591702</v>
       </c>
       <c r="O82">
-        <v>-123.946913400248</v>
+        <v>-126.260374817751</v>
       </c>
       <c r="P82">
-        <v>-289.2094646005786</v>
+        <v>-294.6075412414191</v>
       </c>
       <c r="Q82">
-        <v>-288.3094646005786</v>
+        <v>-293.7075412414192</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2206232901231263</v>
+        <v>0.2298245159190803</v>
       </c>
       <c r="T82">
-        <v>2.543891886991834</v>
+        <v>2.677780933675615</v>
       </c>
       <c r="U82">
         <v>0.2546574882221671</v>
       </c>
       <c r="V82">
-        <v>0.0990885338591098</v>
+        <v>0.09786521862628129</v>
       </c>
       <c r="W82">
-        <v>0.229423851077989</v>
+        <v>0.2297353774624851</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3302951128636993</v>
+        <v>0.3262173954209375</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2297523137692382</v>
+        <v>0.2318408886514598</v>
       </c>
       <c r="C83">
-        <v>-1498.376769717899</v>
+        <v>-1535.823918031366</v>
       </c>
       <c r="D83">
-        <v>673.2652302821014</v>
+        <v>666.1000819686337</v>
       </c>
       <c r="E83">
-        <v>1604.542</v>
+        <v>1634.824</v>
       </c>
       <c r="F83">
-        <v>2452.842</v>
+        <v>2483.124</v>
       </c>
       <c r="G83">
         <v>281.2</v>
@@ -8099,37 +8099,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M83">
-        <v>624.6345827258368</v>
+        <v>632.3461207841806</v>
       </c>
       <c r="N83">
-        <v>-420.8679160591702</v>
+        <v>-428.5794541175139</v>
       </c>
       <c r="O83">
-        <v>-126.260374817751</v>
+        <v>-128.5738362352542</v>
       </c>
       <c r="P83">
-        <v>-294.6075412414191</v>
+        <v>-300.0056178822598</v>
       </c>
       <c r="Q83">
-        <v>-293.7075412414192</v>
+        <v>-299.1056178822598</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2298245159190803</v>
+        <v>0.240048100136807</v>
       </c>
       <c r="T83">
-        <v>2.677780933675615</v>
+        <v>2.826546541102038</v>
       </c>
       <c r="U83">
         <v>0.2546574882221671</v>
       </c>
       <c r="V83">
-        <v>0.09786521862628129</v>
+        <v>0.096671740350351</v>
       </c>
       <c r="W83">
-        <v>0.2297353774624851</v>
+        <v>0.2300393056424812</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3262173954209375</v>
+        <v>0.32223913450117</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2318408886514598</v>
+        <v>0.2339294635336815</v>
       </c>
       <c r="C84">
-        <v>-1535.823918031366</v>
+        <v>-1573.120163763265</v>
       </c>
       <c r="D84">
-        <v>666.1000819686337</v>
+        <v>659.0858362367348</v>
       </c>
       <c r="E84">
-        <v>1634.824</v>
+        <v>1665.106</v>
       </c>
       <c r="F84">
-        <v>2483.124</v>
+        <v>2513.406</v>
       </c>
       <c r="G84">
         <v>281.2</v>
@@ -8181,37 +8181,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M84">
-        <v>632.3461207841806</v>
+        <v>640.0576588425241</v>
       </c>
       <c r="N84">
-        <v>-428.5794541175139</v>
+        <v>-436.2909921758575</v>
       </c>
       <c r="O84">
-        <v>-128.5738362352542</v>
+        <v>-130.8872976527572</v>
       </c>
       <c r="P84">
-        <v>-300.0056178822598</v>
+        <v>-305.4036945231002</v>
       </c>
       <c r="Q84">
-        <v>-299.1056178822598</v>
+        <v>-304.5036945231003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.240048100136807</v>
+        <v>0.2514744589683838</v>
       </c>
       <c r="T84">
-        <v>2.826546541102038</v>
+        <v>2.992813984696276</v>
       </c>
       <c r="U84">
         <v>0.2546574882221671</v>
       </c>
       <c r="V84">
-        <v>0.096671740350351</v>
+        <v>0.09550702058709377</v>
       </c>
       <c r="W84">
-        <v>0.2300393056424812</v>
+        <v>0.230335910251875</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.32223913450117</v>
+        <v>0.3183567352903126</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2339294635336815</v>
+        <v>0.2360180384159032</v>
       </c>
       <c r="C85">
-        <v>-1573.120163763265</v>
+        <v>-1610.270224393576</v>
       </c>
       <c r="D85">
-        <v>659.0858362367348</v>
+        <v>652.2177756064242</v>
       </c>
       <c r="E85">
-        <v>1665.106</v>
+        <v>1695.388</v>
       </c>
       <c r="F85">
-        <v>2513.406</v>
+        <v>2543.688</v>
       </c>
       <c r="G85">
         <v>281.2</v>
@@ -8263,37 +8263,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M85">
-        <v>640.0576588425241</v>
+        <v>647.7691969008679</v>
       </c>
       <c r="N85">
-        <v>-436.2909921758575</v>
+        <v>-444.0025302342012</v>
       </c>
       <c r="O85">
-        <v>-130.8872976527572</v>
+        <v>-133.2007590702604</v>
       </c>
       <c r="P85">
-        <v>-305.4036945231002</v>
+        <v>-310.8017711639409</v>
       </c>
       <c r="Q85">
-        <v>-304.5036945231003</v>
+        <v>-309.9017711639409</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2514744589683838</v>
+        <v>0.2643291126539079</v>
       </c>
       <c r="T85">
-        <v>2.992813984696276</v>
+        <v>3.179864858739793</v>
       </c>
       <c r="U85">
         <v>0.2546574882221671</v>
       </c>
       <c r="V85">
-        <v>0.09550702058709377</v>
+        <v>0.09437003224677123</v>
       </c>
       <c r="W85">
-        <v>0.230335910251875</v>
+        <v>0.2306254528467594</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3183567352903126</v>
+        <v>0.3145667741559041</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2360180384159031</v>
+        <v>0.2381066132981249</v>
       </c>
       <c r="C86">
-        <v>-1610.270224393576</v>
+        <v>-1647.278622794584</v>
       </c>
       <c r="D86">
-        <v>652.2177756064242</v>
+        <v>645.4913772054157</v>
       </c>
       <c r="E86">
-        <v>1695.388</v>
+        <v>1725.67</v>
       </c>
       <c r="F86">
-        <v>2543.688</v>
+        <v>2573.97</v>
       </c>
       <c r="G86">
         <v>281.2</v>
@@ -8345,37 +8345,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M86">
-        <v>647.7691969008677</v>
+        <v>655.4807349592114</v>
       </c>
       <c r="N86">
-        <v>-444.002530234201</v>
+        <v>-451.7140682925448</v>
       </c>
       <c r="O86">
-        <v>-133.2007590702603</v>
+        <v>-135.5142204877634</v>
       </c>
       <c r="P86">
-        <v>-310.8017711639407</v>
+        <v>-316.1998478047814</v>
       </c>
       <c r="Q86">
-        <v>-309.9017711639407</v>
+        <v>-315.2998478047814</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2643291126539077</v>
+        <v>0.2788977201641683</v>
       </c>
       <c r="T86">
-        <v>3.179864858739791</v>
+        <v>3.391855849322444</v>
       </c>
       <c r="U86">
         <v>0.2546574882221671</v>
       </c>
       <c r="V86">
-        <v>0.09437003224677126</v>
+        <v>0.09325979657327982</v>
       </c>
       <c r="W86">
-        <v>0.2306254528467594</v>
+        <v>0.2309081826747054</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3145667741559042</v>
+        <v>0.3108659885775994</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2381066132981249</v>
+        <v>0.2401951881803465</v>
       </c>
       <c r="C87">
-        <v>-1647.278622794584</v>
+        <v>-1684.1496971635</v>
       </c>
       <c r="D87">
-        <v>645.4913772054157</v>
+        <v>638.9023028365</v>
       </c>
       <c r="E87">
-        <v>1725.67</v>
+        <v>1755.952</v>
       </c>
       <c r="F87">
-        <v>2573.97</v>
+        <v>2604.252</v>
       </c>
       <c r="G87">
         <v>281.2</v>
@@ -8427,37 +8427,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M87">
-        <v>655.4807349592114</v>
+        <v>663.1922730175551</v>
       </c>
       <c r="N87">
-        <v>-451.7140682925448</v>
+        <v>-459.4256063508884</v>
       </c>
       <c r="O87">
-        <v>-135.5142204877634</v>
+        <v>-137.8276819052665</v>
       </c>
       <c r="P87">
-        <v>-316.1998478047814</v>
+        <v>-321.5979244456219</v>
       </c>
       <c r="Q87">
-        <v>-315.2998478047814</v>
+        <v>-320.6979244456219</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2788977201641683</v>
+        <v>0.2955475573187517</v>
       </c>
       <c r="T87">
-        <v>3.391855849322444</v>
+        <v>3.63413126713119</v>
       </c>
       <c r="U87">
         <v>0.2546574882221671</v>
       </c>
       <c r="V87">
-        <v>0.09325979657327982</v>
+        <v>0.09217538033405563</v>
       </c>
       <c r="W87">
-        <v>0.2309081826747054</v>
+        <v>0.2311843373903736</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3108659885775994</v>
+        <v>0.3072512677801854</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2401951881803465</v>
+        <v>0.2422837630625682</v>
       </c>
       <c r="C88">
-        <v>-1684.1496971635</v>
+        <v>-1720.887610352889</v>
       </c>
       <c r="D88">
-        <v>638.9023028365</v>
+        <v>632.4463896471107</v>
       </c>
       <c r="E88">
-        <v>1755.952</v>
+        <v>1786.234</v>
       </c>
       <c r="F88">
-        <v>2604.252</v>
+        <v>2634.534</v>
       </c>
       <c r="G88">
         <v>281.2</v>
@@ -8509,37 +8509,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M88">
-        <v>663.1922730175551</v>
+        <v>670.9038110758987</v>
       </c>
       <c r="N88">
-        <v>-459.4256063508884</v>
+        <v>-467.1371444092321</v>
       </c>
       <c r="O88">
-        <v>-137.8276819052665</v>
+        <v>-140.1411433227696</v>
       </c>
       <c r="P88">
-        <v>-321.5979244456219</v>
+        <v>-326.9960010864625</v>
       </c>
       <c r="Q88">
-        <v>-320.6979244456219</v>
+        <v>-326.0960010864625</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2955475573187517</v>
+        <v>0.3147589078817326</v>
       </c>
       <c r="T88">
-        <v>3.63413126713119</v>
+        <v>3.913679826141282</v>
       </c>
       <c r="U88">
         <v>0.2546574882221671</v>
       </c>
       <c r="V88">
-        <v>0.09217538033405563</v>
+        <v>0.09111589320377915</v>
       </c>
       <c r="W88">
-        <v>0.2311843373903736</v>
+        <v>0.2314541437217735</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3072512677801854</v>
+        <v>0.3037196440125971</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2422837630625682</v>
+        <v>0.2443723379447899</v>
       </c>
       <c r="C89">
-        <v>-1720.887610352889</v>
+        <v>-1757.496358641068</v>
       </c>
       <c r="D89">
-        <v>632.4463896471107</v>
+        <v>626.1196413589316</v>
       </c>
       <c r="E89">
-        <v>1786.234</v>
+        <v>1816.516</v>
       </c>
       <c r="F89">
-        <v>2634.534</v>
+        <v>2664.816</v>
       </c>
       <c r="G89">
         <v>281.2</v>
@@ -8591,37 +8591,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M89">
-        <v>670.9038110758987</v>
+        <v>678.6153491342424</v>
       </c>
       <c r="N89">
-        <v>-467.1371444092321</v>
+        <v>-474.8486824675757</v>
       </c>
       <c r="O89">
-        <v>-140.1411433227696</v>
+        <v>-142.4546047402727</v>
       </c>
       <c r="P89">
-        <v>-326.9960010864625</v>
+        <v>-332.394077727303</v>
       </c>
       <c r="Q89">
-        <v>-326.0960010864625</v>
+        <v>-331.494077727303</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3147589078817326</v>
+        <v>0.3371721502052104</v>
       </c>
       <c r="T89">
-        <v>3.913679826141282</v>
+        <v>4.239819811653056</v>
       </c>
       <c r="U89">
         <v>0.2546574882221671</v>
       </c>
       <c r="V89">
-        <v>0.09111589320377915</v>
+        <v>0.09008048532646347</v>
       </c>
       <c r="W89">
-        <v>0.2314541437217735</v>
+        <v>0.2317178180910961</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3037196440125971</v>
+        <v>0.3002682844215449</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2443723379447899</v>
+        <v>0.2464609128270115</v>
       </c>
       <c r="C90">
-        <v>-1757.496358641068</v>
+        <v>-1793.979779981307</v>
       </c>
       <c r="D90">
-        <v>626.1196413589316</v>
+        <v>619.9182200186926</v>
       </c>
       <c r="E90">
-        <v>1816.516</v>
+        <v>1846.798</v>
       </c>
       <c r="F90">
-        <v>2664.816</v>
+        <v>2695.098</v>
       </c>
       <c r="G90">
         <v>281.2</v>
@@ -8673,37 +8673,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M90">
-        <v>678.6153491342424</v>
+        <v>686.3268871925861</v>
       </c>
       <c r="N90">
-        <v>-474.8486824675757</v>
+        <v>-482.5602205259195</v>
       </c>
       <c r="O90">
-        <v>-142.4546047402727</v>
+        <v>-144.7680661577758</v>
       </c>
       <c r="P90">
-        <v>-332.394077727303</v>
+        <v>-337.7921543681437</v>
       </c>
       <c r="Q90">
-        <v>-331.494077727303</v>
+        <v>-336.8921543681437</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3371721502052104</v>
+        <v>0.3636605274965932</v>
       </c>
       <c r="T90">
-        <v>4.239819811653056</v>
+        <v>4.625257976348789</v>
       </c>
       <c r="U90">
         <v>0.2546574882221671</v>
       </c>
       <c r="V90">
-        <v>0.09008048532646347</v>
+        <v>0.08906834504189645</v>
       </c>
       <c r="W90">
-        <v>0.2317178180910961</v>
+        <v>0.2319755671936924</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3002682844215449</v>
+        <v>0.2968944834729881</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2464609128270115</v>
+        <v>0.2485494877092332</v>
       </c>
       <c r="C91">
-        <v>-1793.979779981307</v>
+        <v>-1830.341561765606</v>
       </c>
       <c r="D91">
-        <v>619.9182200186926</v>
+        <v>613.8384382343944</v>
       </c>
       <c r="E91">
-        <v>1846.798</v>
+        <v>1877.08</v>
       </c>
       <c r="F91">
-        <v>2695.098</v>
+        <v>2725.38</v>
       </c>
       <c r="G91">
         <v>281.2</v>
@@ -8755,37 +8755,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M91">
-        <v>686.3268871925861</v>
+        <v>694.0384252509298</v>
       </c>
       <c r="N91">
-        <v>-482.5602205259195</v>
+        <v>-490.2717585842631</v>
       </c>
       <c r="O91">
-        <v>-144.7680661577758</v>
+        <v>-147.0815275752789</v>
       </c>
       <c r="P91">
-        <v>-337.7921543681437</v>
+        <v>-343.1902310089842</v>
       </c>
       <c r="Q91">
-        <v>-336.8921543681437</v>
+        <v>-342.2902310089842</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3636605274965932</v>
+        <v>0.3954465802462526</v>
       </c>
       <c r="T91">
-        <v>4.625257976348789</v>
+        <v>5.087783773983668</v>
       </c>
       <c r="U91">
         <v>0.2546574882221671</v>
       </c>
       <c r="V91">
-        <v>0.08906834504189645</v>
+        <v>0.08807869676365315</v>
       </c>
       <c r="W91">
-        <v>0.2319755671936924</v>
+        <v>0.2322275885384533</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2968944834729881</v>
+        <v>0.2935956558788438</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2485494877092332</v>
+        <v>0.2506380625914549</v>
       </c>
       <c r="C92">
-        <v>-1830.341561765606</v>
+        <v>-1866.585248136058</v>
       </c>
       <c r="D92">
-        <v>613.8384382343944</v>
+        <v>607.8767518639418</v>
       </c>
       <c r="E92">
-        <v>1877.08</v>
+        <v>1907.362</v>
       </c>
       <c r="F92">
-        <v>2725.38</v>
+        <v>2755.662</v>
       </c>
       <c r="G92">
         <v>281.2</v>
@@ -8837,37 +8837,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M92">
-        <v>694.0384252509298</v>
+        <v>701.7499633092734</v>
       </c>
       <c r="N92">
-        <v>-490.2717585842631</v>
+        <v>-497.9832966426068</v>
       </c>
       <c r="O92">
-        <v>-147.0815275752789</v>
+        <v>-149.394988992782</v>
       </c>
       <c r="P92">
-        <v>-343.1902310089842</v>
+        <v>-348.5883076498247</v>
       </c>
       <c r="Q92">
-        <v>-342.2902310089842</v>
+        <v>-347.6883076498248</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3954465802462526</v>
+        <v>0.4342962002736139</v>
       </c>
       <c r="T92">
-        <v>5.087783773983668</v>
+        <v>5.653093082204076</v>
       </c>
       <c r="U92">
         <v>0.2546574882221671</v>
       </c>
       <c r="V92">
-        <v>0.08807869676365315</v>
+        <v>0.08711079899701961</v>
       </c>
       <c r="W92">
-        <v>0.2322275885384533</v>
+        <v>0.23247407095256</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2935956558788438</v>
+        <v>0.2903693299900654</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2506380625914549</v>
+        <v>0.2527266374736765</v>
       </c>
       <c r="C93">
-        <v>-1866.585248136058</v>
+        <v>-1902.714246874261</v>
       </c>
       <c r="D93">
-        <v>607.8767518639418</v>
+        <v>602.0297531257391</v>
       </c>
       <c r="E93">
-        <v>1907.362</v>
+        <v>1937.644</v>
       </c>
       <c r="F93">
-        <v>2755.662</v>
+        <v>2785.944</v>
       </c>
       <c r="G93">
         <v>281.2</v>
@@ -8919,37 +8919,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M93">
-        <v>701.7499633092734</v>
+        <v>709.4615013676171</v>
       </c>
       <c r="N93">
-        <v>-497.9832966426068</v>
+        <v>-505.6948347009504</v>
       </c>
       <c r="O93">
-        <v>-149.394988992782</v>
+        <v>-151.7084504102851</v>
       </c>
       <c r="P93">
-        <v>-348.5883076498247</v>
+        <v>-353.9863842906653</v>
       </c>
       <c r="Q93">
-        <v>-347.6883076498248</v>
+        <v>-353.0863842906654</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4342962002736139</v>
+        <v>0.4828582253078158</v>
       </c>
       <c r="T93">
-        <v>5.653093082204076</v>
+        <v>6.359729717479587</v>
       </c>
       <c r="U93">
         <v>0.2546574882221671</v>
       </c>
       <c r="V93">
-        <v>0.08711079899701961</v>
+        <v>0.08616394248618243</v>
       </c>
       <c r="W93">
-        <v>0.23247407095256</v>
+        <v>0.2327151950533166</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2903693299900654</v>
+        <v>0.2872131416206081</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2527266374736765</v>
+        <v>0.2548152123558982</v>
       </c>
       <c r="C94">
-        <v>-1902.714246874261</v>
+        <v>-1938.7318358969</v>
       </c>
       <c r="D94">
-        <v>602.0297531257391</v>
+        <v>596.2941641030998</v>
       </c>
       <c r="E94">
-        <v>1937.644</v>
+        <v>1967.926</v>
       </c>
       <c r="F94">
-        <v>2785.944</v>
+        <v>2816.226</v>
       </c>
       <c r="G94">
         <v>281.2</v>
@@ -9001,37 +9001,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M94">
-        <v>709.4615013676171</v>
+        <v>717.1730394259608</v>
       </c>
       <c r="N94">
-        <v>-505.6948347009504</v>
+        <v>-513.4063727592942</v>
       </c>
       <c r="O94">
-        <v>-151.7084504102851</v>
+        <v>-154.0219118277882</v>
       </c>
       <c r="P94">
-        <v>-353.9863842906653</v>
+        <v>-359.3844609315059</v>
       </c>
       <c r="Q94">
-        <v>-353.0863842906654</v>
+        <v>-358.484460931506</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4828582253078158</v>
+        <v>0.5452951146375038</v>
       </c>
       <c r="T94">
-        <v>6.359729717479587</v>
+        <v>7.268262534262386</v>
       </c>
       <c r="U94">
         <v>0.2546574882221671</v>
       </c>
       <c r="V94">
-        <v>0.08616394248618243</v>
+        <v>0.08523744848095466</v>
       </c>
       <c r="W94">
-        <v>0.2327151950533166</v>
+        <v>0.2329511336895408</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2872131416206081</v>
+        <v>0.2841248282698489</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2548152123558982</v>
+        <v>0.2569037872381199</v>
       </c>
       <c r="C95">
-        <v>-1938.7318358969</v>
+        <v>-1974.641169383545</v>
       </c>
       <c r="D95">
-        <v>596.2941641030998</v>
+        <v>590.6668306164549</v>
       </c>
       <c r="E95">
-        <v>1967.926</v>
+        <v>1998.208</v>
       </c>
       <c r="F95">
-        <v>2816.226</v>
+        <v>2846.508</v>
       </c>
       <c r="G95">
         <v>281.2</v>
@@ -9083,37 +9083,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M95">
-        <v>717.1730394259608</v>
+        <v>724.8845774843044</v>
       </c>
       <c r="N95">
-        <v>-513.4063727592942</v>
+        <v>-521.1179108176377</v>
       </c>
       <c r="O95">
-        <v>-154.0219118277882</v>
+        <v>-156.3353732452913</v>
       </c>
       <c r="P95">
-        <v>-359.3844609315059</v>
+        <v>-364.7825375723464</v>
       </c>
       <c r="Q95">
-        <v>-358.484460931506</v>
+        <v>-363.8825375723465</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5452951146375038</v>
+        <v>0.6285443004104213</v>
       </c>
       <c r="T95">
-        <v>7.268262534262386</v>
+        <v>8.47963962330612</v>
       </c>
       <c r="U95">
         <v>0.2546574882221671</v>
       </c>
       <c r="V95">
-        <v>0.08523744848095466</v>
+        <v>0.084330667114136</v>
       </c>
       <c r="W95">
-        <v>0.2329511336895408</v>
+        <v>0.2331820523547815</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2841248282698489</v>
+        <v>0.2811022237137867</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2569037872381199</v>
+        <v>0.2589923621203416</v>
       </c>
       <c r="C96">
-        <v>-1974.641169383545</v>
+        <v>-2010.445283560706</v>
       </c>
       <c r="D96">
-        <v>590.6668306164549</v>
+        <v>585.1447164392938</v>
       </c>
       <c r="E96">
-        <v>1998.208</v>
+        <v>2028.49</v>
       </c>
       <c r="F96">
-        <v>2846.508</v>
+        <v>2876.79</v>
       </c>
       <c r="G96">
         <v>281.2</v>
@@ -9165,37 +9165,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M96">
-        <v>724.8845774843044</v>
+        <v>732.5961155426481</v>
       </c>
       <c r="N96">
-        <v>-521.1179108176377</v>
+        <v>-528.8294488759815</v>
       </c>
       <c r="O96">
-        <v>-156.3353732452913</v>
+        <v>-158.6488346627944</v>
       </c>
       <c r="P96">
-        <v>-364.7825375723464</v>
+        <v>-370.180614213187</v>
       </c>
       <c r="Q96">
-        <v>-363.8825375723465</v>
+        <v>-369.2806142131871</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6285443004104213</v>
+        <v>0.745093160492506</v>
       </c>
       <c r="T96">
-        <v>8.47963962330612</v>
+        <v>10.17556754796735</v>
       </c>
       <c r="U96">
         <v>0.2546574882221671</v>
       </c>
       <c r="V96">
-        <v>0.084330667114136</v>
+        <v>0.08344297588135562</v>
       </c>
       <c r="W96">
-        <v>0.2331820523547815</v>
+        <v>0.2334081095744382</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2811022237137867</v>
+        <v>0.278143252937852</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2589923621203416</v>
+        <v>0.2610809370025632</v>
       </c>
       <c r="C97">
-        <v>-2010.445283560706</v>
+        <v>-2046.147102164452</v>
       </c>
       <c r="D97">
-        <v>585.1447164392938</v>
+        <v>579.7248978355477</v>
       </c>
       <c r="E97">
-        <v>2028.49</v>
+        <v>2058.772</v>
       </c>
       <c r="F97">
-        <v>2876.79</v>
+        <v>2907.072</v>
       </c>
       <c r="G97">
         <v>281.2</v>
@@ -9247,37 +9247,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M97">
-        <v>732.5961155426481</v>
+        <v>740.3076536009918</v>
       </c>
       <c r="N97">
-        <v>-528.8294488759815</v>
+        <v>-536.5409869343251</v>
       </c>
       <c r="O97">
-        <v>-158.6488346627944</v>
+        <v>-160.9622960802975</v>
       </c>
       <c r="P97">
-        <v>-370.180614213187</v>
+        <v>-375.5786908540276</v>
       </c>
       <c r="Q97">
-        <v>-369.2806142131871</v>
+        <v>-374.6786908540276</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.745093160492506</v>
+        <v>0.9199164506156327</v>
       </c>
       <c r="T97">
-        <v>10.17556754796735</v>
+        <v>12.71945943495919</v>
       </c>
       <c r="U97">
         <v>0.2546574882221671</v>
       </c>
       <c r="V97">
-        <v>0.08344297588135562</v>
+        <v>0.08257377821592483</v>
       </c>
       <c r="W97">
-        <v>0.2334081095744382</v>
+        <v>0.2336294572686854</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.278143252937852</v>
+        <v>0.2752459273864161</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2610809370025632</v>
+        <v>0.2631695118847849</v>
       </c>
       <c r="C98">
-        <v>-2046.147102164452</v>
+        <v>-2081.749441602233</v>
       </c>
       <c r="D98">
-        <v>579.7248978355477</v>
+        <v>574.4045583977671</v>
       </c>
       <c r="E98">
-        <v>2058.772</v>
+        <v>2089.054</v>
       </c>
       <c r="F98">
-        <v>2907.072</v>
+        <v>2937.354</v>
       </c>
       <c r="G98">
         <v>281.2</v>
@@ -9329,37 +9329,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M98">
-        <v>740.3076536009917</v>
+        <v>748.0191916593354</v>
       </c>
       <c r="N98">
-        <v>-536.540986934325</v>
+        <v>-544.2525249926688</v>
       </c>
       <c r="O98">
-        <v>-160.9622960802975</v>
+        <v>-163.2757574978006</v>
       </c>
       <c r="P98">
-        <v>-375.5786908540275</v>
+        <v>-380.9767674948681</v>
       </c>
       <c r="Q98">
-        <v>-374.6786908540275</v>
+        <v>-380.0767674948681</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9199164506156303</v>
+        <v>1.211288600820841</v>
       </c>
       <c r="T98">
-        <v>12.71945943495916</v>
+        <v>16.95927924661221</v>
       </c>
       <c r="U98">
         <v>0.2546574882221671</v>
       </c>
       <c r="V98">
-        <v>0.08257377821592485</v>
+        <v>0.08172250215184312</v>
       </c>
       <c r="W98">
-        <v>0.2336294572686854</v>
+        <v>0.2338462410929481</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2752459273864161</v>
+        <v>0.2724083405061437</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2631695118847849</v>
+        <v>0.2652580867670066</v>
       </c>
       <c r="C99">
-        <v>-2081.749441602233</v>
+        <v>-2117.255015833052</v>
       </c>
       <c r="D99">
-        <v>574.4045583977671</v>
+        <v>569.1809841669481</v>
       </c>
       <c r="E99">
-        <v>2089.054</v>
+        <v>2119.336</v>
       </c>
       <c r="F99">
-        <v>2937.354</v>
+        <v>2967.636</v>
       </c>
       <c r="G99">
         <v>281.2</v>
@@ -9411,37 +9411,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M99">
-        <v>748.0191916593354</v>
+        <v>755.7307297176791</v>
       </c>
       <c r="N99">
-        <v>-544.2525249926688</v>
+        <v>-551.9640630510124</v>
       </c>
       <c r="O99">
-        <v>-163.2757574978006</v>
+        <v>-165.5892189153037</v>
       </c>
       <c r="P99">
-        <v>-380.9767674948681</v>
+        <v>-386.3748441357087</v>
       </c>
       <c r="Q99">
-        <v>-380.0767674948681</v>
+        <v>-385.4748441357087</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.211288600820841</v>
+        <v>1.794032901231261</v>
       </c>
       <c r="T99">
-        <v>16.95927924661221</v>
+        <v>25.43891886991831</v>
       </c>
       <c r="U99">
         <v>0.2546574882221671</v>
       </c>
       <c r="V99">
-        <v>0.08172250215184312</v>
+        <v>0.08088859906866107</v>
       </c>
       <c r="W99">
-        <v>0.2338462410929481</v>
+        <v>0.234058600757532</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2724083405061437</v>
+        <v>0.2696286635622035</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2652580867670066</v>
+        <v>0.2673466616492282</v>
       </c>
       <c r="C100">
-        <v>-2117.255015833052</v>
+        <v>-2152.666440983766</v>
       </c>
       <c r="D100">
-        <v>569.1809841669481</v>
+        <v>564.0515590162335</v>
       </c>
       <c r="E100">
-        <v>2119.336</v>
+        <v>2149.617999999999</v>
       </c>
       <c r="F100">
-        <v>2967.636</v>
+        <v>2997.918</v>
       </c>
       <c r="G100">
         <v>281.2</v>
@@ -9493,37 +9493,37 @@
         <v>203.7666666666667</v>
       </c>
       <c r="M100">
-        <v>755.7307297176791</v>
+        <v>763.4422677760227</v>
       </c>
       <c r="N100">
-        <v>-551.9640630510124</v>
+        <v>-559.6756011093561</v>
       </c>
       <c r="O100">
-        <v>-165.5892189153037</v>
+        <v>-167.9026803328068</v>
       </c>
       <c r="P100">
-        <v>-386.3748441357087</v>
+        <v>-391.7729207765493</v>
       </c>
       <c r="Q100">
-        <v>-385.4748441357087</v>
+        <v>-390.8729207765493</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.794032901231261</v>
+        <v>3.542265802462521</v>
       </c>
       <c r="T100">
-        <v>25.43891886991831</v>
+        <v>50.87783773983662</v>
       </c>
       <c r="U100">
         <v>0.2546574882221671</v>
       </c>
       <c r="V100">
-        <v>0.08088859906866107</v>
+        <v>0.08007154251241196</v>
       </c>
       <c r="W100">
-        <v>0.234058600757532</v>
+        <v>0.2342666703278818</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2696286635622035</v>
+        <v>0.2669051417080398</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2673466616492282</v>
-      </c>
-      <c r="C101">
-        <v>-2152.666440983766</v>
-      </c>
-      <c r="D101">
-        <v>564.0515590162335</v>
-      </c>
-      <c r="E101">
-        <v>2149.617999999999</v>
-      </c>
-      <c r="F101">
-        <v>2997.918</v>
-      </c>
-      <c r="G101">
-        <v>281.2</v>
-      </c>
-      <c r="H101">
-        <v>2179.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>204.6666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.8999999999999773</v>
-      </c>
-      <c r="L101">
-        <v>203.7666666666667</v>
-      </c>
-      <c r="M101">
-        <v>763.4422677760227</v>
-      </c>
-      <c r="N101">
-        <v>-559.6756011093561</v>
-      </c>
-      <c r="O101">
-        <v>-167.9026803328068</v>
-      </c>
-      <c r="P101">
-        <v>-391.7729207765493</v>
-      </c>
-      <c r="Q101">
-        <v>-390.8729207765493</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.542265802462521</v>
-      </c>
-      <c r="T101">
-        <v>50.87783773983662</v>
-      </c>
-      <c r="U101">
-        <v>0.2546574882221671</v>
-      </c>
-      <c r="V101">
-        <v>0.08007154251241196</v>
-      </c>
-      <c r="W101">
-        <v>0.2342666703278818</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2669051417080398</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
